--- a/demo2-xlsx/demo2-input_3.xlsx
+++ b/demo2-xlsx/demo2-input_3.xlsx
@@ -4700,14 +4700,34 @@
       </c>
       <c r="B73" s="39" t="inlineStr">
         <is>
-          <t>İçerik / Metin  (düzenlenebilir)</t>
-        </is>
-      </c>
-      <c r="C73" s="39" t="n"/>
-      <c r="D73" s="39" t="n"/>
-      <c r="E73" s="39" t="n"/>
-      <c r="F73" s="39" t="n"/>
-      <c r="G73" s="39" t="n"/>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C73" s="39" t="inlineStr">
+        <is>
+          <t>İçerik / URL</t>
+        </is>
+      </c>
+      <c r="D73" s="39" t="inlineStr">
+        <is>
+          <t>Genişlik</t>
+        </is>
+      </c>
+      <c r="E73" s="39" t="inlineStr">
+        <is>
+          <t>Yükseklik</t>
+        </is>
+      </c>
+      <c r="F73" s="39" t="inlineStr">
+        <is>
+          <t>Caption</t>
+        </is>
+      </c>
+      <c r="G73" s="39" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
       <c r="H73" s="39" t="n"/>
       <c r="I73" s="39" t="n"/>
       <c r="J73" s="39" t="n"/>
@@ -4725,24 +4745,16 @@
       </c>
       <c r="B74" s="85" t="inlineStr">
         <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
           <t>Interaktif 3D gayrimenkul deneyimine hoş geldiniz.
 Bu demo, yeni nesil konut projesinin tüm detaylarını immersive bir ortamda sunmaktadır.
 ▶ Başlamak için ekrana tıklayın</t>
         </is>
       </c>
-      <c r="C74" s="86" t="n"/>
-      <c r="D74" s="86" t="n"/>
-      <c r="E74" s="86" t="n"/>
-      <c r="F74" s="86" t="n"/>
-      <c r="G74" s="86" t="n"/>
-      <c r="H74" s="86" t="n"/>
-      <c r="I74" s="86" t="n"/>
-      <c r="J74" s="86" t="n"/>
-      <c r="K74" s="86" t="n"/>
-      <c r="L74" s="86" t="n"/>
-      <c r="M74" s="86" t="n"/>
-      <c r="N74" s="86" t="n"/>
-      <c r="O74" s="87" t="n"/>
     </row>
     <row r="75" ht="18" customHeight="1" s="72">
       <c r="A75" s="32" t="inlineStr">
@@ -5531,14 +5543,34 @@
       </c>
       <c r="B88" s="45" t="inlineStr">
         <is>
-          <t>İçerik / Metin  (düzenlenebilir)</t>
-        </is>
-      </c>
-      <c r="C88" s="45" t="n"/>
-      <c r="D88" s="45" t="n"/>
-      <c r="E88" s="45" t="n"/>
-      <c r="F88" s="45" t="n"/>
-      <c r="G88" s="45" t="n"/>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C88" s="45" t="inlineStr">
+        <is>
+          <t>İçerik / URL</t>
+        </is>
+      </c>
+      <c r="D88" s="45" t="inlineStr">
+        <is>
+          <t>Genişlik</t>
+        </is>
+      </c>
+      <c r="E88" s="45" t="inlineStr">
+        <is>
+          <t>Yükseklik</t>
+        </is>
+      </c>
+      <c r="F88" s="45" t="inlineStr">
+        <is>
+          <t>Caption</t>
+        </is>
+      </c>
+      <c r="G88" s="45" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
       <c r="H88" s="45" t="n"/>
       <c r="I88" s="45" t="n"/>
       <c r="J88" s="45" t="n"/>
@@ -5556,6 +5588,11 @@
       </c>
       <c r="B89" s="89" t="inlineStr">
         <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
           <t>Proje: Nova Residence
 Geliştirici: VEA Development
 Konum: İstanbul, Türkiye
@@ -5563,19 +5600,6 @@
 Toplam Ünite: 240</t>
         </is>
       </c>
-      <c r="C89" s="90" t="n"/>
-      <c r="D89" s="90" t="n"/>
-      <c r="E89" s="90" t="n"/>
-      <c r="F89" s="90" t="n"/>
-      <c r="G89" s="90" t="n"/>
-      <c r="H89" s="90" t="n"/>
-      <c r="I89" s="90" t="n"/>
-      <c r="J89" s="90" t="n"/>
-      <c r="K89" s="90" t="n"/>
-      <c r="L89" s="90" t="n"/>
-      <c r="M89" s="90" t="n"/>
-      <c r="N89" s="90" t="n"/>
-      <c r="O89" s="91" t="n"/>
     </row>
     <row r="90" ht="18" customHeight="1" s="72">
       <c r="A90" s="92" t="inlineStr">
@@ -5583,37 +5607,37 @@
           <t xml:space="preserve">  ↓  Bu panel için ek içerik slotları (SAĞ):</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="0" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C90" s="0" t="inlineStr">
         <is>
           <t>İçerik / URL</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D90" s="0" t="inlineStr">
         <is>
           <t>Genişlik</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E90" s="0" t="inlineStr">
         <is>
           <t>Yükseklik</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F90" s="0" t="inlineStr">
         <is>
           <t>Caption</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="G90" s="0" t="inlineStr">
         <is>
           <t>Extra</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="I90" s="0" t="inlineStr">
         <is>
           <t>Slot Tipleri: text · html · image · video · youtube · drive · iframe · link · glb   |   Boyut örn: 300px, 100%, auto</t>
         </is>
@@ -8516,14 +8540,34 @@
       </c>
       <c r="B148" s="39" t="inlineStr">
         <is>
-          <t>İçerik / Metin  (düzenlenebilir)</t>
-        </is>
-      </c>
-      <c r="C148" s="39" t="n"/>
-      <c r="D148" s="39" t="n"/>
-      <c r="E148" s="39" t="n"/>
-      <c r="F148" s="39" t="n"/>
-      <c r="G148" s="39" t="n"/>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C148" s="39" t="inlineStr">
+        <is>
+          <t>İçerik / URL</t>
+        </is>
+      </c>
+      <c r="D148" s="39" t="inlineStr">
+        <is>
+          <t>Genişlik</t>
+        </is>
+      </c>
+      <c r="E148" s="39" t="inlineStr">
+        <is>
+          <t>Yükseklik</t>
+        </is>
+      </c>
+      <c r="F148" s="39" t="inlineStr">
+        <is>
+          <t>Caption</t>
+        </is>
+      </c>
+      <c r="G148" s="39" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
       <c r="H148" s="39" t="n"/>
       <c r="I148" s="39" t="n"/>
       <c r="J148" s="39" t="n"/>
@@ -8541,6 +8585,11 @@
       </c>
       <c r="B149" s="95" t="inlineStr">
         <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
           <t>Koordinatlar: 41.0082° K, 28.9784° D
 🚇 Metro A İstasyonu — 350m
 🚇 Metro B İstasyonu — 800m
@@ -8550,19 +8599,6 @@
 🌳 Kent Parkı — 200m</t>
         </is>
       </c>
-      <c r="C149" s="90" t="n"/>
-      <c r="D149" s="90" t="n"/>
-      <c r="E149" s="90" t="n"/>
-      <c r="F149" s="90" t="n"/>
-      <c r="G149" s="90" t="n"/>
-      <c r="H149" s="90" t="n"/>
-      <c r="I149" s="90" t="n"/>
-      <c r="J149" s="90" t="n"/>
-      <c r="K149" s="90" t="n"/>
-      <c r="L149" s="90" t="n"/>
-      <c r="M149" s="90" t="n"/>
-      <c r="N149" s="90" t="n"/>
-      <c r="O149" s="91" t="n"/>
     </row>
     <row r="150" ht="18" customHeight="1" s="72">
       <c r="A150" s="96" t="inlineStr">
@@ -8570,37 +8606,37 @@
           <t xml:space="preserve">  ↓  Bu panel için ek içerik slotları (SOL):</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
+      <c r="B150" s="0" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
+      <c r="C150" s="0" t="inlineStr">
         <is>
           <t>İçerik / URL</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
+      <c r="D150" s="0" t="inlineStr">
         <is>
           <t>Genişlik</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
+      <c r="E150" s="0" t="inlineStr">
         <is>
           <t>Yükseklik</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr">
+      <c r="F150" s="0" t="inlineStr">
         <is>
           <t>Caption</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr">
+      <c r="G150" s="0" t="inlineStr">
         <is>
           <t>Extra</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr">
+      <c r="I150" s="0" t="inlineStr">
         <is>
           <t>Slot Tipleri: text · html · image · video · youtube · drive · iframe · link · glb   |   Boyut örn: 300px, 100%, auto</t>
         </is>
@@ -9392,14 +9428,34 @@
       </c>
       <c r="B163" s="45" t="inlineStr">
         <is>
-          <t>İçerik / Metin  (düzenlenebilir)</t>
-        </is>
-      </c>
-      <c r="C163" s="45" t="n"/>
-      <c r="D163" s="45" t="n"/>
-      <c r="E163" s="45" t="n"/>
-      <c r="F163" s="45" t="n"/>
-      <c r="G163" s="45" t="n"/>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C163" s="45" t="inlineStr">
+        <is>
+          <t>İçerik / URL</t>
+        </is>
+      </c>
+      <c r="D163" s="45" t="inlineStr">
+        <is>
+          <t>Genişlik</t>
+        </is>
+      </c>
+      <c r="E163" s="45" t="inlineStr">
+        <is>
+          <t>Yükseklik</t>
+        </is>
+      </c>
+      <c r="F163" s="45" t="inlineStr">
+        <is>
+          <t>Caption</t>
+        </is>
+      </c>
+      <c r="G163" s="45" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
       <c r="H163" s="45" t="n"/>
       <c r="I163" s="45" t="n"/>
       <c r="J163" s="45" t="n"/>
@@ -9417,6 +9473,11 @@
       </c>
       <c r="B164" s="89" t="inlineStr">
         <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
           <t>Geliştirici: VEA Development A.Ş.
 4 Blok | 240 Daire | 1+1 / 2+1 / 3+1
 Teslim: Aralık 2026
@@ -9424,19 +9485,6 @@
 🌱 Enerji Sınıfı: A+</t>
         </is>
       </c>
-      <c r="C164" s="90" t="n"/>
-      <c r="D164" s="90" t="n"/>
-      <c r="E164" s="90" t="n"/>
-      <c r="F164" s="90" t="n"/>
-      <c r="G164" s="90" t="n"/>
-      <c r="H164" s="90" t="n"/>
-      <c r="I164" s="90" t="n"/>
-      <c r="J164" s="90" t="n"/>
-      <c r="K164" s="90" t="n"/>
-      <c r="L164" s="90" t="n"/>
-      <c r="M164" s="90" t="n"/>
-      <c r="N164" s="90" t="n"/>
-      <c r="O164" s="91" t="n"/>
     </row>
     <row r="165" ht="18" customHeight="1" s="72">
       <c r="A165" s="92" t="inlineStr">
@@ -9444,37 +9492,37 @@
           <t xml:space="preserve">  ↓  Bu panel için ek içerik slotları (SAĞ):</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
+      <c r="B165" s="0" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr">
+      <c r="C165" s="0" t="inlineStr">
         <is>
           <t>İçerik / URL</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr">
+      <c r="D165" s="0" t="inlineStr">
         <is>
           <t>Genişlik</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
+      <c r="E165" s="0" t="inlineStr">
         <is>
           <t>Yükseklik</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr">
+      <c r="F165" s="0" t="inlineStr">
         <is>
           <t>Caption</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr">
+      <c r="G165" s="0" t="inlineStr">
         <is>
           <t>Extra</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr">
+      <c r="I165" s="0" t="inlineStr">
         <is>
           <t>Slot Tipleri: text · html · image · video · youtube · drive · iframe · link · glb   |   Boyut örn: 300px, 100%, auto</t>
         </is>
@@ -10266,14 +10314,34 @@
       </c>
       <c r="B178" s="39" t="inlineStr">
         <is>
-          <t>İçerik / Metin  (düzenlenebilir)</t>
-        </is>
-      </c>
-      <c r="C178" s="39" t="n"/>
-      <c r="D178" s="39" t="n"/>
-      <c r="E178" s="39" t="n"/>
-      <c r="F178" s="39" t="n"/>
-      <c r="G178" s="39" t="n"/>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C178" s="39" t="inlineStr">
+        <is>
+          <t>İçerik / URL</t>
+        </is>
+      </c>
+      <c r="D178" s="39" t="inlineStr">
+        <is>
+          <t>Genişlik</t>
+        </is>
+      </c>
+      <c r="E178" s="39" t="inlineStr">
+        <is>
+          <t>Yükseklik</t>
+        </is>
+      </c>
+      <c r="F178" s="39" t="inlineStr">
+        <is>
+          <t>Caption</t>
+        </is>
+      </c>
+      <c r="G178" s="39" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
       <c r="H178" s="39" t="n"/>
       <c r="I178" s="39" t="n"/>
       <c r="J178" s="39" t="n"/>
@@ -10291,6 +10359,11 @@
       </c>
       <c r="B179" s="95" t="inlineStr">
         <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
           <t>🚇 M3 Metro Hattı — 350m
 🚌 Otobüs Durağı — 120m
 🚖 Taksi Durağı — 80m
@@ -10300,19 +10373,6 @@
 TEM Bağlantısı: 5 dk</t>
         </is>
       </c>
-      <c r="C179" s="90" t="n"/>
-      <c r="D179" s="90" t="n"/>
-      <c r="E179" s="90" t="n"/>
-      <c r="F179" s="90" t="n"/>
-      <c r="G179" s="90" t="n"/>
-      <c r="H179" s="90" t="n"/>
-      <c r="I179" s="90" t="n"/>
-      <c r="J179" s="90" t="n"/>
-      <c r="K179" s="90" t="n"/>
-      <c r="L179" s="90" t="n"/>
-      <c r="M179" s="90" t="n"/>
-      <c r="N179" s="90" t="n"/>
-      <c r="O179" s="91" t="n"/>
     </row>
     <row r="180" ht="18" customHeight="1" s="72">
       <c r="A180" s="96" t="inlineStr">
@@ -10320,37 +10380,37 @@
           <t xml:space="preserve">  ↓  Bu panel için ek içerik slotları (SOL):</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
+      <c r="B180" s="0" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr">
+      <c r="C180" s="0" t="inlineStr">
         <is>
           <t>İçerik / URL</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr">
+      <c r="D180" s="0" t="inlineStr">
         <is>
           <t>Genişlik</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr">
+      <c r="E180" s="0" t="inlineStr">
         <is>
           <t>Yükseklik</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr">
+      <c r="F180" s="0" t="inlineStr">
         <is>
           <t>Caption</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr">
+      <c r="G180" s="0" t="inlineStr">
         <is>
           <t>Extra</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr">
+      <c r="I180" s="0" t="inlineStr">
         <is>
           <t>Slot Tipleri: text · html · image · video · youtube · drive · iframe · link · glb   |   Boyut örn: 300px, 100%, auto</t>
         </is>
@@ -11142,14 +11202,34 @@
       </c>
       <c r="B193" s="45" t="inlineStr">
         <is>
-          <t>İçerik / Metin  (düzenlenebilir)</t>
-        </is>
-      </c>
-      <c r="C193" s="45" t="n"/>
-      <c r="D193" s="45" t="n"/>
-      <c r="E193" s="45" t="n"/>
-      <c r="F193" s="45" t="n"/>
-      <c r="G193" s="45" t="n"/>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C193" s="45" t="inlineStr">
+        <is>
+          <t>İçerik / URL</t>
+        </is>
+      </c>
+      <c r="D193" s="45" t="inlineStr">
+        <is>
+          <t>Genişlik</t>
+        </is>
+      </c>
+      <c r="E193" s="45" t="inlineStr">
+        <is>
+          <t>Yükseklik</t>
+        </is>
+      </c>
+      <c r="F193" s="45" t="inlineStr">
+        <is>
+          <t>Caption</t>
+        </is>
+      </c>
+      <c r="G193" s="45" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
       <c r="H193" s="45" t="n"/>
       <c r="I193" s="45" t="n"/>
       <c r="J193" s="45" t="n"/>
@@ -11167,25 +11247,17 @@
       </c>
       <c r="B194" s="89" t="inlineStr">
         <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
           <t>Walk Score®: 9.2 / 10
 🚶 Yürünebilirlik: Mükemmel
 🚲 Bisiklet Dostu: İyi
 🚇 Toplu Ulaşım: Çok İyi</t>
         </is>
       </c>
-      <c r="C194" s="90" t="n"/>
-      <c r="D194" s="90" t="n"/>
-      <c r="E194" s="90" t="n"/>
-      <c r="F194" s="90" t="n"/>
-      <c r="G194" s="90" t="n"/>
-      <c r="H194" s="90" t="n"/>
-      <c r="I194" s="90" t="n"/>
-      <c r="J194" s="90" t="n"/>
-      <c r="K194" s="90" t="n"/>
-      <c r="L194" s="90" t="n"/>
-      <c r="M194" s="90" t="n"/>
-      <c r="N194" s="90" t="n"/>
-      <c r="O194" s="91" t="n"/>
     </row>
     <row r="195" ht="18" customHeight="1" s="72">
       <c r="A195" s="92" t="inlineStr">
@@ -11193,37 +11265,37 @@
           <t xml:space="preserve">  ↓  Bu panel için ek içerik slotları (SAĞ):</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
+      <c r="B195" s="0" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr">
+      <c r="C195" s="0" t="inlineStr">
         <is>
           <t>İçerik / URL</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr">
+      <c r="D195" s="0" t="inlineStr">
         <is>
           <t>Genişlik</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr">
+      <c r="E195" s="0" t="inlineStr">
         <is>
           <t>Yükseklik</t>
         </is>
       </c>
-      <c r="F195" t="inlineStr">
+      <c r="F195" s="0" t="inlineStr">
         <is>
           <t>Caption</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr">
+      <c r="G195" s="0" t="inlineStr">
         <is>
           <t>Extra</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr">
+      <c r="I195" s="0" t="inlineStr">
         <is>
           <t>Slot Tipleri: text · html · image · video · youtube · drive · iframe · link · glb   |   Boyut örn: 300px, 100%, auto</t>
         </is>
@@ -12015,14 +12087,34 @@
       </c>
       <c r="B208" s="39" t="inlineStr">
         <is>
-          <t>İçerik / Metin  (düzenlenebilir)</t>
-        </is>
-      </c>
-      <c r="C208" s="39" t="n"/>
-      <c r="D208" s="39" t="n"/>
-      <c r="E208" s="39" t="n"/>
-      <c r="F208" s="39" t="n"/>
-      <c r="G208" s="39" t="n"/>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C208" s="39" t="inlineStr">
+        <is>
+          <t>İçerik / URL</t>
+        </is>
+      </c>
+      <c r="D208" s="39" t="inlineStr">
+        <is>
+          <t>Genişlik</t>
+        </is>
+      </c>
+      <c r="E208" s="39" t="inlineStr">
+        <is>
+          <t>Yükseklik</t>
+        </is>
+      </c>
+      <c r="F208" s="39" t="inlineStr">
+        <is>
+          <t>Caption</t>
+        </is>
+      </c>
+      <c r="G208" s="39" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
       <c r="H208" s="39" t="n"/>
       <c r="I208" s="39" t="n"/>
       <c r="J208" s="39" t="n"/>
@@ -12040,6 +12132,11 @@
       </c>
       <c r="B209" s="95" t="inlineStr">
         <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
           <t>1+1 — 55–65 m² — 68 Daire
 2+1 — 85–100 m² — 120 Daire
 3+1 — 130–155 m² — 52 Daire
@@ -12047,19 +12144,6 @@
 ✅ Panoramik balkon her dairede</t>
         </is>
       </c>
-      <c r="C209" s="90" t="n"/>
-      <c r="D209" s="90" t="n"/>
-      <c r="E209" s="90" t="n"/>
-      <c r="F209" s="90" t="n"/>
-      <c r="G209" s="90" t="n"/>
-      <c r="H209" s="90" t="n"/>
-      <c r="I209" s="90" t="n"/>
-      <c r="J209" s="90" t="n"/>
-      <c r="K209" s="90" t="n"/>
-      <c r="L209" s="90" t="n"/>
-      <c r="M209" s="90" t="n"/>
-      <c r="N209" s="90" t="n"/>
-      <c r="O209" s="91" t="n"/>
     </row>
     <row r="210" ht="18" customHeight="1" s="72">
       <c r="A210" s="96" t="inlineStr">
@@ -12067,37 +12151,37 @@
           <t xml:space="preserve">  ↓  Bu panel için ek içerik slotları (SOL):</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr">
+      <c r="B210" s="0" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr">
+      <c r="C210" s="0" t="inlineStr">
         <is>
           <t>İçerik / URL</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr">
+      <c r="D210" s="0" t="inlineStr">
         <is>
           <t>Genişlik</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr">
+      <c r="E210" s="0" t="inlineStr">
         <is>
           <t>Yükseklik</t>
         </is>
       </c>
-      <c r="F210" t="inlineStr">
+      <c r="F210" s="0" t="inlineStr">
         <is>
           <t>Caption</t>
         </is>
       </c>
-      <c r="G210" t="inlineStr">
+      <c r="G210" s="0" t="inlineStr">
         <is>
           <t>Extra</t>
         </is>
       </c>
-      <c r="I210" t="inlineStr">
+      <c r="I210" s="0" t="inlineStr">
         <is>
           <t>Slot Tipleri: text · html · image · video · youtube · drive · iframe · link · glb   |   Boyut örn: 300px, 100%, auto</t>
         </is>
@@ -12889,14 +12973,34 @@
       </c>
       <c r="B223" s="45" t="inlineStr">
         <is>
-          <t>İçerik / Metin  (düzenlenebilir)</t>
-        </is>
-      </c>
-      <c r="C223" s="45" t="n"/>
-      <c r="D223" s="45" t="n"/>
-      <c r="E223" s="45" t="n"/>
-      <c r="F223" s="45" t="n"/>
-      <c r="G223" s="45" t="n"/>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C223" s="45" t="inlineStr">
+        <is>
+          <t>İçerik / URL</t>
+        </is>
+      </c>
+      <c r="D223" s="45" t="inlineStr">
+        <is>
+          <t>Genişlik</t>
+        </is>
+      </c>
+      <c r="E223" s="45" t="inlineStr">
+        <is>
+          <t>Yükseklik</t>
+        </is>
+      </c>
+      <c r="F223" s="45" t="inlineStr">
+        <is>
+          <t>Caption</t>
+        </is>
+      </c>
+      <c r="G223" s="45" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
       <c r="H223" s="45" t="n"/>
       <c r="I223" s="45" t="n"/>
       <c r="J223" s="45" t="n"/>
@@ -12914,25 +13018,17 @@
       </c>
       <c r="B224" s="89" t="inlineStr">
         <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
           <t>1+1 — 2.850.000 ₺'den başlayan
 2+1 — 4.200.000 ₺'den başlayan
 3+1 — 6.500.000 ₺'den başlayan
 * Fiyatlar piyasa koşullarına göre değişkenlik gösterebilir.</t>
         </is>
       </c>
-      <c r="C224" s="90" t="n"/>
-      <c r="D224" s="90" t="n"/>
-      <c r="E224" s="90" t="n"/>
-      <c r="F224" s="90" t="n"/>
-      <c r="G224" s="90" t="n"/>
-      <c r="H224" s="90" t="n"/>
-      <c r="I224" s="90" t="n"/>
-      <c r="J224" s="90" t="n"/>
-      <c r="K224" s="90" t="n"/>
-      <c r="L224" s="90" t="n"/>
-      <c r="M224" s="90" t="n"/>
-      <c r="N224" s="90" t="n"/>
-      <c r="O224" s="91" t="n"/>
     </row>
     <row r="225" ht="18" customHeight="1" s="72">
       <c r="A225" s="92" t="inlineStr">
@@ -12940,37 +13036,37 @@
           <t xml:space="preserve">  ↓  Bu panel için ek içerik slotları (SAĞ):</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
+      <c r="B225" s="0" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="C225" t="inlineStr">
+      <c r="C225" s="0" t="inlineStr">
         <is>
           <t>İçerik / URL</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr">
+      <c r="D225" s="0" t="inlineStr">
         <is>
           <t>Genişlik</t>
         </is>
       </c>
-      <c r="E225" t="inlineStr">
+      <c r="E225" s="0" t="inlineStr">
         <is>
           <t>Yükseklik</t>
         </is>
       </c>
-      <c r="F225" t="inlineStr">
+      <c r="F225" s="0" t="inlineStr">
         <is>
           <t>Caption</t>
         </is>
       </c>
-      <c r="G225" t="inlineStr">
+      <c r="G225" s="0" t="inlineStr">
         <is>
           <t>Extra</t>
         </is>
       </c>
-      <c r="I225" t="inlineStr">
+      <c r="I225" s="0" t="inlineStr">
         <is>
           <t>Slot Tipleri: text · html · image · video · youtube · drive · iframe · link · glb   |   Boyut örn: 300px, 100%, auto</t>
         </is>
@@ -15954,14 +16050,34 @@
       </c>
       <c r="B284" s="39" t="inlineStr">
         <is>
-          <t>İçerik / Metin  (düzenlenebilir)</t>
-        </is>
-      </c>
-      <c r="C284" s="39" t="n"/>
-      <c r="D284" s="39" t="n"/>
-      <c r="E284" s="39" t="n"/>
-      <c r="F284" s="39" t="n"/>
-      <c r="G284" s="39" t="n"/>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C284" s="39" t="inlineStr">
+        <is>
+          <t>İçerik / URL</t>
+        </is>
+      </c>
+      <c r="D284" s="39" t="inlineStr">
+        <is>
+          <t>Genişlik</t>
+        </is>
+      </c>
+      <c r="E284" s="39" t="inlineStr">
+        <is>
+          <t>Yükseklik</t>
+        </is>
+      </c>
+      <c r="F284" s="39" t="inlineStr">
+        <is>
+          <t>Caption</t>
+        </is>
+      </c>
+      <c r="G284" s="39" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
       <c r="H284" s="39" t="n"/>
       <c r="I284" s="39" t="n"/>
       <c r="J284" s="39" t="n"/>
@@ -15979,6 +16095,11 @@
       </c>
       <c r="B285" s="95" t="inlineStr">
         <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
           <t>Geleneksel mimari dil ile modern detayların buluştuğu tasarım.
 Cephe: Travertin &amp; Alüminyum
 Renk Paleti: Krem / Antrasit
@@ -15986,19 +16107,6 @@
 Bina Yüksekliği: 14 kat</t>
         </is>
       </c>
-      <c r="C285" s="90" t="n"/>
-      <c r="D285" s="90" t="n"/>
-      <c r="E285" s="90" t="n"/>
-      <c r="F285" s="90" t="n"/>
-      <c r="G285" s="90" t="n"/>
-      <c r="H285" s="90" t="n"/>
-      <c r="I285" s="90" t="n"/>
-      <c r="J285" s="90" t="n"/>
-      <c r="K285" s="90" t="n"/>
-      <c r="L285" s="90" t="n"/>
-      <c r="M285" s="90" t="n"/>
-      <c r="N285" s="90" t="n"/>
-      <c r="O285" s="91" t="n"/>
     </row>
     <row r="286" ht="18" customHeight="1" s="72">
       <c r="A286" s="96" t="inlineStr">
@@ -16006,37 +16114,37 @@
           <t xml:space="preserve">  ↓  Bu panel için ek içerik slotları (SOL):</t>
         </is>
       </c>
-      <c r="B286" t="inlineStr">
+      <c r="B286" s="0" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="C286" t="inlineStr">
+      <c r="C286" s="0" t="inlineStr">
         <is>
           <t>İçerik / URL</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr">
+      <c r="D286" s="0" t="inlineStr">
         <is>
           <t>Genişlik</t>
         </is>
       </c>
-      <c r="E286" t="inlineStr">
+      <c r="E286" s="0" t="inlineStr">
         <is>
           <t>Yükseklik</t>
         </is>
       </c>
-      <c r="F286" t="inlineStr">
+      <c r="F286" s="0" t="inlineStr">
         <is>
           <t>Caption</t>
         </is>
       </c>
-      <c r="G286" t="inlineStr">
+      <c r="G286" s="0" t="inlineStr">
         <is>
           <t>Extra</t>
         </is>
       </c>
-      <c r="I286" t="inlineStr">
+      <c r="I286" s="0" t="inlineStr">
         <is>
           <t>Slot Tipleri: text · html · image · video · youtube · drive · iframe · link · glb   |   Boyut örn: 300px, 100%, auto</t>
         </is>
@@ -16828,14 +16936,34 @@
       </c>
       <c r="B299" s="45" t="inlineStr">
         <is>
-          <t>İçerik / Metin  (düzenlenebilir)</t>
-        </is>
-      </c>
-      <c r="C299" s="45" t="n"/>
-      <c r="D299" s="45" t="n"/>
-      <c r="E299" s="45" t="n"/>
-      <c r="F299" s="45" t="n"/>
-      <c r="G299" s="45" t="n"/>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C299" s="45" t="inlineStr">
+        <is>
+          <t>İçerik / URL</t>
+        </is>
+      </c>
+      <c r="D299" s="45" t="inlineStr">
+        <is>
+          <t>Genişlik</t>
+        </is>
+      </c>
+      <c r="E299" s="45" t="inlineStr">
+        <is>
+          <t>Yükseklik</t>
+        </is>
+      </c>
+      <c r="F299" s="45" t="inlineStr">
+        <is>
+          <t>Caption</t>
+        </is>
+      </c>
+      <c r="G299" s="45" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
       <c r="H299" s="45" t="n"/>
       <c r="I299" s="45" t="n"/>
       <c r="J299" s="45" t="n"/>
@@ -16853,6 +16981,11 @@
       </c>
       <c r="B300" s="89" t="inlineStr">
         <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
           <t>✅ Düşük bakım maliyeti
 ✅ Zamansız estetik
 ✅ Daha iyi ısı yalıtımı
@@ -16860,19 +16993,6 @@
 ⭐ En Çok Tercih Edilen Seçenek</t>
         </is>
       </c>
-      <c r="C300" s="90" t="n"/>
-      <c r="D300" s="90" t="n"/>
-      <c r="E300" s="90" t="n"/>
-      <c r="F300" s="90" t="n"/>
-      <c r="G300" s="90" t="n"/>
-      <c r="H300" s="90" t="n"/>
-      <c r="I300" s="90" t="n"/>
-      <c r="J300" s="90" t="n"/>
-      <c r="K300" s="90" t="n"/>
-      <c r="L300" s="90" t="n"/>
-      <c r="M300" s="90" t="n"/>
-      <c r="N300" s="90" t="n"/>
-      <c r="O300" s="91" t="n"/>
     </row>
     <row r="301" ht="18" customHeight="1" s="72">
       <c r="A301" s="92" t="inlineStr">
@@ -16880,37 +17000,37 @@
           <t xml:space="preserve">  ↓  Bu panel için ek içerik slotları (SAĞ):</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr">
+      <c r="B301" s="0" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="C301" t="inlineStr">
+      <c r="C301" s="0" t="inlineStr">
         <is>
           <t>İçerik / URL</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr">
+      <c r="D301" s="0" t="inlineStr">
         <is>
           <t>Genişlik</t>
         </is>
       </c>
-      <c r="E301" t="inlineStr">
+      <c r="E301" s="0" t="inlineStr">
         <is>
           <t>Yükseklik</t>
         </is>
       </c>
-      <c r="F301" t="inlineStr">
+      <c r="F301" s="0" t="inlineStr">
         <is>
           <t>Caption</t>
         </is>
       </c>
-      <c r="G301" t="inlineStr">
+      <c r="G301" s="0" t="inlineStr">
         <is>
           <t>Extra</t>
         </is>
       </c>
-      <c r="I301" t="inlineStr">
+      <c r="I301" s="0" t="inlineStr">
         <is>
           <t>Slot Tipleri: text · html · image · video · youtube · drive · iframe · link · glb   |   Boyut örn: 300px, 100%, auto</t>
         </is>
@@ -17702,14 +17822,34 @@
       </c>
       <c r="B314" s="39" t="inlineStr">
         <is>
-          <t>İçerik / Metin  (düzenlenebilir)</t>
-        </is>
-      </c>
-      <c r="C314" s="39" t="n"/>
-      <c r="D314" s="39" t="n"/>
-      <c r="E314" s="39" t="n"/>
-      <c r="F314" s="39" t="n"/>
-      <c r="G314" s="39" t="n"/>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C314" s="39" t="inlineStr">
+        <is>
+          <t>İçerik / URL</t>
+        </is>
+      </c>
+      <c r="D314" s="39" t="inlineStr">
+        <is>
+          <t>Genişlik</t>
+        </is>
+      </c>
+      <c r="E314" s="39" t="inlineStr">
+        <is>
+          <t>Yükseklik</t>
+        </is>
+      </c>
+      <c r="F314" s="39" t="inlineStr">
+        <is>
+          <t>Caption</t>
+        </is>
+      </c>
+      <c r="G314" s="39" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
       <c r="H314" s="39" t="n"/>
       <c r="I314" s="39" t="n"/>
       <c r="J314" s="39" t="n"/>
@@ -17727,6 +17867,11 @@
       </c>
       <c r="B315" s="95" t="inlineStr">
         <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
           <t>Endüstriyel estetiği ile öne çıkan, geleceğe yönelik tasarım dili.
 Cephe: Çelik Perforeli Panel
 Renk Paleti: Koyu Gri / Paslanmaz
@@ -17734,19 +17879,6 @@
 Bina Yüksekliği: 14 kat</t>
         </is>
       </c>
-      <c r="C315" s="90" t="n"/>
-      <c r="D315" s="90" t="n"/>
-      <c r="E315" s="90" t="n"/>
-      <c r="F315" s="90" t="n"/>
-      <c r="G315" s="90" t="n"/>
-      <c r="H315" s="90" t="n"/>
-      <c r="I315" s="90" t="n"/>
-      <c r="J315" s="90" t="n"/>
-      <c r="K315" s="90" t="n"/>
-      <c r="L315" s="90" t="n"/>
-      <c r="M315" s="90" t="n"/>
-      <c r="N315" s="90" t="n"/>
-      <c r="O315" s="91" t="n"/>
     </row>
     <row r="316" ht="18" customHeight="1" s="72">
       <c r="A316" s="96" t="inlineStr">
@@ -17754,37 +17886,37 @@
           <t xml:space="preserve">  ↓  Bu panel için ek içerik slotları (SOL):</t>
         </is>
       </c>
-      <c r="B316" t="inlineStr">
+      <c r="B316" s="0" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="C316" t="inlineStr">
+      <c r="C316" s="0" t="inlineStr">
         <is>
           <t>İçerik / URL</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr">
+      <c r="D316" s="0" t="inlineStr">
         <is>
           <t>Genişlik</t>
         </is>
       </c>
-      <c r="E316" t="inlineStr">
+      <c r="E316" s="0" t="inlineStr">
         <is>
           <t>Yükseklik</t>
         </is>
       </c>
-      <c r="F316" t="inlineStr">
+      <c r="F316" s="0" t="inlineStr">
         <is>
           <t>Caption</t>
         </is>
       </c>
-      <c r="G316" t="inlineStr">
+      <c r="G316" s="0" t="inlineStr">
         <is>
           <t>Extra</t>
         </is>
       </c>
-      <c r="I316" t="inlineStr">
+      <c r="I316" s="0" t="inlineStr">
         <is>
           <t>Slot Tipleri: text · html · image · video · youtube · drive · iframe · link · glb   |   Boyut örn: 300px, 100%, auto</t>
         </is>
@@ -18576,14 +18708,34 @@
       </c>
       <c r="B329" s="45" t="inlineStr">
         <is>
-          <t>İçerik / Metin  (düzenlenebilir)</t>
-        </is>
-      </c>
-      <c r="C329" s="45" t="n"/>
-      <c r="D329" s="45" t="n"/>
-      <c r="E329" s="45" t="n"/>
-      <c r="F329" s="45" t="n"/>
-      <c r="G329" s="45" t="n"/>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C329" s="45" t="inlineStr">
+        <is>
+          <t>İçerik / URL</t>
+        </is>
+      </c>
+      <c r="D329" s="45" t="inlineStr">
+        <is>
+          <t>Genişlik</t>
+        </is>
+      </c>
+      <c r="E329" s="45" t="inlineStr">
+        <is>
+          <t>Yükseklik</t>
+        </is>
+      </c>
+      <c r="F329" s="45" t="inlineStr">
+        <is>
+          <t>Caption</t>
+        </is>
+      </c>
+      <c r="G329" s="45" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
       <c r="H329" s="45" t="n"/>
       <c r="I329" s="45" t="n"/>
       <c r="J329" s="45" t="n"/>
@@ -18601,25 +18753,17 @@
       </c>
       <c r="B330" s="89" t="inlineStr">
         <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
           <t>✅ Yüksek cam oranı — daha fazla ışık
 ✅ Çarpıcı modern görünüm
 ✅ Uzun ömürlü malzeme
 ✅ Değer artışı potansiyeli</t>
         </is>
       </c>
-      <c r="C330" s="90" t="n"/>
-      <c r="D330" s="90" t="n"/>
-      <c r="E330" s="90" t="n"/>
-      <c r="F330" s="90" t="n"/>
-      <c r="G330" s="90" t="n"/>
-      <c r="H330" s="90" t="n"/>
-      <c r="I330" s="90" t="n"/>
-      <c r="J330" s="90" t="n"/>
-      <c r="K330" s="90" t="n"/>
-      <c r="L330" s="90" t="n"/>
-      <c r="M330" s="90" t="n"/>
-      <c r="N330" s="90" t="n"/>
-      <c r="O330" s="91" t="n"/>
     </row>
     <row r="331" ht="18" customHeight="1" s="72">
       <c r="A331" s="92" t="inlineStr">
@@ -18627,37 +18771,37 @@
           <t xml:space="preserve">  ↓  Bu panel için ek içerik slotları (SAĞ):</t>
         </is>
       </c>
-      <c r="B331" t="inlineStr">
+      <c r="B331" s="0" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="C331" t="inlineStr">
+      <c r="C331" s="0" t="inlineStr">
         <is>
           <t>İçerik / URL</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr">
+      <c r="D331" s="0" t="inlineStr">
         <is>
           <t>Genişlik</t>
         </is>
       </c>
-      <c r="E331" t="inlineStr">
+      <c r="E331" s="0" t="inlineStr">
         <is>
           <t>Yükseklik</t>
         </is>
       </c>
-      <c r="F331" t="inlineStr">
+      <c r="F331" s="0" t="inlineStr">
         <is>
           <t>Caption</t>
         </is>
       </c>
-      <c r="G331" t="inlineStr">
+      <c r="G331" s="0" t="inlineStr">
         <is>
           <t>Extra</t>
         </is>
       </c>
-      <c r="I331" t="inlineStr">
+      <c r="I331" s="0" t="inlineStr">
         <is>
           <t>Slot Tipleri: text · html · image · video · youtube · drive · iframe · link · glb   |   Boyut örn: 300px, 100%, auto</t>
         </is>
@@ -21517,14 +21661,34 @@
       </c>
       <c r="B386" s="39" t="inlineStr">
         <is>
-          <t>İçerik / Metin  (düzenlenebilir)</t>
-        </is>
-      </c>
-      <c r="C386" s="39" t="n"/>
-      <c r="D386" s="39" t="n"/>
-      <c r="E386" s="39" t="n"/>
-      <c r="F386" s="39" t="n"/>
-      <c r="G386" s="39" t="n"/>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C386" s="39" t="inlineStr">
+        <is>
+          <t>İçerik / URL</t>
+        </is>
+      </c>
+      <c r="D386" s="39" t="inlineStr">
+        <is>
+          <t>Genişlik</t>
+        </is>
+      </c>
+      <c r="E386" s="39" t="inlineStr">
+        <is>
+          <t>Yükseklik</t>
+        </is>
+      </c>
+      <c r="F386" s="39" t="inlineStr">
+        <is>
+          <t>Caption</t>
+        </is>
+      </c>
+      <c r="G386" s="39" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
       <c r="H386" s="39" t="n"/>
       <c r="I386" s="39" t="n"/>
       <c r="J386" s="39" t="n"/>
@@ -21542,6 +21706,11 @@
       </c>
       <c r="B387" s="95" t="inlineStr">
         <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
           <t>Projeyi istediğiniz açıdan inceleyin.
 🖱️ Fare ile döndürün
 🖱️ Kaydırarak zoom yapın
@@ -21550,19 +21719,6 @@
 Otopark: 480 araç kapasiteli</t>
         </is>
       </c>
-      <c r="C387" s="90" t="n"/>
-      <c r="D387" s="90" t="n"/>
-      <c r="E387" s="90" t="n"/>
-      <c r="F387" s="90" t="n"/>
-      <c r="G387" s="90" t="n"/>
-      <c r="H387" s="90" t="n"/>
-      <c r="I387" s="90" t="n"/>
-      <c r="J387" s="90" t="n"/>
-      <c r="K387" s="90" t="n"/>
-      <c r="L387" s="90" t="n"/>
-      <c r="M387" s="90" t="n"/>
-      <c r="N387" s="90" t="n"/>
-      <c r="O387" s="91" t="n"/>
     </row>
     <row r="388" ht="18" customHeight="1" s="72">
       <c r="A388" s="96" t="inlineStr">
@@ -21570,37 +21726,37 @@
           <t xml:space="preserve">  ↓  Bu panel için ek içerik slotları (SOL):</t>
         </is>
       </c>
-      <c r="B388" t="inlineStr">
+      <c r="B388" s="0" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="C388" t="inlineStr">
+      <c r="C388" s="0" t="inlineStr">
         <is>
           <t>İçerik / URL</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr">
+      <c r="D388" s="0" t="inlineStr">
         <is>
           <t>Genişlik</t>
         </is>
       </c>
-      <c r="E388" t="inlineStr">
+      <c r="E388" s="0" t="inlineStr">
         <is>
           <t>Yükseklik</t>
         </is>
       </c>
-      <c r="F388" t="inlineStr">
+      <c r="F388" s="0" t="inlineStr">
         <is>
           <t>Caption</t>
         </is>
       </c>
-      <c r="G388" t="inlineStr">
+      <c r="G388" s="0" t="inlineStr">
         <is>
           <t>Extra</t>
         </is>
       </c>
-      <c r="I388" t="inlineStr">
+      <c r="I388" s="0" t="inlineStr">
         <is>
           <t>Slot Tipleri: text · html · image · video · youtube · drive · iframe · link · glb   |   Boyut örn: 300px, 100%, auto</t>
         </is>
@@ -22392,14 +22548,34 @@
       </c>
       <c r="B401" s="45" t="inlineStr">
         <is>
-          <t>İçerik / Metin  (düzenlenebilir)</t>
-        </is>
-      </c>
-      <c r="C401" s="45" t="n"/>
-      <c r="D401" s="45" t="n"/>
-      <c r="E401" s="45" t="n"/>
-      <c r="F401" s="45" t="n"/>
-      <c r="G401" s="45" t="n"/>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C401" s="45" t="inlineStr">
+        <is>
+          <t>İçerik / URL</t>
+        </is>
+      </c>
+      <c r="D401" s="45" t="inlineStr">
+        <is>
+          <t>Genişlik</t>
+        </is>
+      </c>
+      <c r="E401" s="45" t="inlineStr">
+        <is>
+          <t>Yükseklik</t>
+        </is>
+      </c>
+      <c r="F401" s="45" t="inlineStr">
+        <is>
+          <t>Caption</t>
+        </is>
+      </c>
+      <c r="G401" s="45" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
       <c r="H401" s="45" t="n"/>
       <c r="I401" s="45" t="n"/>
       <c r="J401" s="45" t="n"/>
@@ -22417,6 +22593,11 @@
       </c>
       <c r="B402" s="89" t="inlineStr">
         <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
           <t>🏊 Yüzme Havuzu
 🏋️ Fitness Merkezi
 🧖 Spa &amp; Sauna
@@ -22426,19 +22607,6 @@
 📦 Kargo Odası</t>
         </is>
       </c>
-      <c r="C402" s="90" t="n"/>
-      <c r="D402" s="90" t="n"/>
-      <c r="E402" s="90" t="n"/>
-      <c r="F402" s="90" t="n"/>
-      <c r="G402" s="90" t="n"/>
-      <c r="H402" s="90" t="n"/>
-      <c r="I402" s="90" t="n"/>
-      <c r="J402" s="90" t="n"/>
-      <c r="K402" s="90" t="n"/>
-      <c r="L402" s="90" t="n"/>
-      <c r="M402" s="90" t="n"/>
-      <c r="N402" s="90" t="n"/>
-      <c r="O402" s="91" t="n"/>
     </row>
     <row r="403" ht="18" customHeight="1" s="72">
       <c r="A403" s="92" t="inlineStr">
@@ -22446,37 +22614,37 @@
           <t xml:space="preserve">  ↓  Bu panel için ek içerik slotları (SAĞ):</t>
         </is>
       </c>
-      <c r="B403" t="inlineStr">
+      <c r="B403" s="0" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="C403" t="inlineStr">
+      <c r="C403" s="0" t="inlineStr">
         <is>
           <t>İçerik / URL</t>
         </is>
       </c>
-      <c r="D403" t="inlineStr">
+      <c r="D403" s="0" t="inlineStr">
         <is>
           <t>Genişlik</t>
         </is>
       </c>
-      <c r="E403" t="inlineStr">
+      <c r="E403" s="0" t="inlineStr">
         <is>
           <t>Yükseklik</t>
         </is>
       </c>
-      <c r="F403" t="inlineStr">
+      <c r="F403" s="0" t="inlineStr">
         <is>
           <t>Caption</t>
         </is>
       </c>
-      <c r="G403" t="inlineStr">
+      <c r="G403" s="0" t="inlineStr">
         <is>
           <t>Extra</t>
         </is>
       </c>
-      <c r="I403" t="inlineStr">
+      <c r="I403" s="0" t="inlineStr">
         <is>
           <t>Slot Tipleri: text · html · image · video · youtube · drive · iframe · link · glb   |   Boyut örn: 300px, 100%, auto</t>
         </is>
@@ -25374,14 +25542,34 @@
       </c>
       <c r="B462" s="39" t="inlineStr">
         <is>
-          <t>İçerik / Metin  (düzenlenebilir)</t>
-        </is>
-      </c>
-      <c r="C462" s="39" t="n"/>
-      <c r="D462" s="39" t="n"/>
-      <c r="E462" s="39" t="n"/>
-      <c r="F462" s="39" t="n"/>
-      <c r="G462" s="39" t="n"/>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C462" s="39" t="inlineStr">
+        <is>
+          <t>İçerik / URL</t>
+        </is>
+      </c>
+      <c r="D462" s="39" t="inlineStr">
+        <is>
+          <t>Genişlik</t>
+        </is>
+      </c>
+      <c r="E462" s="39" t="inlineStr">
+        <is>
+          <t>Yükseklik</t>
+        </is>
+      </c>
+      <c r="F462" s="39" t="inlineStr">
+        <is>
+          <t>Caption</t>
+        </is>
+      </c>
+      <c r="G462" s="39" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
       <c r="H462" s="39" t="n"/>
       <c r="I462" s="39" t="n"/>
       <c r="J462" s="39" t="n"/>
@@ -25399,6 +25587,11 @@
       </c>
       <c r="B463" s="95" t="inlineStr">
         <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
           <t>Alan: 32 m²
 Zemin: Geniş Format Seramik
 Tavan Yüksekliği: 2.85m
@@ -25406,19 +25599,6 @@
 ☀️ Günün 7 saati doğal ışık</t>
         </is>
       </c>
-      <c r="C463" s="90" t="n"/>
-      <c r="D463" s="90" t="n"/>
-      <c r="E463" s="90" t="n"/>
-      <c r="F463" s="90" t="n"/>
-      <c r="G463" s="90" t="n"/>
-      <c r="H463" s="90" t="n"/>
-      <c r="I463" s="90" t="n"/>
-      <c r="J463" s="90" t="n"/>
-      <c r="K463" s="90" t="n"/>
-      <c r="L463" s="90" t="n"/>
-      <c r="M463" s="90" t="n"/>
-      <c r="N463" s="90" t="n"/>
-      <c r="O463" s="91" t="n"/>
     </row>
     <row r="464" ht="18" customHeight="1" s="72">
       <c r="A464" s="96" t="inlineStr">
@@ -25426,37 +25606,37 @@
           <t xml:space="preserve">  ↓  Bu panel için ek içerik slotları (SOL):</t>
         </is>
       </c>
-      <c r="B464" t="inlineStr">
+      <c r="B464" s="0" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="C464" t="inlineStr">
+      <c r="C464" s="0" t="inlineStr">
         <is>
           <t>İçerik / URL</t>
         </is>
       </c>
-      <c r="D464" t="inlineStr">
+      <c r="D464" s="0" t="inlineStr">
         <is>
           <t>Genişlik</t>
         </is>
       </c>
-      <c r="E464" t="inlineStr">
+      <c r="E464" s="0" t="inlineStr">
         <is>
           <t>Yükseklik</t>
         </is>
       </c>
-      <c r="F464" t="inlineStr">
+      <c r="F464" s="0" t="inlineStr">
         <is>
           <t>Caption</t>
         </is>
       </c>
-      <c r="G464" t="inlineStr">
+      <c r="G464" s="0" t="inlineStr">
         <is>
           <t>Extra</t>
         </is>
       </c>
-      <c r="I464" t="inlineStr">
+      <c r="I464" s="0" t="inlineStr">
         <is>
           <t>Slot Tipleri: text · html · image · video · youtube · drive · iframe · link · glb   |   Boyut örn: 300px, 100%, auto</t>
         </is>
@@ -26248,14 +26428,34 @@
       </c>
       <c r="B477" s="45" t="inlineStr">
         <is>
-          <t>İçerik / Metin  (düzenlenebilir)</t>
-        </is>
-      </c>
-      <c r="C477" s="45" t="n"/>
-      <c r="D477" s="45" t="n"/>
-      <c r="E477" s="45" t="n"/>
-      <c r="F477" s="45" t="n"/>
-      <c r="G477" s="45" t="n"/>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C477" s="45" t="inlineStr">
+        <is>
+          <t>İçerik / URL</t>
+        </is>
+      </c>
+      <c r="D477" s="45" t="inlineStr">
+        <is>
+          <t>Genişlik</t>
+        </is>
+      </c>
+      <c r="E477" s="45" t="inlineStr">
+        <is>
+          <t>Yükseklik</t>
+        </is>
+      </c>
+      <c r="F477" s="45" t="inlineStr">
+        <is>
+          <t>Caption</t>
+        </is>
+      </c>
+      <c r="G477" s="45" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
       <c r="H477" s="45" t="n"/>
       <c r="I477" s="45" t="n"/>
       <c r="J477" s="45" t="n"/>
@@ -26273,6 +26473,11 @@
       </c>
       <c r="B478" s="89" t="inlineStr">
         <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
           <t>🪑 Koltuk: Poliform
 💡 Avize: Tom Dixon
 🖼️ TV Ünitesi: Custom MDF
@@ -26280,19 +26485,6 @@
 * Aksesuarlar örnek gösterim amaçlıdır.</t>
         </is>
       </c>
-      <c r="C478" s="90" t="n"/>
-      <c r="D478" s="90" t="n"/>
-      <c r="E478" s="90" t="n"/>
-      <c r="F478" s="90" t="n"/>
-      <c r="G478" s="90" t="n"/>
-      <c r="H478" s="90" t="n"/>
-      <c r="I478" s="90" t="n"/>
-      <c r="J478" s="90" t="n"/>
-      <c r="K478" s="90" t="n"/>
-      <c r="L478" s="90" t="n"/>
-      <c r="M478" s="90" t="n"/>
-      <c r="N478" s="90" t="n"/>
-      <c r="O478" s="91" t="n"/>
     </row>
     <row r="479" ht="18" customHeight="1" s="72">
       <c r="A479" s="92" t="inlineStr">
@@ -26300,37 +26492,37 @@
           <t xml:space="preserve">  ↓  Bu panel için ek içerik slotları (SAĞ):</t>
         </is>
       </c>
-      <c r="B479" t="inlineStr">
+      <c r="B479" s="0" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="C479" t="inlineStr">
+      <c r="C479" s="0" t="inlineStr">
         <is>
           <t>İçerik / URL</t>
         </is>
       </c>
-      <c r="D479" t="inlineStr">
+      <c r="D479" s="0" t="inlineStr">
         <is>
           <t>Genişlik</t>
         </is>
       </c>
-      <c r="E479" t="inlineStr">
+      <c r="E479" s="0" t="inlineStr">
         <is>
           <t>Yükseklik</t>
         </is>
       </c>
-      <c r="F479" t="inlineStr">
+      <c r="F479" s="0" t="inlineStr">
         <is>
           <t>Caption</t>
         </is>
       </c>
-      <c r="G479" t="inlineStr">
+      <c r="G479" s="0" t="inlineStr">
         <is>
           <t>Extra</t>
         </is>
       </c>
-      <c r="I479" t="inlineStr">
+      <c r="I479" s="0" t="inlineStr">
         <is>
           <t>Slot Tipleri: text · html · image · video · youtube · drive · iframe · link · glb   |   Boyut örn: 300px, 100%, auto</t>
         </is>
@@ -27122,14 +27314,34 @@
       </c>
       <c r="B492" s="39" t="inlineStr">
         <is>
-          <t>İçerik / Metin  (düzenlenebilir)</t>
-        </is>
-      </c>
-      <c r="C492" s="39" t="n"/>
-      <c r="D492" s="39" t="n"/>
-      <c r="E492" s="39" t="n"/>
-      <c r="F492" s="39" t="n"/>
-      <c r="G492" s="39" t="n"/>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C492" s="39" t="inlineStr">
+        <is>
+          <t>İçerik / URL</t>
+        </is>
+      </c>
+      <c r="D492" s="39" t="inlineStr">
+        <is>
+          <t>Genişlik</t>
+        </is>
+      </c>
+      <c r="E492" s="39" t="inlineStr">
+        <is>
+          <t>Yükseklik</t>
+        </is>
+      </c>
+      <c r="F492" s="39" t="inlineStr">
+        <is>
+          <t>Caption</t>
+        </is>
+      </c>
+      <c r="G492" s="39" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
       <c r="H492" s="39" t="n"/>
       <c r="I492" s="39" t="n"/>
       <c r="J492" s="39" t="n"/>
@@ -27147,6 +27359,11 @@
       </c>
       <c r="B493" s="95" t="inlineStr">
         <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
           <t>Alan: 16 m²
 Tezgah: Silestone Quartz
 Dolap: Lake Boyalı MDF
@@ -27154,19 +27371,6 @@
 ✅ Ankastre cihazlar dahil</t>
         </is>
       </c>
-      <c r="C493" s="90" t="n"/>
-      <c r="D493" s="90" t="n"/>
-      <c r="E493" s="90" t="n"/>
-      <c r="F493" s="90" t="n"/>
-      <c r="G493" s="90" t="n"/>
-      <c r="H493" s="90" t="n"/>
-      <c r="I493" s="90" t="n"/>
-      <c r="J493" s="90" t="n"/>
-      <c r="K493" s="90" t="n"/>
-      <c r="L493" s="90" t="n"/>
-      <c r="M493" s="90" t="n"/>
-      <c r="N493" s="90" t="n"/>
-      <c r="O493" s="91" t="n"/>
     </row>
     <row r="494" ht="18" customHeight="1" s="72">
       <c r="A494" s="96" t="inlineStr">
@@ -27174,37 +27378,37 @@
           <t xml:space="preserve">  ↓  Bu panel için ek içerik slotları (SOL):</t>
         </is>
       </c>
-      <c r="B494" t="inlineStr">
+      <c r="B494" s="0" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="C494" t="inlineStr">
+      <c r="C494" s="0" t="inlineStr">
         <is>
           <t>İçerik / URL</t>
         </is>
       </c>
-      <c r="D494" t="inlineStr">
+      <c r="D494" s="0" t="inlineStr">
         <is>
           <t>Genişlik</t>
         </is>
       </c>
-      <c r="E494" t="inlineStr">
+      <c r="E494" s="0" t="inlineStr">
         <is>
           <t>Yükseklik</t>
         </is>
       </c>
-      <c r="F494" t="inlineStr">
+      <c r="F494" s="0" t="inlineStr">
         <is>
           <t>Caption</t>
         </is>
       </c>
-      <c r="G494" t="inlineStr">
+      <c r="G494" s="0" t="inlineStr">
         <is>
           <t>Extra</t>
         </is>
       </c>
-      <c r="I494" t="inlineStr">
+      <c r="I494" s="0" t="inlineStr">
         <is>
           <t>Slot Tipleri: text · html · image · video · youtube · drive · iframe · link · glb   |   Boyut örn: 300px, 100%, auto</t>
         </is>
@@ -27996,14 +28200,34 @@
       </c>
       <c r="B507" s="45" t="inlineStr">
         <is>
-          <t>İçerik / Metin  (düzenlenebilir)</t>
-        </is>
-      </c>
-      <c r="C507" s="45" t="n"/>
-      <c r="D507" s="45" t="n"/>
-      <c r="E507" s="45" t="n"/>
-      <c r="F507" s="45" t="n"/>
-      <c r="G507" s="45" t="n"/>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C507" s="45" t="inlineStr">
+        <is>
+          <t>İçerik / URL</t>
+        </is>
+      </c>
+      <c r="D507" s="45" t="inlineStr">
+        <is>
+          <t>Genişlik</t>
+        </is>
+      </c>
+      <c r="E507" s="45" t="inlineStr">
+        <is>
+          <t>Yükseklik</t>
+        </is>
+      </c>
+      <c r="F507" s="45" t="inlineStr">
+        <is>
+          <t>Caption</t>
+        </is>
+      </c>
+      <c r="G507" s="45" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
       <c r="H507" s="45" t="n"/>
       <c r="I507" s="45" t="n"/>
       <c r="J507" s="45" t="n"/>
@@ -28021,25 +28245,17 @@
       </c>
       <c r="B508" s="89" t="inlineStr">
         <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
           <t>🔧 Davlumbaz: Bosch Series 6
 🔧 Fırın: Siemens iQ700
 🔧 Bulaşık: Miele G7000
 🔧 Buzdolabı: Samsung French Door</t>
         </is>
       </c>
-      <c r="C508" s="90" t="n"/>
-      <c r="D508" s="90" t="n"/>
-      <c r="E508" s="90" t="n"/>
-      <c r="F508" s="90" t="n"/>
-      <c r="G508" s="90" t="n"/>
-      <c r="H508" s="90" t="n"/>
-      <c r="I508" s="90" t="n"/>
-      <c r="J508" s="90" t="n"/>
-      <c r="K508" s="90" t="n"/>
-      <c r="L508" s="90" t="n"/>
-      <c r="M508" s="90" t="n"/>
-      <c r="N508" s="90" t="n"/>
-      <c r="O508" s="91" t="n"/>
     </row>
     <row r="509" ht="18" customHeight="1" s="72">
       <c r="A509" s="92" t="inlineStr">
@@ -28047,37 +28263,37 @@
           <t xml:space="preserve">  ↓  Bu panel için ek içerik slotları (SAĞ):</t>
         </is>
       </c>
-      <c r="B509" t="inlineStr">
+      <c r="B509" s="0" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="C509" t="inlineStr">
+      <c r="C509" s="0" t="inlineStr">
         <is>
           <t>İçerik / URL</t>
         </is>
       </c>
-      <c r="D509" t="inlineStr">
+      <c r="D509" s="0" t="inlineStr">
         <is>
           <t>Genişlik</t>
         </is>
       </c>
-      <c r="E509" t="inlineStr">
+      <c r="E509" s="0" t="inlineStr">
         <is>
           <t>Yükseklik</t>
         </is>
       </c>
-      <c r="F509" t="inlineStr">
+      <c r="F509" s="0" t="inlineStr">
         <is>
           <t>Caption</t>
         </is>
       </c>
-      <c r="G509" t="inlineStr">
+      <c r="G509" s="0" t="inlineStr">
         <is>
           <t>Extra</t>
         </is>
       </c>
-      <c r="I509" t="inlineStr">
+      <c r="I509" s="0" t="inlineStr">
         <is>
           <t>Slot Tipleri: text · html · image · video · youtube · drive · iframe · link · glb   |   Boyut örn: 300px, 100%, auto</t>
         </is>
@@ -28869,14 +29085,34 @@
       </c>
       <c r="B522" s="39" t="inlineStr">
         <is>
-          <t>İçerik / Metin  (düzenlenebilir)</t>
-        </is>
-      </c>
-      <c r="C522" s="39" t="n"/>
-      <c r="D522" s="39" t="n"/>
-      <c r="E522" s="39" t="n"/>
-      <c r="F522" s="39" t="n"/>
-      <c r="G522" s="39" t="n"/>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C522" s="39" t="inlineStr">
+        <is>
+          <t>İçerik / URL</t>
+        </is>
+      </c>
+      <c r="D522" s="39" t="inlineStr">
+        <is>
+          <t>Genişlik</t>
+        </is>
+      </c>
+      <c r="E522" s="39" t="inlineStr">
+        <is>
+          <t>Yükseklik</t>
+        </is>
+      </c>
+      <c r="F522" s="39" t="inlineStr">
+        <is>
+          <t>Caption</t>
+        </is>
+      </c>
+      <c r="G522" s="39" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
       <c r="H522" s="39" t="n"/>
       <c r="I522" s="39" t="n"/>
       <c r="J522" s="39" t="n"/>
@@ -28894,6 +29130,11 @@
       </c>
       <c r="B523" s="95" t="inlineStr">
         <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
           <t>Alan: 18 m²
 Zemin: Meşe Laminat Parke
 Pencere: Doğu Yönü
@@ -28901,19 +29142,6 @@
 🌅 Sabah güneşi</t>
         </is>
       </c>
-      <c r="C523" s="90" t="n"/>
-      <c r="D523" s="90" t="n"/>
-      <c r="E523" s="90" t="n"/>
-      <c r="F523" s="90" t="n"/>
-      <c r="G523" s="90" t="n"/>
-      <c r="H523" s="90" t="n"/>
-      <c r="I523" s="90" t="n"/>
-      <c r="J523" s="90" t="n"/>
-      <c r="K523" s="90" t="n"/>
-      <c r="L523" s="90" t="n"/>
-      <c r="M523" s="90" t="n"/>
-      <c r="N523" s="90" t="n"/>
-      <c r="O523" s="91" t="n"/>
     </row>
     <row r="524" ht="18" customHeight="1" s="72">
       <c r="A524" s="96" t="inlineStr">
@@ -28921,37 +29149,37 @@
           <t xml:space="preserve">  ↓  Bu panel için ek içerik slotları (SOL):</t>
         </is>
       </c>
-      <c r="B524" t="inlineStr">
+      <c r="B524" s="0" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="C524" t="inlineStr">
+      <c r="C524" s="0" t="inlineStr">
         <is>
           <t>İçerik / URL</t>
         </is>
       </c>
-      <c r="D524" t="inlineStr">
+      <c r="D524" s="0" t="inlineStr">
         <is>
           <t>Genişlik</t>
         </is>
       </c>
-      <c r="E524" t="inlineStr">
+      <c r="E524" s="0" t="inlineStr">
         <is>
           <t>Yükseklik</t>
         </is>
       </c>
-      <c r="F524" t="inlineStr">
+      <c r="F524" s="0" t="inlineStr">
         <is>
           <t>Caption</t>
         </is>
       </c>
-      <c r="G524" t="inlineStr">
+      <c r="G524" s="0" t="inlineStr">
         <is>
           <t>Extra</t>
         </is>
       </c>
-      <c r="I524" t="inlineStr">
+      <c r="I524" s="0" t="inlineStr">
         <is>
           <t>Slot Tipleri: text · html · image · video · youtube · drive · iframe · link · glb   |   Boyut örn: 300px, 100%, auto</t>
         </is>
@@ -29743,14 +29971,34 @@
       </c>
       <c r="B537" s="45" t="inlineStr">
         <is>
-          <t>İçerik / Metin  (düzenlenebilir)</t>
-        </is>
-      </c>
-      <c r="C537" s="45" t="n"/>
-      <c r="D537" s="45" t="n"/>
-      <c r="E537" s="45" t="n"/>
-      <c r="F537" s="45" t="n"/>
-      <c r="G537" s="45" t="n"/>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C537" s="45" t="inlineStr">
+        <is>
+          <t>İçerik / URL</t>
+        </is>
+      </c>
+      <c r="D537" s="45" t="inlineStr">
+        <is>
+          <t>Genişlik</t>
+        </is>
+      </c>
+      <c r="E537" s="45" t="inlineStr">
+        <is>
+          <t>Yükseklik</t>
+        </is>
+      </c>
+      <c r="F537" s="45" t="inlineStr">
+        <is>
+          <t>Caption</t>
+        </is>
+      </c>
+      <c r="G537" s="45" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
       <c r="H537" s="45" t="n"/>
       <c r="I537" s="45" t="n"/>
       <c r="J537" s="45" t="n"/>
@@ -29768,25 +30016,17 @@
       </c>
       <c r="B538" s="89" t="inlineStr">
         <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
           <t>🛏️ King Size 180×200
 🪟 Gömme Gardırop 4 kanat
 💡 LED Bant Aydınlatma
 ❄️ Daikin Inverter A++</t>
         </is>
       </c>
-      <c r="C538" s="90" t="n"/>
-      <c r="D538" s="90" t="n"/>
-      <c r="E538" s="90" t="n"/>
-      <c r="F538" s="90" t="n"/>
-      <c r="G538" s="90" t="n"/>
-      <c r="H538" s="90" t="n"/>
-      <c r="I538" s="90" t="n"/>
-      <c r="J538" s="90" t="n"/>
-      <c r="K538" s="90" t="n"/>
-      <c r="L538" s="90" t="n"/>
-      <c r="M538" s="90" t="n"/>
-      <c r="N538" s="90" t="n"/>
-      <c r="O538" s="91" t="n"/>
     </row>
     <row r="539" ht="18" customHeight="1" s="72">
       <c r="A539" s="92" t="inlineStr">
@@ -29794,37 +30034,37 @@
           <t xml:space="preserve">  ↓  Bu panel için ek içerik slotları (SAĞ):</t>
         </is>
       </c>
-      <c r="B539" t="inlineStr">
+      <c r="B539" s="0" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="C539" t="inlineStr">
+      <c r="C539" s="0" t="inlineStr">
         <is>
           <t>İçerik / URL</t>
         </is>
       </c>
-      <c r="D539" t="inlineStr">
+      <c r="D539" s="0" t="inlineStr">
         <is>
           <t>Genişlik</t>
         </is>
       </c>
-      <c r="E539" t="inlineStr">
+      <c r="E539" s="0" t="inlineStr">
         <is>
           <t>Yükseklik</t>
         </is>
       </c>
-      <c r="F539" t="inlineStr">
+      <c r="F539" s="0" t="inlineStr">
         <is>
           <t>Caption</t>
         </is>
       </c>
-      <c r="G539" t="inlineStr">
+      <c r="G539" s="0" t="inlineStr">
         <is>
           <t>Extra</t>
         </is>
       </c>
-      <c r="I539" t="inlineStr">
+      <c r="I539" s="0" t="inlineStr">
         <is>
           <t>Slot Tipleri: text · html · image · video · youtube · drive · iframe · link · glb   |   Boyut örn: 300px, 100%, auto</t>
         </is>
@@ -30616,14 +30856,34 @@
       </c>
       <c r="B552" s="39" t="inlineStr">
         <is>
-          <t>İçerik / Metin  (düzenlenebilir)</t>
-        </is>
-      </c>
-      <c r="C552" s="39" t="n"/>
-      <c r="D552" s="39" t="n"/>
-      <c r="E552" s="39" t="n"/>
-      <c r="F552" s="39" t="n"/>
-      <c r="G552" s="39" t="n"/>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C552" s="39" t="inlineStr">
+        <is>
+          <t>İçerik / URL</t>
+        </is>
+      </c>
+      <c r="D552" s="39" t="inlineStr">
+        <is>
+          <t>Genişlik</t>
+        </is>
+      </c>
+      <c r="E552" s="39" t="inlineStr">
+        <is>
+          <t>Yükseklik</t>
+        </is>
+      </c>
+      <c r="F552" s="39" t="inlineStr">
+        <is>
+          <t>Caption</t>
+        </is>
+      </c>
+      <c r="G552" s="39" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
       <c r="H552" s="39" t="n"/>
       <c r="I552" s="39" t="n"/>
       <c r="J552" s="39" t="n"/>
@@ -30641,6 +30901,11 @@
       </c>
       <c r="B553" s="95" t="inlineStr">
         <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
           <t>Alan: 8 m²
 Zemin: Mermer Görünümlü Seramik
 Duvar: Geniş Format Beyaz Fayans
@@ -30648,19 +30913,6 @@
 ✅ Yerden ısıtma sistemi</t>
         </is>
       </c>
-      <c r="C553" s="90" t="n"/>
-      <c r="D553" s="90" t="n"/>
-      <c r="E553" s="90" t="n"/>
-      <c r="F553" s="90" t="n"/>
-      <c r="G553" s="90" t="n"/>
-      <c r="H553" s="90" t="n"/>
-      <c r="I553" s="90" t="n"/>
-      <c r="J553" s="90" t="n"/>
-      <c r="K553" s="90" t="n"/>
-      <c r="L553" s="90" t="n"/>
-      <c r="M553" s="90" t="n"/>
-      <c r="N553" s="90" t="n"/>
-      <c r="O553" s="91" t="n"/>
     </row>
     <row r="554" ht="18" customHeight="1" s="72">
       <c r="A554" s="96" t="inlineStr">
@@ -30668,37 +30920,37 @@
           <t xml:space="preserve">  ↓  Bu panel için ek içerik slotları (SOL):</t>
         </is>
       </c>
-      <c r="B554" t="inlineStr">
+      <c r="B554" s="0" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="C554" t="inlineStr">
+      <c r="C554" s="0" t="inlineStr">
         <is>
           <t>İçerik / URL</t>
         </is>
       </c>
-      <c r="D554" t="inlineStr">
+      <c r="D554" s="0" t="inlineStr">
         <is>
           <t>Genişlik</t>
         </is>
       </c>
-      <c r="E554" t="inlineStr">
+      <c r="E554" s="0" t="inlineStr">
         <is>
           <t>Yükseklik</t>
         </is>
       </c>
-      <c r="F554" t="inlineStr">
+      <c r="F554" s="0" t="inlineStr">
         <is>
           <t>Caption</t>
         </is>
       </c>
-      <c r="G554" t="inlineStr">
+      <c r="G554" s="0" t="inlineStr">
         <is>
           <t>Extra</t>
         </is>
       </c>
-      <c r="I554" t="inlineStr">
+      <c r="I554" s="0" t="inlineStr">
         <is>
           <t>Slot Tipleri: text · html · image · video · youtube · drive · iframe · link · glb   |   Boyut örn: 300px, 100%, auto</t>
         </is>
@@ -31490,14 +31742,34 @@
       </c>
       <c r="B567" s="45" t="inlineStr">
         <is>
-          <t>İçerik / Metin  (düzenlenebilir)</t>
-        </is>
-      </c>
-      <c r="C567" s="45" t="n"/>
-      <c r="D567" s="45" t="n"/>
-      <c r="E567" s="45" t="n"/>
-      <c r="F567" s="45" t="n"/>
-      <c r="G567" s="45" t="n"/>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C567" s="45" t="inlineStr">
+        <is>
+          <t>İçerik / URL</t>
+        </is>
+      </c>
+      <c r="D567" s="45" t="inlineStr">
+        <is>
+          <t>Genişlik</t>
+        </is>
+      </c>
+      <c r="E567" s="45" t="inlineStr">
+        <is>
+          <t>Yükseklik</t>
+        </is>
+      </c>
+      <c r="F567" s="45" t="inlineStr">
+        <is>
+          <t>Caption</t>
+        </is>
+      </c>
+      <c r="G567" s="45" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
       <c r="H567" s="45" t="n"/>
       <c r="I567" s="45" t="n"/>
       <c r="J567" s="45" t="n"/>
@@ -31515,25 +31787,17 @@
       </c>
       <c r="B568" s="89" t="inlineStr">
         <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
           <t>🚰 Lavabo: Villeroy &amp; Boch
 🪞 Ayna: LED Aydınlatmalı
 🛁 Duşakabin: 90×90 Cam
 🔧 Batarya: Hansgrohe Metris</t>
         </is>
       </c>
-      <c r="C568" s="90" t="n"/>
-      <c r="D568" s="90" t="n"/>
-      <c r="E568" s="90" t="n"/>
-      <c r="F568" s="90" t="n"/>
-      <c r="G568" s="90" t="n"/>
-      <c r="H568" s="90" t="n"/>
-      <c r="I568" s="90" t="n"/>
-      <c r="J568" s="90" t="n"/>
-      <c r="K568" s="90" t="n"/>
-      <c r="L568" s="90" t="n"/>
-      <c r="M568" s="90" t="n"/>
-      <c r="N568" s="90" t="n"/>
-      <c r="O568" s="91" t="n"/>
     </row>
     <row r="569" ht="18" customHeight="1" s="72">
       <c r="A569" s="92" t="inlineStr">
@@ -31541,37 +31805,37 @@
           <t xml:space="preserve">  ↓  Bu panel için ek içerik slotları (SAĞ):</t>
         </is>
       </c>
-      <c r="B569" t="inlineStr">
+      <c r="B569" s="0" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="C569" t="inlineStr">
+      <c r="C569" s="0" t="inlineStr">
         <is>
           <t>İçerik / URL</t>
         </is>
       </c>
-      <c r="D569" t="inlineStr">
+      <c r="D569" s="0" t="inlineStr">
         <is>
           <t>Genişlik</t>
         </is>
       </c>
-      <c r="E569" t="inlineStr">
+      <c r="E569" s="0" t="inlineStr">
         <is>
           <t>Yükseklik</t>
         </is>
       </c>
-      <c r="F569" t="inlineStr">
+      <c r="F569" s="0" t="inlineStr">
         <is>
           <t>Caption</t>
         </is>
       </c>
-      <c r="G569" t="inlineStr">
+      <c r="G569" s="0" t="inlineStr">
         <is>
           <t>Extra</t>
         </is>
       </c>
-      <c r="I569" t="inlineStr">
+      <c r="I569" s="0" t="inlineStr">
         <is>
           <t>Slot Tipleri: text · html · image · video · youtube · drive · iframe · link · glb   |   Boyut örn: 300px, 100%, auto</t>
         </is>
@@ -32363,14 +32627,34 @@
       </c>
       <c r="B582" s="39" t="inlineStr">
         <is>
-          <t>İçerik / Metin  (düzenlenebilir)</t>
-        </is>
-      </c>
-      <c r="C582" s="39" t="n"/>
-      <c r="D582" s="39" t="n"/>
-      <c r="E582" s="39" t="n"/>
-      <c r="F582" s="39" t="n"/>
-      <c r="G582" s="39" t="n"/>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C582" s="39" t="inlineStr">
+        <is>
+          <t>İçerik / URL</t>
+        </is>
+      </c>
+      <c r="D582" s="39" t="inlineStr">
+        <is>
+          <t>Genişlik</t>
+        </is>
+      </c>
+      <c r="E582" s="39" t="inlineStr">
+        <is>
+          <t>Yükseklik</t>
+        </is>
+      </c>
+      <c r="F582" s="39" t="inlineStr">
+        <is>
+          <t>Caption</t>
+        </is>
+      </c>
+      <c r="G582" s="39" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
       <c r="H582" s="39" t="n"/>
       <c r="I582" s="39" t="n"/>
       <c r="J582" s="39" t="n"/>
@@ -32388,24 +32672,16 @@
       </c>
       <c r="B583" s="95" t="inlineStr">
         <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
           <t>Alan: 14 m²
 Zemin: Laminat Parke
 Pencere: Güney Yönü</t>
         </is>
       </c>
-      <c r="C583" s="90" t="n"/>
-      <c r="D583" s="90" t="n"/>
-      <c r="E583" s="90" t="n"/>
-      <c r="F583" s="90" t="n"/>
-      <c r="G583" s="90" t="n"/>
-      <c r="H583" s="90" t="n"/>
-      <c r="I583" s="90" t="n"/>
-      <c r="J583" s="90" t="n"/>
-      <c r="K583" s="90" t="n"/>
-      <c r="L583" s="90" t="n"/>
-      <c r="M583" s="90" t="n"/>
-      <c r="N583" s="90" t="n"/>
-      <c r="O583" s="91" t="n"/>
     </row>
     <row r="584" ht="18" customHeight="1" s="72">
       <c r="A584" s="96" t="inlineStr">
@@ -32413,37 +32689,37 @@
           <t xml:space="preserve">  ↓  Bu panel için ek içerik slotları (SOL):</t>
         </is>
       </c>
-      <c r="B584" t="inlineStr">
+      <c r="B584" s="0" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="C584" t="inlineStr">
+      <c r="C584" s="0" t="inlineStr">
         <is>
           <t>İçerik / URL</t>
         </is>
       </c>
-      <c r="D584" t="inlineStr">
+      <c r="D584" s="0" t="inlineStr">
         <is>
           <t>Genişlik</t>
         </is>
       </c>
-      <c r="E584" t="inlineStr">
+      <c r="E584" s="0" t="inlineStr">
         <is>
           <t>Yükseklik</t>
         </is>
       </c>
-      <c r="F584" t="inlineStr">
+      <c r="F584" s="0" t="inlineStr">
         <is>
           <t>Caption</t>
         </is>
       </c>
-      <c r="G584" t="inlineStr">
+      <c r="G584" s="0" t="inlineStr">
         <is>
           <t>Extra</t>
         </is>
       </c>
-      <c r="I584" t="inlineStr">
+      <c r="I584" s="0" t="inlineStr">
         <is>
           <t>Slot Tipleri: text · html · image · video · youtube · drive · iframe · link · glb   |   Boyut örn: 300px, 100%, auto</t>
         </is>
@@ -33235,14 +33511,34 @@
       </c>
       <c r="B597" s="45" t="inlineStr">
         <is>
-          <t>İçerik / Metin  (düzenlenebilir)</t>
-        </is>
-      </c>
-      <c r="C597" s="45" t="n"/>
-      <c r="D597" s="45" t="n"/>
-      <c r="E597" s="45" t="n"/>
-      <c r="F597" s="45" t="n"/>
-      <c r="G597" s="45" t="n"/>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C597" s="45" t="inlineStr">
+        <is>
+          <t>İçerik / URL</t>
+        </is>
+      </c>
+      <c r="D597" s="45" t="inlineStr">
+        <is>
+          <t>Genişlik</t>
+        </is>
+      </c>
+      <c r="E597" s="45" t="inlineStr">
+        <is>
+          <t>Yükseklik</t>
+        </is>
+      </c>
+      <c r="F597" s="45" t="inlineStr">
+        <is>
+          <t>Caption</t>
+        </is>
+      </c>
+      <c r="G597" s="45" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
       <c r="H597" s="45" t="n"/>
       <c r="I597" s="45" t="n"/>
       <c r="J597" s="45" t="n"/>
@@ -33260,24 +33556,16 @@
       </c>
       <c r="B598" s="89" t="inlineStr">
         <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
           <t>Gömme Gardırop 3 kanat
 Daikin Inverter klima
 8cm XPS Isı Yalıtımı</t>
         </is>
       </c>
-      <c r="C598" s="90" t="n"/>
-      <c r="D598" s="90" t="n"/>
-      <c r="E598" s="90" t="n"/>
-      <c r="F598" s="90" t="n"/>
-      <c r="G598" s="90" t="n"/>
-      <c r="H598" s="90" t="n"/>
-      <c r="I598" s="90" t="n"/>
-      <c r="J598" s="90" t="n"/>
-      <c r="K598" s="90" t="n"/>
-      <c r="L598" s="90" t="n"/>
-      <c r="M598" s="90" t="n"/>
-      <c r="N598" s="90" t="n"/>
-      <c r="O598" s="91" t="n"/>
     </row>
     <row r="599" ht="18" customHeight="1" s="72">
       <c r="A599" s="92" t="inlineStr">
@@ -33285,37 +33573,37 @@
           <t xml:space="preserve">  ↓  Bu panel için ek içerik slotları (SAĞ):</t>
         </is>
       </c>
-      <c r="B599" t="inlineStr">
+      <c r="B599" s="0" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="C599" t="inlineStr">
+      <c r="C599" s="0" t="inlineStr">
         <is>
           <t>İçerik / URL</t>
         </is>
       </c>
-      <c r="D599" t="inlineStr">
+      <c r="D599" s="0" t="inlineStr">
         <is>
           <t>Genişlik</t>
         </is>
       </c>
-      <c r="E599" t="inlineStr">
+      <c r="E599" s="0" t="inlineStr">
         <is>
           <t>Yükseklik</t>
         </is>
       </c>
-      <c r="F599" t="inlineStr">
+      <c r="F599" s="0" t="inlineStr">
         <is>
           <t>Caption</t>
         </is>
       </c>
-      <c r="G599" t="inlineStr">
+      <c r="G599" s="0" t="inlineStr">
         <is>
           <t>Extra</t>
         </is>
       </c>
-      <c r="I599" t="inlineStr">
+      <c r="I599" s="0" t="inlineStr">
         <is>
           <t>Slot Tipleri: text · html · image · video · youtube · drive · iframe · link · glb   |   Boyut örn: 300px, 100%, auto</t>
         </is>
@@ -34107,14 +34395,34 @@
       </c>
       <c r="B612" s="39" t="inlineStr">
         <is>
-          <t>İçerik / Metin  (düzenlenebilir)</t>
-        </is>
-      </c>
-      <c r="C612" s="39" t="n"/>
-      <c r="D612" s="39" t="n"/>
-      <c r="E612" s="39" t="n"/>
-      <c r="F612" s="39" t="n"/>
-      <c r="G612" s="39" t="n"/>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C612" s="39" t="inlineStr">
+        <is>
+          <t>İçerik / URL</t>
+        </is>
+      </c>
+      <c r="D612" s="39" t="inlineStr">
+        <is>
+          <t>Genişlik</t>
+        </is>
+      </c>
+      <c r="E612" s="39" t="inlineStr">
+        <is>
+          <t>Yükseklik</t>
+        </is>
+      </c>
+      <c r="F612" s="39" t="inlineStr">
+        <is>
+          <t>Caption</t>
+        </is>
+      </c>
+      <c r="G612" s="39" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
       <c r="H612" s="39" t="n"/>
       <c r="I612" s="39" t="n"/>
       <c r="J612" s="39" t="n"/>
@@ -34132,25 +34440,17 @@
       </c>
       <c r="B613" s="95" t="inlineStr">
         <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
           <t>Alan: 5 m²
 Zemin: Taş Doku Seramik
 Duvar: Beyaz Fayans
 ✅ Pencereli — doğal havalandırma</t>
         </is>
       </c>
-      <c r="C613" s="90" t="n"/>
-      <c r="D613" s="90" t="n"/>
-      <c r="E613" s="90" t="n"/>
-      <c r="F613" s="90" t="n"/>
-      <c r="G613" s="90" t="n"/>
-      <c r="H613" s="90" t="n"/>
-      <c r="I613" s="90" t="n"/>
-      <c r="J613" s="90" t="n"/>
-      <c r="K613" s="90" t="n"/>
-      <c r="L613" s="90" t="n"/>
-      <c r="M613" s="90" t="n"/>
-      <c r="N613" s="90" t="n"/>
-      <c r="O613" s="91" t="n"/>
     </row>
     <row r="614" ht="18" customHeight="1" s="72">
       <c r="A614" s="96" t="inlineStr">
@@ -34158,37 +34458,37 @@
           <t xml:space="preserve">  ↓  Bu panel için ek içerik slotları (SOL):</t>
         </is>
       </c>
-      <c r="B614" t="inlineStr">
+      <c r="B614" s="0" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="C614" t="inlineStr">
+      <c r="C614" s="0" t="inlineStr">
         <is>
           <t>İçerik / URL</t>
         </is>
       </c>
-      <c r="D614" t="inlineStr">
+      <c r="D614" s="0" t="inlineStr">
         <is>
           <t>Genişlik</t>
         </is>
       </c>
-      <c r="E614" t="inlineStr">
+      <c r="E614" s="0" t="inlineStr">
         <is>
           <t>Yükseklik</t>
         </is>
       </c>
-      <c r="F614" t="inlineStr">
+      <c r="F614" s="0" t="inlineStr">
         <is>
           <t>Caption</t>
         </is>
       </c>
-      <c r="G614" t="inlineStr">
+      <c r="G614" s="0" t="inlineStr">
         <is>
           <t>Extra</t>
         </is>
       </c>
-      <c r="I614" t="inlineStr">
+      <c r="I614" s="0" t="inlineStr">
         <is>
           <t>Slot Tipleri: text · html · image · video · youtube · drive · iframe · link · glb   |   Boyut örn: 300px, 100%, auto</t>
         </is>
@@ -34980,14 +35280,34 @@
       </c>
       <c r="B627" s="45" t="inlineStr">
         <is>
-          <t>İçerik / Metin  (düzenlenebilir)</t>
-        </is>
-      </c>
-      <c r="C627" s="45" t="n"/>
-      <c r="D627" s="45" t="n"/>
-      <c r="E627" s="45" t="n"/>
-      <c r="F627" s="45" t="n"/>
-      <c r="G627" s="45" t="n"/>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C627" s="45" t="inlineStr">
+        <is>
+          <t>İçerik / URL</t>
+        </is>
+      </c>
+      <c r="D627" s="45" t="inlineStr">
+        <is>
+          <t>Genişlik</t>
+        </is>
+      </c>
+      <c r="E627" s="45" t="inlineStr">
+        <is>
+          <t>Yükseklik</t>
+        </is>
+      </c>
+      <c r="F627" s="45" t="inlineStr">
+        <is>
+          <t>Caption</t>
+        </is>
+      </c>
+      <c r="G627" s="45" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
       <c r="H627" s="45" t="n"/>
       <c r="I627" s="45" t="n"/>
       <c r="J627" s="45" t="n"/>
@@ -35005,25 +35325,17 @@
       </c>
       <c r="B628" s="89" t="inlineStr">
         <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
           <t>🚰 Lavabo: Roca Nexo
 🪞 Ayna: Standart
 🚿 Duş: Köşe Duşakabin
 🔧 Batarya: Grohe Eurosmart</t>
         </is>
       </c>
-      <c r="C628" s="90" t="n"/>
-      <c r="D628" s="90" t="n"/>
-      <c r="E628" s="90" t="n"/>
-      <c r="F628" s="90" t="n"/>
-      <c r="G628" s="90" t="n"/>
-      <c r="H628" s="90" t="n"/>
-      <c r="I628" s="90" t="n"/>
-      <c r="J628" s="90" t="n"/>
-      <c r="K628" s="90" t="n"/>
-      <c r="L628" s="90" t="n"/>
-      <c r="M628" s="90" t="n"/>
-      <c r="N628" s="90" t="n"/>
-      <c r="O628" s="91" t="n"/>
     </row>
     <row r="629" ht="18" customHeight="1" s="72">
       <c r="A629" s="92" t="inlineStr">
@@ -35031,37 +35343,37 @@
           <t xml:space="preserve">  ↓  Bu panel için ek içerik slotları (SAĞ):</t>
         </is>
       </c>
-      <c r="B629" t="inlineStr">
+      <c r="B629" s="0" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="C629" t="inlineStr">
+      <c r="C629" s="0" t="inlineStr">
         <is>
           <t>İçerik / URL</t>
         </is>
       </c>
-      <c r="D629" t="inlineStr">
+      <c r="D629" s="0" t="inlineStr">
         <is>
           <t>Genişlik</t>
         </is>
       </c>
-      <c r="E629" t="inlineStr">
+      <c r="E629" s="0" t="inlineStr">
         <is>
           <t>Yükseklik</t>
         </is>
       </c>
-      <c r="F629" t="inlineStr">
+      <c r="F629" s="0" t="inlineStr">
         <is>
           <t>Caption</t>
         </is>
       </c>
-      <c r="G629" t="inlineStr">
+      <c r="G629" s="0" t="inlineStr">
         <is>
           <t>Extra</t>
         </is>
       </c>
-      <c r="I629" t="inlineStr">
+      <c r="I629" s="0" t="inlineStr">
         <is>
           <t>Slot Tipleri: text · html · image · video · youtube · drive · iframe · link · glb   |   Boyut örn: 300px, 100%, auto</t>
         </is>
@@ -37841,14 +38153,34 @@
       </c>
       <c r="B684" s="39" t="inlineStr">
         <is>
-          <t>İçerik / Metin  (düzenlenebilir)</t>
-        </is>
-      </c>
-      <c r="C684" s="39" t="n"/>
-      <c r="D684" s="39" t="n"/>
-      <c r="E684" s="39" t="n"/>
-      <c r="F684" s="39" t="n"/>
-      <c r="G684" s="39" t="n"/>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C684" s="39" t="inlineStr">
+        <is>
+          <t>İçerik / URL</t>
+        </is>
+      </c>
+      <c r="D684" s="39" t="inlineStr">
+        <is>
+          <t>Genişlik</t>
+        </is>
+      </c>
+      <c r="E684" s="39" t="inlineStr">
+        <is>
+          <t>Yükseklik</t>
+        </is>
+      </c>
+      <c r="F684" s="39" t="inlineStr">
+        <is>
+          <t>Caption</t>
+        </is>
+      </c>
+      <c r="G684" s="39" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
       <c r="H684" s="39" t="n"/>
       <c r="I684" s="39" t="n"/>
       <c r="J684" s="39" t="n"/>
@@ -37866,6 +38198,11 @@
       </c>
       <c r="B685" s="95" t="inlineStr">
         <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
           <t>W / A / S / D — Hareket et
 Fare — Kamera yönü
 Shift — Hızlı koş
@@ -37874,19 +38211,6 @@
 📱 Mobil: Joystick ile kontrol</t>
         </is>
       </c>
-      <c r="C685" s="90" t="n"/>
-      <c r="D685" s="90" t="n"/>
-      <c r="E685" s="90" t="n"/>
-      <c r="F685" s="90" t="n"/>
-      <c r="G685" s="90" t="n"/>
-      <c r="H685" s="90" t="n"/>
-      <c r="I685" s="90" t="n"/>
-      <c r="J685" s="90" t="n"/>
-      <c r="K685" s="90" t="n"/>
-      <c r="L685" s="90" t="n"/>
-      <c r="M685" s="90" t="n"/>
-      <c r="N685" s="90" t="n"/>
-      <c r="O685" s="91" t="n"/>
     </row>
     <row r="686" ht="18" customHeight="1" s="72">
       <c r="A686" s="96" t="inlineStr">
@@ -37894,37 +38218,37 @@
           <t xml:space="preserve">  ↓  Bu panel için ek içerik slotları (SOL):</t>
         </is>
       </c>
-      <c r="B686" t="inlineStr">
+      <c r="B686" s="0" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="C686" t="inlineStr">
+      <c r="C686" s="0" t="inlineStr">
         <is>
           <t>İçerik / URL</t>
         </is>
       </c>
-      <c r="D686" t="inlineStr">
+      <c r="D686" s="0" t="inlineStr">
         <is>
           <t>Genişlik</t>
         </is>
       </c>
-      <c r="E686" t="inlineStr">
+      <c r="E686" s="0" t="inlineStr">
         <is>
           <t>Yükseklik</t>
         </is>
       </c>
-      <c r="F686" t="inlineStr">
+      <c r="F686" s="0" t="inlineStr">
         <is>
           <t>Caption</t>
         </is>
       </c>
-      <c r="G686" t="inlineStr">
+      <c r="G686" s="0" t="inlineStr">
         <is>
           <t>Extra</t>
         </is>
       </c>
-      <c r="I686" t="inlineStr">
+      <c r="I686" s="0" t="inlineStr">
         <is>
           <t>Slot Tipleri: text · html · image · video · youtube · drive · iframe · link · glb   |   Boyut örn: 300px, 100%, auto</t>
         </is>
@@ -38716,14 +39040,34 @@
       </c>
       <c r="B699" s="45" t="inlineStr">
         <is>
-          <t>İçerik / Metin  (düzenlenebilir)</t>
-        </is>
-      </c>
-      <c r="C699" s="45" t="n"/>
-      <c r="D699" s="45" t="n"/>
-      <c r="E699" s="45" t="n"/>
-      <c r="F699" s="45" t="n"/>
-      <c r="G699" s="45" t="n"/>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C699" s="45" t="inlineStr">
+        <is>
+          <t>İçerik / URL</t>
+        </is>
+      </c>
+      <c r="D699" s="45" t="inlineStr">
+        <is>
+          <t>Genişlik</t>
+        </is>
+      </c>
+      <c r="E699" s="45" t="inlineStr">
+        <is>
+          <t>Yükseklik</t>
+        </is>
+      </c>
+      <c r="F699" s="45" t="inlineStr">
+        <is>
+          <t>Caption</t>
+        </is>
+      </c>
+      <c r="G699" s="45" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
       <c r="H699" s="45" t="n"/>
       <c r="I699" s="45" t="n"/>
       <c r="J699" s="45" t="n"/>
@@ -38741,6 +39085,11 @@
       </c>
       <c r="B700" s="89" t="inlineStr">
         <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
           <t>Dairenin içinde serbestçe dolaşın.
 Tüm odaları gerçekçi ölçülerinde keşfedin.
 Toplam Alan: 110 m²
@@ -38748,19 +39097,6 @@
 VR kulaklık bağlıysa: Enter VR seçin</t>
         </is>
       </c>
-      <c r="C700" s="90" t="n"/>
-      <c r="D700" s="90" t="n"/>
-      <c r="E700" s="90" t="n"/>
-      <c r="F700" s="90" t="n"/>
-      <c r="G700" s="90" t="n"/>
-      <c r="H700" s="90" t="n"/>
-      <c r="I700" s="90" t="n"/>
-      <c r="J700" s="90" t="n"/>
-      <c r="K700" s="90" t="n"/>
-      <c r="L700" s="90" t="n"/>
-      <c r="M700" s="90" t="n"/>
-      <c r="N700" s="90" t="n"/>
-      <c r="O700" s="91" t="n"/>
     </row>
     <row r="701" ht="18" customHeight="1" s="72">
       <c r="A701" s="92" t="inlineStr">
@@ -38768,37 +39104,37 @@
           <t xml:space="preserve">  ↓  Bu panel için ek içerik slotları (SAĞ):</t>
         </is>
       </c>
-      <c r="B701" t="inlineStr">
+      <c r="B701" s="0" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="C701" t="inlineStr">
+      <c r="C701" s="0" t="inlineStr">
         <is>
           <t>İçerik / URL</t>
         </is>
       </c>
-      <c r="D701" t="inlineStr">
+      <c r="D701" s="0" t="inlineStr">
         <is>
           <t>Genişlik</t>
         </is>
       </c>
-      <c r="E701" t="inlineStr">
+      <c r="E701" s="0" t="inlineStr">
         <is>
           <t>Yükseklik</t>
         </is>
       </c>
-      <c r="F701" t="inlineStr">
+      <c r="F701" s="0" t="inlineStr">
         <is>
           <t>Caption</t>
         </is>
       </c>
-      <c r="G701" t="inlineStr">
+      <c r="G701" s="0" t="inlineStr">
         <is>
           <t>Extra</t>
         </is>
       </c>
-      <c r="I701" t="inlineStr">
+      <c r="I701" s="0" t="inlineStr">
         <is>
           <t>Slot Tipleri: text · html · image · video · youtube · drive · iframe · link · glb   |   Boyut örn: 300px, 100%, auto</t>
         </is>
@@ -39872,15 +40208,11 @@
     <row r="999" ht="15.75" customHeight="1" s="72"/>
     <row r="1000" ht="15.75" customHeight="1" s="72"/>
   </sheetData>
-  <mergeCells count="106">
-    <mergeCell ref="B330:O330"/>
+  <mergeCells count="78">
     <mergeCell ref="A668:O668"/>
     <mergeCell ref="A551:O551"/>
     <mergeCell ref="A354:O354"/>
-    <mergeCell ref="B553:O553"/>
     <mergeCell ref="A652:O652"/>
-    <mergeCell ref="B194:O194"/>
-    <mergeCell ref="B209:O209"/>
     <mergeCell ref="A419:O419"/>
     <mergeCell ref="A717:O717"/>
     <mergeCell ref="A698:O698"/>
@@ -39889,24 +40221,17 @@
     <mergeCell ref="A3:O3"/>
     <mergeCell ref="A596:O596"/>
     <mergeCell ref="A248:O248"/>
-    <mergeCell ref="B523:O523"/>
     <mergeCell ref="A106:O106"/>
-    <mergeCell ref="B538:O538"/>
-    <mergeCell ref="B179:O179"/>
     <mergeCell ref="A372:O372"/>
     <mergeCell ref="A347:O347"/>
     <mergeCell ref="A58:O58"/>
-    <mergeCell ref="B628:O628"/>
     <mergeCell ref="A266:O266"/>
     <mergeCell ref="A536:O536"/>
     <mergeCell ref="A241:O241"/>
-    <mergeCell ref="B89:O89"/>
     <mergeCell ref="A146:O146"/>
     <mergeCell ref="A237:O237"/>
     <mergeCell ref="A7:O7"/>
-    <mergeCell ref="B315:O315"/>
     <mergeCell ref="A448:O448"/>
-    <mergeCell ref="B224:O224"/>
     <mergeCell ref="A626:O626"/>
     <mergeCell ref="A683:O683"/>
     <mergeCell ref="A385:O385"/>
@@ -39914,17 +40239,13 @@
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="A384:O384"/>
     <mergeCell ref="A440:O440"/>
-    <mergeCell ref="B583:O583"/>
     <mergeCell ref="A491:O491"/>
     <mergeCell ref="A72:O72"/>
     <mergeCell ref="A134:O134"/>
     <mergeCell ref="A506:O506"/>
-    <mergeCell ref="B568:O568"/>
     <mergeCell ref="A59:O59"/>
-    <mergeCell ref="B74:O74"/>
     <mergeCell ref="A461:O461"/>
     <mergeCell ref="A476:O476"/>
-    <mergeCell ref="B493:O493"/>
     <mergeCell ref="A162:O162"/>
     <mergeCell ref="A346:O346"/>
     <mergeCell ref="A177:O177"/>
@@ -39932,31 +40253,23 @@
     <mergeCell ref="A283:O283"/>
     <mergeCell ref="A566:O566"/>
     <mergeCell ref="A581:O581"/>
-    <mergeCell ref="B700:O700"/>
     <mergeCell ref="A611:O611"/>
     <mergeCell ref="A129:O129"/>
     <mergeCell ref="A313:O313"/>
-    <mergeCell ref="B508:O508"/>
     <mergeCell ref="A33:O33"/>
-    <mergeCell ref="B387:O387"/>
-    <mergeCell ref="B685:O685"/>
     <mergeCell ref="A240:O240"/>
     <mergeCell ref="A102:O102"/>
     <mergeCell ref="A400:O400"/>
     <mergeCell ref="A34:O34"/>
     <mergeCell ref="A270:O270"/>
     <mergeCell ref="A328:O328"/>
-    <mergeCell ref="B300:O300"/>
-    <mergeCell ref="B478:O478"/>
     <mergeCell ref="A521:O521"/>
     <mergeCell ref="A207:O207"/>
-    <mergeCell ref="B463:O463"/>
     <mergeCell ref="A343:O343"/>
     <mergeCell ref="A370:O370"/>
     <mergeCell ref="A87:O87"/>
     <mergeCell ref="A670:O670"/>
     <mergeCell ref="A282:O282"/>
-    <mergeCell ref="B149:O149"/>
     <mergeCell ref="A105:O105"/>
     <mergeCell ref="A192:O192"/>
     <mergeCell ref="A57:O57"/>
@@ -39965,18 +40278,13 @@
     <mergeCell ref="A713:O713"/>
     <mergeCell ref="A71:O71"/>
     <mergeCell ref="A298:O298"/>
-    <mergeCell ref="B598:O598"/>
-    <mergeCell ref="B402:O402"/>
-    <mergeCell ref="B613:O613"/>
     <mergeCell ref="A641:O641"/>
     <mergeCell ref="A147:O147"/>
     <mergeCell ref="A371:O371"/>
     <mergeCell ref="A460:O460"/>
-    <mergeCell ref="B285:O285"/>
     <mergeCell ref="A682:O682"/>
     <mergeCell ref="A222:O222"/>
     <mergeCell ref="A669:O669"/>
-    <mergeCell ref="B164:O164"/>
     <mergeCell ref="A6:O6"/>
     <mergeCell ref="A644:O644"/>
   </mergeCells>

--- a/demo2-xlsx/demo2-input_3.xlsx
+++ b/demo2-xlsx/demo2-input_3.xlsx
@@ -1051,7 +1051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O717"/>
+  <dimension ref="A2:O717"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="18" customWidth="1" style="72" min="1" max="1"/>
@@ -4748,7 +4748,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="0" t="inlineStr">
         <is>
           <t>Interaktif 3D gayrimenkul deneyimine hoş geldiniz.
 Bu demo, yeni nesil konut projesinin tüm detaylarını immersive bir ortamda sunmaktadır.
@@ -5591,7 +5591,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C89" s="0" t="inlineStr">
         <is>
           <t>Proje: Nova Residence
 Geliştirici: VEA Development
@@ -7605,7 +7605,6 @@
         </is>
       </c>
     </row>
-    <row r="127"/>
     <row r="128" ht="9.75" customHeight="1" s="72"/>
     <row r="129" ht="21.75" customHeight="1" s="72">
       <c r="A129" s="80" t="inlineStr">
@@ -8588,7 +8587,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
+      <c r="C149" s="0" t="inlineStr">
         <is>
           <t>Koordinatlar: 41.0082° K, 28.9784° D
 🚇 Metro A İstasyonu — 350m
@@ -9476,7 +9475,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
+      <c r="C164" s="0" t="inlineStr">
         <is>
           <t>Geliştirici: VEA Development A.Ş.
 4 Blok | 240 Daire | 1+1 / 2+1 / 3+1
@@ -10362,7 +10361,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr">
+      <c r="C179" s="0" t="inlineStr">
         <is>
           <t>🚇 M3 Metro Hattı — 350m
 🚌 Otobüs Durağı — 120m
@@ -11250,7 +11249,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr">
+      <c r="C194" s="0" t="inlineStr">
         <is>
           <t>Walk Score®: 9.2 / 10
 🚶 Yürünebilirlik: Mükemmel
@@ -12135,7 +12134,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr">
+      <c r="C209" s="0" t="inlineStr">
         <is>
           <t>1+1 — 55–65 m² — 68 Daire
 2+1 — 85–100 m² — 120 Daire
@@ -13021,7 +13020,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C224" t="inlineStr">
+      <c r="C224" s="0" t="inlineStr">
         <is>
           <t>1+1 — 2.850.000 ₺'den başlayan
 2+1 — 4.200.000 ₺'den başlayan
@@ -16098,7 +16097,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C285" t="inlineStr">
+      <c r="C285" s="0" t="inlineStr">
         <is>
           <t>Geleneksel mimari dil ile modern detayların buluştuğu tasarım.
 Cephe: Travertin &amp; Alüminyum
@@ -16158,27 +16157,27 @@
       </c>
       <c r="B287" s="19" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>image</t>
         </is>
       </c>
       <c r="C287" s="19" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>https://picsum.photos/seed/veaklasik/480/300</t>
         </is>
       </c>
       <c r="D287" s="19" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E287" s="19" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="F287" s="19" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>Görsel</t>
         </is>
       </c>
       <c r="G287" s="19" t="inlineStr">
@@ -16235,27 +16234,27 @@
       </c>
       <c r="B288" s="19" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="C288" s="19" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>https://www.youtube.com/watch?v=aqz-KE-bpKQ</t>
         </is>
       </c>
       <c r="D288" s="19" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E288" s="19" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>170px</t>
         </is>
       </c>
       <c r="F288" s="19" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="G288" s="19" t="inlineStr">
@@ -16312,12 +16311,12 @@
       </c>
       <c r="B289" s="19" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>link</t>
         </is>
       </c>
       <c r="C289" s="19" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>https://example.com/klasik-cephe-brosur.pdf</t>
         </is>
       </c>
       <c r="D289" s="19" t="inlineStr">
@@ -16332,7 +16331,7 @@
       </c>
       <c r="F289" s="19" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>Broşür (PDF)</t>
         </is>
       </c>
       <c r="G289" s="19" t="inlineStr">
@@ -16389,12 +16388,12 @@
       </c>
       <c r="B290" s="19" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C290" s="19" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>**Ek Detay:** Klasik cephede kullanılan travertin Denizli Kocabaş ocağından doğal çıkarılmaktadır. Kendi kendini temizleyen yüzey kaplaması 25 yıl garanti.</t>
         </is>
       </c>
       <c r="D290" s="19" t="inlineStr">
@@ -16409,7 +16408,7 @@
       </c>
       <c r="F290" s="19" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>Detay</t>
         </is>
       </c>
       <c r="G290" s="19" t="inlineStr">
@@ -16984,7 +16983,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C300" t="inlineStr">
+      <c r="C300" s="0" t="inlineStr">
         <is>
           <t>✅ Düşük bakım maliyeti
 ✅ Zamansız estetik
@@ -17870,7 +17869,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C315" t="inlineStr">
+      <c r="C315" s="0" t="inlineStr">
         <is>
           <t>Endüstriyel estetiği ile öne çıkan, geleceğe yönelik tasarım dili.
 Cephe: Çelik Perforeli Panel
@@ -18756,7 +18755,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C330" t="inlineStr">
+      <c r="C330" s="0" t="inlineStr">
         <is>
           <t>✅ Yüksek cam oranı — daha fazla ışık
 ✅ Çarpıcı modern görünüm
@@ -21709,7 +21708,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C387" t="inlineStr">
+      <c r="C387" s="0" t="inlineStr">
         <is>
           <t>Projeyi istediğiniz açıdan inceleyin.
 🖱️ Fare ile döndürün
@@ -22596,7 +22595,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C402" t="inlineStr">
+      <c r="C402" s="0" t="inlineStr">
         <is>
           <t>🏊 Yüzme Havuzu
 🏋️ Fitness Merkezi
@@ -25590,7 +25589,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C463" t="inlineStr">
+      <c r="C463" s="0" t="inlineStr">
         <is>
           <t>Alan: 32 m²
 Zemin: Geniş Format Seramik
@@ -26476,7 +26475,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C478" t="inlineStr">
+      <c r="C478" s="0" t="inlineStr">
         <is>
           <t>🪑 Koltuk: Poliform
 💡 Avize: Tom Dixon
@@ -27362,7 +27361,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C493" t="inlineStr">
+      <c r="C493" s="0" t="inlineStr">
         <is>
           <t>Alan: 16 m²
 Tezgah: Silestone Quartz
@@ -28248,7 +28247,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C508" t="inlineStr">
+      <c r="C508" s="0" t="inlineStr">
         <is>
           <t>🔧 Davlumbaz: Bosch Series 6
 🔧 Fırın: Siemens iQ700
@@ -29133,7 +29132,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C523" t="inlineStr">
+      <c r="C523" s="0" t="inlineStr">
         <is>
           <t>Alan: 18 m²
 Zemin: Meşe Laminat Parke
@@ -30019,7 +30018,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C538" t="inlineStr">
+      <c r="C538" s="0" t="inlineStr">
         <is>
           <t>🛏️ King Size 180×200
 🪟 Gömme Gardırop 4 kanat
@@ -30904,7 +30903,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C553" t="inlineStr">
+      <c r="C553" s="0" t="inlineStr">
         <is>
           <t>Alan: 8 m²
 Zemin: Mermer Görünümlü Seramik
@@ -31790,7 +31789,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C568" t="inlineStr">
+      <c r="C568" s="0" t="inlineStr">
         <is>
           <t>🚰 Lavabo: Villeroy &amp; Boch
 🪞 Ayna: LED Aydınlatmalı
@@ -32675,7 +32674,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C583" t="inlineStr">
+      <c r="C583" s="0" t="inlineStr">
         <is>
           <t>Alan: 14 m²
 Zemin: Laminat Parke
@@ -33559,7 +33558,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C598" t="inlineStr">
+      <c r="C598" s="0" t="inlineStr">
         <is>
           <t>Gömme Gardırop 3 kanat
 Daikin Inverter klima
@@ -34443,7 +34442,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C613" t="inlineStr">
+      <c r="C613" s="0" t="inlineStr">
         <is>
           <t>Alan: 5 m²
 Zemin: Taş Doku Seramik
@@ -35328,7 +35327,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C628" t="inlineStr">
+      <c r="C628" s="0" t="inlineStr">
         <is>
           <t>🚰 Lavabo: Roca Nexo
 🪞 Ayna: Standart
@@ -38201,7 +38200,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C685" t="inlineStr">
+      <c r="C685" s="0" t="inlineStr">
         <is>
           <t>W / A / S / D — Hareket et
 Fare — Kamera yönü
@@ -39088,7 +39087,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C700" t="inlineStr">
+      <c r="C700" s="0" t="inlineStr">
         <is>
           <t>Dairenin içinde serbestçe dolaşın.
 Tüm odaları gerçekçi ölçülerinde keşfedin.
@@ -40270,8 +40269,8 @@
     <mergeCell ref="A87:O87"/>
     <mergeCell ref="A670:O670"/>
     <mergeCell ref="A282:O282"/>
+    <mergeCell ref="A192:O192"/>
     <mergeCell ref="A105:O105"/>
-    <mergeCell ref="A192:O192"/>
     <mergeCell ref="A57:O57"/>
     <mergeCell ref="A113:O113"/>
     <mergeCell ref="A415:O415"/>

--- a/demo2-xlsx/demo2-input_3.xlsx
+++ b/demo2-xlsx/demo2-input_3.xlsx
@@ -1051,7 +1051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:O717"/>
+  <dimension ref="A1:O717"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="18" customWidth="1" style="72" min="1" max="1"/>
@@ -2932,13 +2932,15 @@
       <c r="A43" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="B43" s="9">
-        <f>B9</f>
-        <v/>
-      </c>
-      <c r="C43" s="29">
-        <f>C9</f>
-        <v/>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>City Model v2</t>
+        </is>
+      </c>
+      <c r="C43" s="29" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/decentralize-dfw/vea-randomfiles/main/DEMO2city-opt-v2.glb</t>
+        </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
@@ -2987,13 +2989,15 @@
       <c r="A44" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="B44" s="14">
-        <f>B13</f>
-        <v/>
-      </c>
-      <c r="C44" s="31">
-        <f>C13</f>
-        <v/>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>Kopuk Normal Facade v5</t>
+        </is>
+      </c>
+      <c r="C44" s="31" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/decentralize-dfw/vea-randomfiles/main/DEMO2kopuk-normalfacade-opt-v5.glb</t>
+        </is>
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
@@ -6732,9 +6736,10 @@
           <t>City Model v2 (S0'dan devralınır)</t>
         </is>
       </c>
-      <c r="C115" s="53">
-        <f>C9</f>
-        <v/>
+      <c r="C115" s="53" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/decentralize-dfw/vea-randomfiles/main/DEMO2city-opt-v2.glb</t>
+        </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
@@ -6788,9 +6793,10 @@
           <t>Kopuk Normal Facade v5 (S0'dan devralınır)</t>
         </is>
       </c>
-      <c r="C116" s="54">
-        <f>C13</f>
-        <v/>
+      <c r="C116" s="54" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/decentralize-dfw/vea-randomfiles/main/DEMO2kopuk-normalfacade-opt-v5.glb</t>
+        </is>
       </c>
       <c r="D116" s="16" t="inlineStr">
         <is>
@@ -7605,6 +7611,7 @@
         </is>
       </c>
     </row>
+    <row r="127"/>
     <row r="128" ht="9.75" customHeight="1" s="72"/>
     <row r="129" ht="21.75" customHeight="1" s="72">
       <c r="A129" s="80" t="inlineStr">
@@ -14160,9 +14167,10 @@
           <t>City Model v2</t>
         </is>
       </c>
-      <c r="C250" s="63">
-        <f>C9</f>
-        <v/>
+      <c r="C250" s="63" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/decentralize-dfw/vea-randomfiles/main/DEMO2city-opt-v2.glb</t>
+        </is>
       </c>
       <c r="D250" s="11" t="inlineStr">
         <is>
@@ -14216,9 +14224,10 @@
           <t>City White Facade v3</t>
         </is>
       </c>
-      <c r="C251" s="53">
-        <f>C12</f>
-        <v/>
+      <c r="C251" s="53" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/decentralize-dfw/vea-randomfiles/main/DEMO2city-whitefacade-v3.glb</t>
+        </is>
       </c>
       <c r="D251" s="11" t="inlineStr">
         <is>
@@ -14272,9 +14281,10 @@
           <t>City Metal v1</t>
         </is>
       </c>
-      <c r="C252" s="53">
-        <f>C11</f>
-        <v/>
+      <c r="C252" s="53" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/decentralize-dfw/vea-randomfiles/main/DEMO2city-metal-v1.glb</t>
+        </is>
       </c>
       <c r="D252" s="11" t="inlineStr">
         <is>
@@ -14328,9 +14338,10 @@
           <t>Kopuk Normal Facade v5</t>
         </is>
       </c>
-      <c r="C253" s="54">
-        <f>C13</f>
-        <v/>
+      <c r="C253" s="54" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/decentralize-dfw/vea-randomfiles/main/DEMO2kopuk-normalfacade-opt-v5.glb</t>
+        </is>
       </c>
       <c r="D253" s="16" t="inlineStr">
         <is>
@@ -19895,9 +19906,10 @@
           <t>City Metal v1</t>
         </is>
       </c>
-      <c r="C356" s="53">
-        <f>C11</f>
-        <v/>
+      <c r="C356" s="53" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/decentralize-dfw/vea-randomfiles/main/DEMO2city-metal-v1.glb</t>
+        </is>
       </c>
       <c r="D356" s="11" t="inlineStr">
         <is>
@@ -19951,9 +19963,10 @@
           <t>Sehiriçi Apartman v6</t>
         </is>
       </c>
-      <c r="C357" s="54">
-        <f>C14</f>
-        <v/>
+      <c r="C357" s="54" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/decentralize-dfw/vea-randomfiles/main/DEMO2-sehirici-apartmanici-opt-v6.glb</t>
+        </is>
       </c>
       <c r="D357" s="16" t="inlineStr">
         <is>
@@ -23696,9 +23709,10 @@
           <t>Interior Apartment v4</t>
         </is>
       </c>
-      <c r="C427" s="54">
-        <f>C15</f>
-        <v/>
+      <c r="C427" s="54" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/decentralize-dfw/vea-randomfiles/main/DEMO2interior-soloapartement-opt-v4.glb</t>
+        </is>
       </c>
       <c r="D427" s="16" t="inlineStr">
         <is>
@@ -36463,9 +36477,10 @@
           <t>Interior Apartment v4</t>
         </is>
       </c>
-      <c r="C654" s="53">
-        <f>C15</f>
-        <v/>
+      <c r="C654" s="53" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/decentralize-dfw/vea-randomfiles/main/DEMO2interior-soloapartement-opt-v4.glb</t>
+        </is>
       </c>
       <c r="D654" s="11" t="inlineStr">
         <is>
@@ -36519,9 +36534,10 @@
           <t>Scene 5 Collider</t>
         </is>
       </c>
-      <c r="C655" s="54">
-        <f>C16</f>
-        <v/>
+      <c r="C655" s="54" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/decentralize-dfw/vea-randomfiles/main/SCENE5-COLLDERd.glb</t>
+        </is>
       </c>
       <c r="D655" s="16" t="inlineStr">
         <is>

--- a/demo2-xlsx/demo2-input_3.xlsx
+++ b/demo2-xlsx/demo2-input_3.xlsx
@@ -1051,7 +1051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O717"/>
+  <dimension ref="A2:O717"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="18" customWidth="1" style="72" min="1" max="1"/>
@@ -7611,7 +7611,6 @@
         </is>
       </c>
     </row>
-    <row r="127"/>
     <row r="128" ht="9.75" customHeight="1" s="72"/>
     <row r="129" ht="21.75" customHeight="1" s="72">
       <c r="A129" s="80" t="inlineStr">
@@ -7641,7 +7640,11 @@
           <t>Aksiyon / Açıklama</t>
         </is>
       </c>
-      <c r="E130" s="55" t="n"/>
+      <c r="E130" s="55" t="inlineStr">
+        <is>
+          <t>Kod</t>
+        </is>
+      </c>
       <c r="F130" s="55" t="n"/>
       <c r="G130" s="55" t="n"/>
       <c r="H130" s="55" t="n"/>
@@ -7672,7 +7675,11 @@
           <t>Lokasyon &amp; Çevre panellerini göster → opt1 sol+sağ</t>
         </is>
       </c>
-      <c r="E131" s="57" t="n"/>
+      <c r="E131" s="57" t="inlineStr">
+        <is>
+          <t>toggle-1</t>
+        </is>
+      </c>
       <c r="F131" s="57" t="n"/>
       <c r="G131" s="57" t="n"/>
       <c r="H131" s="57" t="n"/>
@@ -7703,7 +7710,11 @@
           <t>Ulaşım panellerini göster → opt2 sol+sağ</t>
         </is>
       </c>
-      <c r="E132" s="57" t="n"/>
+      <c r="E132" s="57" t="inlineStr">
+        <is>
+          <t>toggle-2</t>
+        </is>
+      </c>
       <c r="F132" s="57" t="n"/>
       <c r="G132" s="57" t="n"/>
       <c r="H132" s="57" t="n"/>
@@ -7734,7 +7745,11 @@
           <t>Ünite Tipleri &amp; Fiyat panellerini göster → opt3 sol+sağ</t>
         </is>
       </c>
-      <c r="E133" s="57" t="n"/>
+      <c r="E133" s="57" t="inlineStr">
+        <is>
+          <t>toggle-3</t>
+        </is>
+      </c>
       <c r="F133" s="57" t="n"/>
       <c r="G133" s="57" t="n"/>
       <c r="H133" s="57" t="n"/>
@@ -8534,47 +8549,76 @@
     <row r="147" ht="15.75" customHeight="1" s="72">
       <c r="A147" s="84" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ◀  SOL PANEL  ·  Panel ID: html_scene1_opt1_left</t>
+          <t>Başlık</t>
+        </is>
+      </c>
+      <c r="B147" s="0" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="C147" s="0" t="inlineStr">
+        <is>
+          <t>İçerik / URL</t>
+        </is>
+      </c>
+      <c r="D147" s="0" t="inlineStr">
+        <is>
+          <t>Genişlik</t>
+        </is>
+      </c>
+      <c r="E147" s="0" t="inlineStr">
+        <is>
+          <t>Yükseklik</t>
+        </is>
+      </c>
+      <c r="F147" s="0" t="inlineStr">
+        <is>
+          <t>Caption</t>
+        </is>
+      </c>
+      <c r="G147" s="0" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
+      <c r="H147" s="0" t="inlineStr">
+        <is>
+          <t>Kod</t>
         </is>
       </c>
     </row>
     <row r="148" ht="15" customHeight="1" s="72">
       <c r="A148" s="39" t="inlineStr">
         <is>
-          <t>Başlık</t>
+          <t>📍 Konum &amp; Çevre</t>
         </is>
       </c>
       <c r="B148" s="39" t="inlineStr">
         <is>
-          <t>Tip</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C148" s="39" t="inlineStr">
         <is>
-          <t>İçerik / URL</t>
-        </is>
-      </c>
-      <c r="D148" s="39" t="inlineStr">
-        <is>
-          <t>Genişlik</t>
-        </is>
-      </c>
-      <c r="E148" s="39" t="inlineStr">
-        <is>
-          <t>Yükseklik</t>
-        </is>
-      </c>
-      <c r="F148" s="39" t="inlineStr">
-        <is>
-          <t>Caption</t>
-        </is>
-      </c>
-      <c r="G148" s="39" t="inlineStr">
-        <is>
-          <t>Extra</t>
-        </is>
-      </c>
-      <c r="H148" s="39" t="n"/>
+          <t>Koordinatlar: 41.0082° K, 28.9784° D
+🚇 Metro A İstasyonu — 350m
+🚇 Metro B İstasyonu — 800m
+🏫 İlköğretim Okulu — 450m
+🏥 Devlet Hastanesi — 1.2 km
+🛒 Alışveriş Merkezi — 600m
+🌳 Kent Parkı — 200m</t>
+        </is>
+      </c>
+      <c r="D148" s="39" t="inlineStr"/>
+      <c r="E148" s="39" t="inlineStr"/>
+      <c r="F148" s="39" t="inlineStr"/>
+      <c r="G148" s="39" t="inlineStr"/>
+      <c r="H148" s="39" t="inlineStr">
+        <is>
+          <t>toggle-1-left</t>
+        </is>
+      </c>
       <c r="I148" s="39" t="n"/>
       <c r="J148" s="39" t="n"/>
       <c r="K148" s="39" t="n"/>
@@ -8586,7 +8630,7 @@
     <row r="149" ht="90.75" customHeight="1" s="72">
       <c r="A149" s="58" t="inlineStr">
         <is>
-          <t>📍 Konum &amp; Çevre  [Buton: Surrounding]</t>
+          <t>Nova Residence</t>
         </is>
       </c>
       <c r="B149" s="95" t="inlineStr">
@@ -8596,50 +8640,52 @@
       </c>
       <c r="C149" s="0" t="inlineStr">
         <is>
-          <t>Koordinatlar: 41.0082° K, 28.9784° D
-🚇 Metro A İstasyonu — 350m
-🚇 Metro B İstasyonu — 800m
-🏫 İlköğretim Okulu — 450m
-🏥 Devlet Hastanesi — 1.2 km
-🛒 Alışveriş Merkezi — 600m
-🌳 Kent Parkı — 200m</t>
+          <t>Geliştirici: VEA Development A.Ş.
+4 Blok | 240 Daire | 1+1 / 2+1 / 3+1
+Teslim: Aralık 2026
+🏅 LEED Gold Sertifikası
+🌱 Enerji Sınıfı: A+</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" s="0" t="inlineStr">
+        <is>
+          <t>toggle-1-right</t>
         </is>
       </c>
     </row>
     <row r="150" ht="18" customHeight="1" s="72">
       <c r="A150" s="96" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↓  Bu panel için ek içerik slotları (SOL):</t>
+          <t>🚌 Ulaşım Ağı</t>
         </is>
       </c>
       <c r="B150" s="0" t="inlineStr">
         <is>
-          <t>Tip</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C150" s="0" t="inlineStr">
         <is>
-          <t>İçerik / URL</t>
-        </is>
-      </c>
-      <c r="D150" s="0" t="inlineStr">
-        <is>
-          <t>Genişlik</t>
-        </is>
-      </c>
-      <c r="E150" s="0" t="inlineStr">
-        <is>
-          <t>Yükseklik</t>
-        </is>
-      </c>
-      <c r="F150" s="0" t="inlineStr">
-        <is>
-          <t>Caption</t>
-        </is>
-      </c>
-      <c r="G150" s="0" t="inlineStr">
-        <is>
-          <t>Extra</t>
+          <t>🚇 M3 Metro Hattı — 350m
+🚌 Otobüs Durağı — 120m
+🚖 Taksi Durağı — 80m
+🛵 Bisiklet Yolu — Proje önünden
+Havalimanı: 28 dk (E80)
+Boğaz Köprüsü: 12 dk
+TEM Bağlantısı: 5 dk</t>
+        </is>
+      </c>
+      <c r="D150" s="0" t="inlineStr"/>
+      <c r="E150" s="0" t="inlineStr"/>
+      <c r="F150" s="0" t="inlineStr"/>
+      <c r="G150" s="0" t="inlineStr"/>
+      <c r="H150" s="0" t="inlineStr">
+        <is>
+          <t>toggle-2-left</t>
         </is>
       </c>
       <c r="I150" s="0" t="inlineStr">
@@ -8651,42 +8697,29 @@
     <row r="151" ht="15" customHeight="1" s="72">
       <c r="A151" s="33" t="inlineStr">
         <is>
-          <t>slot01</t>
+          <t>Bağlantı Puanı</t>
         </is>
       </c>
       <c r="B151" s="19" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C151" s="19" t="inlineStr">
         <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D151" s="19" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E151" s="19" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F151" s="19" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G151" s="19" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>Walk Score®: 9.2 / 10
+🚶 Yürünebilirlik: Mükemmel
+🚲 Bisiklet Dostu: İyi
+🚇 Toplu Ulaşım: Çok İyi</t>
+        </is>
+      </c>
+      <c r="D151" s="19" t="inlineStr"/>
+      <c r="E151" s="19" t="inlineStr"/>
+      <c r="F151" s="19" t="inlineStr"/>
+      <c r="G151" s="19" t="inlineStr"/>
       <c r="H151" s="19" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>toggle-2-right</t>
         </is>
       </c>
       <c r="I151" s="19" t="inlineStr">
@@ -8728,42 +8761,30 @@
     <row r="152" ht="15" customHeight="1" s="72">
       <c r="A152" s="33" t="inlineStr">
         <is>
-          <t>slot02</t>
+          <t>🏠 Ünite Tipleri</t>
         </is>
       </c>
       <c r="B152" s="19" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C152" s="19" t="inlineStr">
         <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D152" s="19" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E152" s="19" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F152" s="19" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G152" s="19" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>1+1 — 55–65 m² — 68 Daire
+2+1 — 85–100 m² — 120 Daire
+3+1 — 130–155 m² — 52 Daire
+✅ Tüm üniteler güney-doğu cepheli
+✅ Panoramik balkon her dairede</t>
+        </is>
+      </c>
+      <c r="D152" s="19" t="inlineStr"/>
+      <c r="E152" s="19" t="inlineStr"/>
+      <c r="F152" s="19" t="inlineStr"/>
+      <c r="G152" s="19" t="inlineStr"/>
       <c r="H152" s="19" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>toggle-3-left</t>
         </is>
       </c>
       <c r="I152" s="19" t="inlineStr">
@@ -8805,42 +8826,29 @@
     <row r="153" ht="15" customHeight="1" s="72">
       <c r="A153" s="33" t="inlineStr">
         <is>
-          <t>slot03</t>
+          <t>Fiyat Aralıkları</t>
         </is>
       </c>
       <c r="B153" s="19" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C153" s="19" t="inlineStr">
         <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D153" s="19" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E153" s="19" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F153" s="19" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G153" s="19" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>1+1 — 2.850.000 ₺'den başlayan
+2+1 — 4.200.000 ₺'den başlayan
+3+1 — 6.500.000 ₺'den başlayan
+* Fiyatlar piyasa koşullarına göre değişkenlik gösterebilir.</t>
+        </is>
+      </c>
+      <c r="D153" s="19" t="inlineStr"/>
+      <c r="E153" s="19" t="inlineStr"/>
+      <c r="F153" s="19" t="inlineStr"/>
+      <c r="G153" s="19" t="inlineStr"/>
       <c r="H153" s="19" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>toggle-3-right</t>
         </is>
       </c>
       <c r="I153" s="19" t="inlineStr">
@@ -8882,7 +8890,7 @@
     <row r="154" ht="15" customHeight="1" s="72">
       <c r="A154" s="33" t="inlineStr">
         <is>
-          <t>slot04</t>
+          <t>slot01</t>
         </is>
       </c>
       <c r="B154" s="19" t="inlineStr">
@@ -8959,7 +8967,7 @@
     <row r="155" ht="15" customHeight="1" s="72">
       <c r="A155" s="33" t="inlineStr">
         <is>
-          <t>slot05</t>
+          <t>slot02</t>
         </is>
       </c>
       <c r="B155" s="19" t="inlineStr">
@@ -9036,7 +9044,7 @@
     <row r="156" ht="15" customHeight="1" s="72">
       <c r="A156" s="33" t="inlineStr">
         <is>
-          <t>slot06</t>
+          <t>slot03</t>
         </is>
       </c>
       <c r="B156" s="19" t="inlineStr">
@@ -9113,7 +9121,7 @@
     <row r="157" ht="15" customHeight="1" s="72">
       <c r="A157" s="33" t="inlineStr">
         <is>
-          <t>slot07</t>
+          <t>slot04</t>
         </is>
       </c>
       <c r="B157" s="19" t="inlineStr">
@@ -9190,7 +9198,7 @@
     <row r="158" ht="15" customHeight="1" s="72">
       <c r="A158" s="33" t="inlineStr">
         <is>
-          <t>slot08</t>
+          <t>slot05</t>
         </is>
       </c>
       <c r="B158" s="19" t="inlineStr">
@@ -9267,7 +9275,7 @@
     <row r="159" ht="15" customHeight="1" s="72">
       <c r="A159" s="33" t="inlineStr">
         <is>
-          <t>slot09</t>
+          <t>slot06</t>
         </is>
       </c>
       <c r="B159" s="19" t="inlineStr">
@@ -9344,7 +9352,7 @@
     <row r="160" ht="15" customHeight="1" s="72">
       <c r="A160" s="33" t="inlineStr">
         <is>
-          <t>slot10</t>
+          <t>slot07</t>
         </is>
       </c>
       <c r="B160" s="19" t="inlineStr">
@@ -9418,51 +9426,131 @@
         </is>
       </c>
     </row>
-    <row r="161" ht="9.75" customHeight="1" s="72"/>
+    <row r="161" ht="9.75" customHeight="1" s="72">
+      <c r="A161" s="0" t="inlineStr">
+        <is>
+          <t>slot08</t>
+        </is>
+      </c>
+      <c r="B161" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C161" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D161" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E161" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F161" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G161" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H161" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
     <row r="162" ht="15.75" customHeight="1" s="72">
       <c r="A162" s="88" t="inlineStr">
         <is>
-          <t xml:space="preserve">  SAĞ PANEL  ▶  ·  Panel ID: html_scene1_opt1_right</t>
+          <t>slot09</t>
+        </is>
+      </c>
+      <c r="B162" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C162" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D162" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E162" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F162" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G162" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H162" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
         </is>
       </c>
     </row>
     <row r="163" ht="15" customHeight="1" s="72">
       <c r="A163" s="45" t="inlineStr">
         <is>
-          <t>Başlık</t>
+          <t>slot10</t>
         </is>
       </c>
       <c r="B163" s="45" t="inlineStr">
         <is>
-          <t>Tip</t>
+          <t>null</t>
         </is>
       </c>
       <c r="C163" s="45" t="inlineStr">
         <is>
-          <t>İçerik / URL</t>
+          <t>null</t>
         </is>
       </c>
       <c r="D163" s="45" t="inlineStr">
         <is>
-          <t>Genişlik</t>
+          <t>null</t>
         </is>
       </c>
       <c r="E163" s="45" t="inlineStr">
         <is>
-          <t>Yükseklik</t>
+          <t>null</t>
         </is>
       </c>
       <c r="F163" s="45" t="inlineStr">
         <is>
-          <t>Caption</t>
+          <t>null</t>
         </is>
       </c>
       <c r="G163" s="45" t="inlineStr">
         <is>
-          <t>Extra</t>
-        </is>
-      </c>
-      <c r="H163" s="45" t="n"/>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H163" s="45" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
       <c r="I163" s="45" t="n"/>
       <c r="J163" s="45" t="n"/>
       <c r="K163" s="45" t="n"/>
@@ -9474,58 +9562,84 @@
     <row r="164" ht="64.5" customHeight="1" s="72">
       <c r="A164" s="46" t="inlineStr">
         <is>
-          <t>Nova Residence  [Buton: Surrounding]</t>
+          <t>slot11</t>
         </is>
       </c>
       <c r="B164" s="89" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>null</t>
         </is>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
-          <t>Geliştirici: VEA Development A.Ş.
-4 Blok | 240 Daire | 1+1 / 2+1 / 3+1
-Teslim: Aralık 2026
-🏅 LEED Gold Sertifikası
-🌱 Enerji Sınıfı: A+</t>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D164" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E164" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F164" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G164" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H164" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
         </is>
       </c>
     </row>
     <row r="165" ht="18" customHeight="1" s="72">
       <c r="A165" s="92" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↓  Bu panel için ek içerik slotları (SAĞ):</t>
+          <t>slot12</t>
         </is>
       </c>
       <c r="B165" s="0" t="inlineStr">
         <is>
-          <t>Tip</t>
+          <t>null</t>
         </is>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
-          <t>İçerik / URL</t>
+          <t>null</t>
         </is>
       </c>
       <c r="D165" s="0" t="inlineStr">
         <is>
-          <t>Genişlik</t>
+          <t>null</t>
         </is>
       </c>
       <c r="E165" s="0" t="inlineStr">
         <is>
-          <t>Yükseklik</t>
+          <t>null</t>
         </is>
       </c>
       <c r="F165" s="0" t="inlineStr">
         <is>
-          <t>Caption</t>
+          <t>null</t>
         </is>
       </c>
       <c r="G165" s="0" t="inlineStr">
         <is>
-          <t>Extra</t>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H165" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
         </is>
       </c>
       <c r="I165" s="0" t="inlineStr">
@@ -9537,7 +9651,7 @@
     <row r="166" ht="15" customHeight="1" s="72">
       <c r="A166" s="33" t="inlineStr">
         <is>
-          <t>slot01</t>
+          <t>slot13</t>
         </is>
       </c>
       <c r="B166" s="19" t="inlineStr">
@@ -9614,7 +9728,7 @@
     <row r="167" ht="15" customHeight="1" s="72">
       <c r="A167" s="33" t="inlineStr">
         <is>
-          <t>slot02</t>
+          <t>slot14</t>
         </is>
       </c>
       <c r="B167" s="19" t="inlineStr">
@@ -9691,7 +9805,7 @@
     <row r="168" ht="15" customHeight="1" s="72">
       <c r="A168" s="33" t="inlineStr">
         <is>
-          <t>slot03</t>
+          <t>slot15</t>
         </is>
       </c>
       <c r="B168" s="19" t="inlineStr">
@@ -9768,7 +9882,7 @@
     <row r="169" ht="15" customHeight="1" s="72">
       <c r="A169" s="33" t="inlineStr">
         <is>
-          <t>slot04</t>
+          <t>slot16</t>
         </is>
       </c>
       <c r="B169" s="19" t="inlineStr">
@@ -9845,7 +9959,7 @@
     <row r="170" ht="15" customHeight="1" s="72">
       <c r="A170" s="33" t="inlineStr">
         <is>
-          <t>slot05</t>
+          <t>slot17</t>
         </is>
       </c>
       <c r="B170" s="19" t="inlineStr">
@@ -9922,7 +10036,7 @@
     <row r="171" ht="15" customHeight="1" s="72">
       <c r="A171" s="33" t="inlineStr">
         <is>
-          <t>slot06</t>
+          <t>slot18</t>
         </is>
       </c>
       <c r="B171" s="19" t="inlineStr">
@@ -9999,7 +10113,7 @@
     <row r="172" ht="15" customHeight="1" s="72">
       <c r="A172" s="33" t="inlineStr">
         <is>
-          <t>slot07</t>
+          <t>slot19</t>
         </is>
       </c>
       <c r="B172" s="19" t="inlineStr">
@@ -10076,7 +10190,7 @@
     <row r="173" ht="15" customHeight="1" s="72">
       <c r="A173" s="33" t="inlineStr">
         <is>
-          <t>slot08</t>
+          <t>slot20</t>
         </is>
       </c>
       <c r="B173" s="19" t="inlineStr">
@@ -10153,7 +10267,7 @@
     <row r="174" ht="15" customHeight="1" s="72">
       <c r="A174" s="33" t="inlineStr">
         <is>
-          <t>slot09</t>
+          <t>slot21</t>
         </is>
       </c>
       <c r="B174" s="19" t="inlineStr">
@@ -10230,7 +10344,7 @@
     <row r="175" ht="15" customHeight="1" s="72">
       <c r="A175" s="33" t="inlineStr">
         <is>
-          <t>slot10</t>
+          <t>slot22</t>
         </is>
       </c>
       <c r="B175" s="19" t="inlineStr">
@@ -40223,85 +40337,78 @@
     <row r="999" ht="15.75" customHeight="1" s="72"/>
     <row r="1000" ht="15.75" customHeight="1" s="72"/>
   </sheetData>
-  <mergeCells count="78">
+  <mergeCells count="71">
     <mergeCell ref="A668:O668"/>
+    <mergeCell ref="A87:O87"/>
+    <mergeCell ref="A7:O7"/>
     <mergeCell ref="A551:O551"/>
     <mergeCell ref="A354:O354"/>
+    <mergeCell ref="A448:O448"/>
     <mergeCell ref="A652:O652"/>
+    <mergeCell ref="A41:O41"/>
     <mergeCell ref="A419:O419"/>
+    <mergeCell ref="A283:O283"/>
+    <mergeCell ref="A566:O566"/>
     <mergeCell ref="A717:O717"/>
+    <mergeCell ref="A581:O581"/>
+    <mergeCell ref="A670:O670"/>
+    <mergeCell ref="A626:O626"/>
+    <mergeCell ref="A282:O282"/>
     <mergeCell ref="A698:O698"/>
     <mergeCell ref="A418:O418"/>
     <mergeCell ref="A645:O645"/>
     <mergeCell ref="A3:O3"/>
-    <mergeCell ref="A596:O596"/>
-    <mergeCell ref="A248:O248"/>
-    <mergeCell ref="A106:O106"/>
-    <mergeCell ref="A372:O372"/>
-    <mergeCell ref="A347:O347"/>
-    <mergeCell ref="A58:O58"/>
-    <mergeCell ref="A266:O266"/>
-    <mergeCell ref="A536:O536"/>
-    <mergeCell ref="A241:O241"/>
-    <mergeCell ref="A146:O146"/>
-    <mergeCell ref="A237:O237"/>
-    <mergeCell ref="A7:O7"/>
-    <mergeCell ref="A448:O448"/>
-    <mergeCell ref="A626:O626"/>
     <mergeCell ref="A683:O683"/>
     <mergeCell ref="A385:O385"/>
+    <mergeCell ref="A596:O596"/>
     <mergeCell ref="A425:O425"/>
-    <mergeCell ref="A2:O2"/>
-    <mergeCell ref="A384:O384"/>
-    <mergeCell ref="A440:O440"/>
-    <mergeCell ref="A491:O491"/>
-    <mergeCell ref="A72:O72"/>
-    <mergeCell ref="A134:O134"/>
-    <mergeCell ref="A506:O506"/>
-    <mergeCell ref="A59:O59"/>
-    <mergeCell ref="A461:O461"/>
-    <mergeCell ref="A476:O476"/>
-    <mergeCell ref="A162:O162"/>
-    <mergeCell ref="A346:O346"/>
-    <mergeCell ref="A177:O177"/>
-    <mergeCell ref="A41:O41"/>
-    <mergeCell ref="A283:O283"/>
-    <mergeCell ref="A566:O566"/>
-    <mergeCell ref="A581:O581"/>
     <mergeCell ref="A611:O611"/>
-    <mergeCell ref="A129:O129"/>
-    <mergeCell ref="A313:O313"/>
-    <mergeCell ref="A33:O33"/>
-    <mergeCell ref="A240:O240"/>
-    <mergeCell ref="A102:O102"/>
-    <mergeCell ref="A400:O400"/>
-    <mergeCell ref="A34:O34"/>
-    <mergeCell ref="A270:O270"/>
-    <mergeCell ref="A328:O328"/>
-    <mergeCell ref="A521:O521"/>
-    <mergeCell ref="A207:O207"/>
-    <mergeCell ref="A343:O343"/>
-    <mergeCell ref="A370:O370"/>
-    <mergeCell ref="A87:O87"/>
-    <mergeCell ref="A670:O670"/>
-    <mergeCell ref="A282:O282"/>
-    <mergeCell ref="A192:O192"/>
     <mergeCell ref="A105:O105"/>
     <mergeCell ref="A57:O57"/>
     <mergeCell ref="A113:O113"/>
+    <mergeCell ref="A248:O248"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A129:O129"/>
+    <mergeCell ref="A313:O313"/>
+    <mergeCell ref="A384:O384"/>
+    <mergeCell ref="A440:O440"/>
     <mergeCell ref="A415:O415"/>
+    <mergeCell ref="A33:O33"/>
     <mergeCell ref="A713:O713"/>
     <mergeCell ref="A71:O71"/>
     <mergeCell ref="A298:O298"/>
     <mergeCell ref="A641:O641"/>
-    <mergeCell ref="A147:O147"/>
+    <mergeCell ref="A106:O106"/>
+    <mergeCell ref="A491:O491"/>
+    <mergeCell ref="A240:O240"/>
     <mergeCell ref="A371:O371"/>
     <mergeCell ref="A460:O460"/>
+    <mergeCell ref="A72:O72"/>
+    <mergeCell ref="A134:O134"/>
+    <mergeCell ref="A372:O372"/>
+    <mergeCell ref="A102:O102"/>
+    <mergeCell ref="A506:O506"/>
+    <mergeCell ref="A400:O400"/>
+    <mergeCell ref="A347:O347"/>
+    <mergeCell ref="A58:O58"/>
+    <mergeCell ref="A34:O34"/>
+    <mergeCell ref="A270:O270"/>
+    <mergeCell ref="A328:O328"/>
+    <mergeCell ref="A59:O59"/>
+    <mergeCell ref="A521:O521"/>
+    <mergeCell ref="A266:O266"/>
     <mergeCell ref="A682:O682"/>
-    <mergeCell ref="A222:O222"/>
+    <mergeCell ref="A536:O536"/>
     <mergeCell ref="A669:O669"/>
+    <mergeCell ref="A241:O241"/>
+    <mergeCell ref="A461:O461"/>
+    <mergeCell ref="A476:O476"/>
+    <mergeCell ref="A343:O343"/>
     <mergeCell ref="A6:O6"/>
+    <mergeCell ref="A370:O370"/>
     <mergeCell ref="A644:O644"/>
+    <mergeCell ref="A237:O237"/>
+    <mergeCell ref="A346:O346"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId1"/>

--- a/demo2-xlsx/demo2-input_3.xlsx
+++ b/demo2-xlsx/demo2-input_3.xlsx
@@ -1051,7 +1051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O717"/>
+  <dimension ref="A2:O717"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="18" customWidth="1" style="72" min="1" max="1"/>
@@ -3906,20 +3906,20 @@
     </row>
     <row r="59" ht="18" customHeight="1" s="72">
       <c r="A59" s="82" t="inlineStr"/>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
+      <c r="B59" s="0" t="inlineStr"/>
+      <c r="C59" s="0" t="inlineStr"/>
+      <c r="D59" s="0" t="inlineStr"/>
+      <c r="E59" s="0" t="inlineStr"/>
+      <c r="F59" s="0" t="inlineStr"/>
+      <c r="G59" s="0" t="inlineStr"/>
+      <c r="H59" s="0" t="inlineStr"/>
+      <c r="I59" s="0" t="inlineStr"/>
+      <c r="J59" s="0" t="inlineStr"/>
+      <c r="K59" s="0" t="inlineStr"/>
+      <c r="L59" s="0" t="inlineStr"/>
+      <c r="M59" s="0" t="inlineStr"/>
+      <c r="N59" s="0" t="inlineStr"/>
+      <c r="O59" s="0" t="inlineStr"/>
     </row>
     <row r="60" ht="15" customHeight="1" s="72">
       <c r="A60" s="33" t="inlineStr">
@@ -4705,48 +4705,48 @@
           <t>Başlık</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="0" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="0" t="inlineStr">
         <is>
           <t>İçerik / URL</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D72" s="0" t="inlineStr">
         <is>
           <t>Genişlik</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E72" s="0" t="inlineStr">
         <is>
           <t>Yükseklik</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F72" s="0" t="inlineStr">
         <is>
           <t>Caption</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G72" s="0" t="inlineStr">
         <is>
           <t>Extra</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="H72" s="0" t="inlineStr">
         <is>
           <t>Kod</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
+      <c r="I72" s="0" t="inlineStr"/>
+      <c r="J72" s="0" t="inlineStr"/>
+      <c r="K72" s="0" t="inlineStr"/>
+      <c r="L72" s="0" t="inlineStr"/>
+      <c r="M72" s="0" t="inlineStr"/>
+      <c r="N72" s="0" t="inlineStr"/>
+      <c r="O72" s="0" t="inlineStr"/>
     </row>
     <row r="73" ht="15" customHeight="1" s="72">
       <c r="A73" s="39" t="inlineStr">
@@ -4803,22 +4803,22 @@
 Toplam Ünite: 240</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr">
+      <c r="D74" s="0" t="inlineStr"/>
+      <c r="E74" s="0" t="inlineStr"/>
+      <c r="F74" s="0" t="inlineStr"/>
+      <c r="G74" s="0" t="inlineStr"/>
+      <c r="H74" s="0" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
+      <c r="I74" s="0" t="inlineStr"/>
+      <c r="J74" s="0" t="inlineStr"/>
+      <c r="K74" s="0" t="inlineStr"/>
+      <c r="L74" s="0" t="inlineStr"/>
+      <c r="M74" s="0" t="inlineStr"/>
+      <c r="N74" s="0" t="inlineStr"/>
+      <c r="O74" s="0" t="inlineStr"/>
     </row>
     <row r="75" ht="18" customHeight="1" s="72">
       <c r="A75" s="32" t="inlineStr">
@@ -5311,102 +5311,102 @@
       <c r="O84" s="19" t="inlineStr"/>
     </row>
     <row r="85" ht="15" customHeight="1" s="72">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="0" t="inlineStr">
         <is>
           <t>slot11</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
+      <c r="B85" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C85" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D85" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E85" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F85" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G85" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H85" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I85" s="0" t="inlineStr"/>
+      <c r="J85" s="0" t="inlineStr"/>
+      <c r="K85" s="0" t="inlineStr"/>
+      <c r="L85" s="0" t="inlineStr"/>
+      <c r="M85" s="0" t="inlineStr"/>
+      <c r="N85" s="0" t="inlineStr"/>
+      <c r="O85" s="0" t="inlineStr"/>
     </row>
     <row r="86" ht="9.75" customHeight="1" s="72">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="0" t="inlineStr">
         <is>
           <t>slot12</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
+      <c r="B86" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C86" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D86" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E86" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F86" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G86" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H86" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I86" s="0" t="inlineStr"/>
+      <c r="J86" s="0" t="inlineStr"/>
+      <c r="K86" s="0" t="inlineStr"/>
+      <c r="L86" s="0" t="inlineStr"/>
+      <c r="M86" s="0" t="inlineStr"/>
+      <c r="N86" s="0" t="inlineStr"/>
+      <c r="O86" s="0" t="inlineStr"/>
     </row>
     <row r="87" ht="15.75" customHeight="1" s="72">
       <c r="A87" s="88" t="inlineStr">
@@ -5414,48 +5414,48 @@
           <t>slot13</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
+      <c r="B87" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C87" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D87" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E87" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F87" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G87" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H87" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I87" s="0" t="inlineStr"/>
+      <c r="J87" s="0" t="inlineStr"/>
+      <c r="K87" s="0" t="inlineStr"/>
+      <c r="L87" s="0" t="inlineStr"/>
+      <c r="M87" s="0" t="inlineStr"/>
+      <c r="N87" s="0" t="inlineStr"/>
+      <c r="O87" s="0" t="inlineStr"/>
     </row>
     <row r="88" ht="15" customHeight="1" s="72">
       <c r="A88" s="45" t="inlineStr">
@@ -5522,38 +5522,38 @@
           <t>null</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
+      <c r="D89" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E89" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F89" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G89" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H89" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I89" s="0" t="inlineStr"/>
+      <c r="J89" s="0" t="inlineStr"/>
+      <c r="K89" s="0" t="inlineStr"/>
+      <c r="L89" s="0" t="inlineStr"/>
+      <c r="M89" s="0" t="inlineStr"/>
+      <c r="N89" s="0" t="inlineStr"/>
+      <c r="O89" s="0" t="inlineStr"/>
     </row>
     <row r="90" ht="18" customHeight="1" s="72">
       <c r="A90" s="92" t="inlineStr">
@@ -5591,18 +5591,18 @@
           <t>null</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="H90" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
       <c r="I90" s="0" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
+      <c r="J90" s="0" t="inlineStr"/>
+      <c r="K90" s="0" t="inlineStr"/>
+      <c r="L90" s="0" t="inlineStr"/>
+      <c r="M90" s="0" t="inlineStr"/>
+      <c r="N90" s="0" t="inlineStr"/>
+      <c r="O90" s="0" t="inlineStr"/>
     </row>
     <row r="91" ht="15" customHeight="1" s="72">
       <c r="A91" s="33" t="inlineStr">
@@ -6095,53 +6095,53 @@
       <c r="O100" s="19" t="inlineStr"/>
     </row>
     <row r="101" ht="9.75" customHeight="1" s="72">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="0" t="inlineStr">
         <is>
           <t>slot27</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
+      <c r="B101" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C101" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D101" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E101" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F101" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G101" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H101" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I101" s="0" t="inlineStr"/>
+      <c r="J101" s="0" t="inlineStr"/>
+      <c r="K101" s="0" t="inlineStr"/>
+      <c r="L101" s="0" t="inlineStr"/>
+      <c r="M101" s="0" t="inlineStr"/>
+      <c r="N101" s="0" t="inlineStr"/>
+      <c r="O101" s="0" t="inlineStr"/>
     </row>
     <row r="102" ht="3.75" customHeight="1" s="72">
       <c r="A102" s="93" t="inlineStr">
@@ -6149,146 +6149,146 @@
           <t>slot28</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
+      <c r="B102" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C102" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D102" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E102" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F102" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G102" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H102" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I102" s="0" t="inlineStr"/>
+      <c r="J102" s="0" t="inlineStr"/>
+      <c r="K102" s="0" t="inlineStr"/>
+      <c r="L102" s="0" t="inlineStr"/>
+      <c r="M102" s="0" t="inlineStr"/>
+      <c r="N102" s="0" t="inlineStr"/>
+      <c r="O102" s="0" t="inlineStr"/>
     </row>
     <row r="103" ht="9.75" customHeight="1" s="72">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="0" t="inlineStr">
         <is>
           <t>slot29</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
+      <c r="B103" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C103" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D103" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E103" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F103" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G103" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H103" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I103" s="0" t="inlineStr"/>
+      <c r="J103" s="0" t="inlineStr"/>
+      <c r="K103" s="0" t="inlineStr"/>
+      <c r="L103" s="0" t="inlineStr"/>
+      <c r="M103" s="0" t="inlineStr"/>
+      <c r="N103" s="0" t="inlineStr"/>
+      <c r="O103" s="0" t="inlineStr"/>
     </row>
     <row r="104" ht="9.75" customHeight="1" s="72">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="0" t="inlineStr">
         <is>
           <t>slot30</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
+      <c r="B104" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C104" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D104" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E104" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F104" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G104" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H104" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I104" s="0" t="inlineStr"/>
+      <c r="J104" s="0" t="inlineStr"/>
+      <c r="K104" s="0" t="inlineStr"/>
+      <c r="L104" s="0" t="inlineStr"/>
+      <c r="M104" s="0" t="inlineStr"/>
+      <c r="N104" s="0" t="inlineStr"/>
+      <c r="O104" s="0" t="inlineStr"/>
     </row>
     <row r="105" ht="27.75" customHeight="1" s="72">
       <c r="A105" s="94" t="inlineStr">
@@ -7478,7 +7478,6 @@
         </is>
       </c>
     </row>
-    <row r="127"/>
     <row r="128" ht="9.75" customHeight="1" s="72"/>
     <row r="129" ht="21.75" customHeight="1" s="72">
       <c r="A129" s="80" t="inlineStr">
@@ -7631,20 +7630,20 @@
     </row>
     <row r="134" ht="18" customHeight="1" s="72">
       <c r="A134" s="82" t="inlineStr"/>
-      <c r="B134" t="inlineStr"/>
-      <c r="C134" t="inlineStr"/>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr"/>
+      <c r="B134" s="0" t="inlineStr"/>
+      <c r="C134" s="0" t="inlineStr"/>
+      <c r="D134" s="0" t="inlineStr"/>
+      <c r="E134" s="0" t="inlineStr"/>
+      <c r="F134" s="0" t="inlineStr"/>
+      <c r="G134" s="0" t="inlineStr"/>
+      <c r="H134" s="0" t="inlineStr"/>
+      <c r="I134" s="0" t="inlineStr"/>
+      <c r="J134" s="0" t="inlineStr"/>
+      <c r="K134" s="0" t="inlineStr"/>
+      <c r="L134" s="0" t="inlineStr"/>
+      <c r="M134" s="0" t="inlineStr"/>
+      <c r="N134" s="0" t="inlineStr"/>
+      <c r="O134" s="0" t="inlineStr"/>
     </row>
     <row r="135" ht="15" customHeight="1" s="72">
       <c r="A135" s="33" t="inlineStr">
@@ -10297,42 +10296,42 @@
       </c>
     </row>
     <row r="176" ht="9.75" customHeight="1" s="72">
-      <c r="A176" t="inlineStr">
+      <c r="A176" s="0" t="inlineStr">
         <is>
           <t>slot23</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
+      <c r="B176" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C176" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D176" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E176" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F176" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G176" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H176" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
@@ -10344,37 +10343,37 @@
           <t>slot24</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
+      <c r="B177" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C177" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D177" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E177" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F177" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G177" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H177" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
@@ -10445,27 +10444,27 @@
           <t>null</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
+      <c r="D179" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E179" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F179" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G179" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H179" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
@@ -10507,18 +10506,18 @@
           <t>null</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
+      <c r="H180" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
       <c r="I180" s="0" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr"/>
-      <c r="N180" t="inlineStr"/>
-      <c r="O180" t="inlineStr"/>
+      <c r="J180" s="0" t="inlineStr"/>
+      <c r="K180" s="0" t="inlineStr"/>
+      <c r="L180" s="0" t="inlineStr"/>
+      <c r="M180" s="0" t="inlineStr"/>
+      <c r="N180" s="0" t="inlineStr"/>
+      <c r="O180" s="0" t="inlineStr"/>
     </row>
     <row r="181" ht="15" customHeight="1" s="72">
       <c r="A181" s="33" t="inlineStr">
@@ -10871,38 +10870,38 @@
       <c r="O190" s="19" t="inlineStr"/>
     </row>
     <row r="191" ht="9.75" customHeight="1" s="72">
-      <c r="A191" t="inlineStr"/>
-      <c r="B191" t="inlineStr"/>
-      <c r="C191" t="inlineStr"/>
-      <c r="D191" t="inlineStr"/>
-      <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr"/>
-      <c r="H191" t="inlineStr"/>
-      <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr"/>
-      <c r="M191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
-      <c r="O191" t="inlineStr"/>
+      <c r="A191" s="0" t="inlineStr"/>
+      <c r="B191" s="0" t="inlineStr"/>
+      <c r="C191" s="0" t="inlineStr"/>
+      <c r="D191" s="0" t="inlineStr"/>
+      <c r="E191" s="0" t="inlineStr"/>
+      <c r="F191" s="0" t="inlineStr"/>
+      <c r="G191" s="0" t="inlineStr"/>
+      <c r="H191" s="0" t="inlineStr"/>
+      <c r="I191" s="0" t="inlineStr"/>
+      <c r="J191" s="0" t="inlineStr"/>
+      <c r="K191" s="0" t="inlineStr"/>
+      <c r="L191" s="0" t="inlineStr"/>
+      <c r="M191" s="0" t="inlineStr"/>
+      <c r="N191" s="0" t="inlineStr"/>
+      <c r="O191" s="0" t="inlineStr"/>
     </row>
     <row r="192" ht="15.75" customHeight="1" s="72">
       <c r="A192" s="88" t="inlineStr"/>
-      <c r="B192" t="inlineStr"/>
-      <c r="C192" t="inlineStr"/>
-      <c r="D192" t="inlineStr"/>
-      <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr"/>
-      <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr"/>
-      <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
-      <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
-      <c r="O192" t="inlineStr"/>
+      <c r="B192" s="0" t="inlineStr"/>
+      <c r="C192" s="0" t="inlineStr"/>
+      <c r="D192" s="0" t="inlineStr"/>
+      <c r="E192" s="0" t="inlineStr"/>
+      <c r="F192" s="0" t="inlineStr"/>
+      <c r="G192" s="0" t="inlineStr"/>
+      <c r="H192" s="0" t="inlineStr"/>
+      <c r="I192" s="0" t="inlineStr"/>
+      <c r="J192" s="0" t="inlineStr"/>
+      <c r="K192" s="0" t="inlineStr"/>
+      <c r="L192" s="0" t="inlineStr"/>
+      <c r="M192" s="0" t="inlineStr"/>
+      <c r="N192" s="0" t="inlineStr"/>
+      <c r="O192" s="0" t="inlineStr"/>
     </row>
     <row r="193" ht="15" customHeight="1" s="72">
       <c r="A193" s="45" t="inlineStr"/>
@@ -10925,18 +10924,18 @@
       <c r="A194" s="46" t="inlineStr"/>
       <c r="B194" s="89" t="inlineStr"/>
       <c r="C194" s="0" t="inlineStr"/>
-      <c r="D194" t="inlineStr"/>
-      <c r="E194" t="inlineStr"/>
-      <c r="F194" t="inlineStr"/>
-      <c r="G194" t="inlineStr"/>
-      <c r="H194" t="inlineStr"/>
-      <c r="I194" t="inlineStr"/>
-      <c r="J194" t="inlineStr"/>
-      <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr"/>
-      <c r="M194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
-      <c r="O194" t="inlineStr"/>
+      <c r="D194" s="0" t="inlineStr"/>
+      <c r="E194" s="0" t="inlineStr"/>
+      <c r="F194" s="0" t="inlineStr"/>
+      <c r="G194" s="0" t="inlineStr"/>
+      <c r="H194" s="0" t="inlineStr"/>
+      <c r="I194" s="0" t="inlineStr"/>
+      <c r="J194" s="0" t="inlineStr"/>
+      <c r="K194" s="0" t="inlineStr"/>
+      <c r="L194" s="0" t="inlineStr"/>
+      <c r="M194" s="0" t="inlineStr"/>
+      <c r="N194" s="0" t="inlineStr"/>
+      <c r="O194" s="0" t="inlineStr"/>
     </row>
     <row r="195" ht="18" customHeight="1" s="72">
       <c r="A195" s="92" t="inlineStr"/>
@@ -10946,14 +10945,14 @@
       <c r="E195" s="0" t="inlineStr"/>
       <c r="F195" s="0" t="inlineStr"/>
       <c r="G195" s="0" t="inlineStr"/>
-      <c r="H195" t="inlineStr"/>
+      <c r="H195" s="0" t="inlineStr"/>
       <c r="I195" s="0" t="inlineStr"/>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr"/>
-      <c r="M195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
-      <c r="O195" t="inlineStr"/>
+      <c r="J195" s="0" t="inlineStr"/>
+      <c r="K195" s="0" t="inlineStr"/>
+      <c r="L195" s="0" t="inlineStr"/>
+      <c r="M195" s="0" t="inlineStr"/>
+      <c r="N195" s="0" t="inlineStr"/>
+      <c r="O195" s="0" t="inlineStr"/>
     </row>
     <row r="196" ht="15" customHeight="1" s="72">
       <c r="A196" s="33" t="inlineStr"/>
@@ -11126,38 +11125,38 @@
       <c r="O205" s="19" t="inlineStr"/>
     </row>
     <row r="206" ht="9.75" customHeight="1" s="72">
-      <c r="A206" t="inlineStr"/>
-      <c r="B206" t="inlineStr"/>
-      <c r="C206" t="inlineStr"/>
-      <c r="D206" t="inlineStr"/>
-      <c r="E206" t="inlineStr"/>
-      <c r="F206" t="inlineStr"/>
-      <c r="G206" t="inlineStr"/>
-      <c r="H206" t="inlineStr"/>
-      <c r="I206" t="inlineStr"/>
-      <c r="J206" t="inlineStr"/>
-      <c r="K206" t="inlineStr"/>
-      <c r="L206" t="inlineStr"/>
-      <c r="M206" t="inlineStr"/>
-      <c r="N206" t="inlineStr"/>
-      <c r="O206" t="inlineStr"/>
+      <c r="A206" s="0" t="inlineStr"/>
+      <c r="B206" s="0" t="inlineStr"/>
+      <c r="C206" s="0" t="inlineStr"/>
+      <c r="D206" s="0" t="inlineStr"/>
+      <c r="E206" s="0" t="inlineStr"/>
+      <c r="F206" s="0" t="inlineStr"/>
+      <c r="G206" s="0" t="inlineStr"/>
+      <c r="H206" s="0" t="inlineStr"/>
+      <c r="I206" s="0" t="inlineStr"/>
+      <c r="J206" s="0" t="inlineStr"/>
+      <c r="K206" s="0" t="inlineStr"/>
+      <c r="L206" s="0" t="inlineStr"/>
+      <c r="M206" s="0" t="inlineStr"/>
+      <c r="N206" s="0" t="inlineStr"/>
+      <c r="O206" s="0" t="inlineStr"/>
     </row>
     <row r="207" ht="15.75" customHeight="1" s="72">
       <c r="A207" s="84" t="inlineStr"/>
-      <c r="B207" t="inlineStr"/>
-      <c r="C207" t="inlineStr"/>
-      <c r="D207" t="inlineStr"/>
-      <c r="E207" t="inlineStr"/>
-      <c r="F207" t="inlineStr"/>
-      <c r="G207" t="inlineStr"/>
-      <c r="H207" t="inlineStr"/>
-      <c r="I207" t="inlineStr"/>
-      <c r="J207" t="inlineStr"/>
-      <c r="K207" t="inlineStr"/>
-      <c r="L207" t="inlineStr"/>
-      <c r="M207" t="inlineStr"/>
-      <c r="N207" t="inlineStr"/>
-      <c r="O207" t="inlineStr"/>
+      <c r="B207" s="0" t="inlineStr"/>
+      <c r="C207" s="0" t="inlineStr"/>
+      <c r="D207" s="0" t="inlineStr"/>
+      <c r="E207" s="0" t="inlineStr"/>
+      <c r="F207" s="0" t="inlineStr"/>
+      <c r="G207" s="0" t="inlineStr"/>
+      <c r="H207" s="0" t="inlineStr"/>
+      <c r="I207" s="0" t="inlineStr"/>
+      <c r="J207" s="0" t="inlineStr"/>
+      <c r="K207" s="0" t="inlineStr"/>
+      <c r="L207" s="0" t="inlineStr"/>
+      <c r="M207" s="0" t="inlineStr"/>
+      <c r="N207" s="0" t="inlineStr"/>
+      <c r="O207" s="0" t="inlineStr"/>
     </row>
     <row r="208" ht="15" customHeight="1" s="72">
       <c r="A208" s="39" t="inlineStr"/>
@@ -11180,18 +11179,18 @@
       <c r="A209" s="58" t="inlineStr"/>
       <c r="B209" s="95" t="inlineStr"/>
       <c r="C209" s="0" t="inlineStr"/>
-      <c r="D209" t="inlineStr"/>
-      <c r="E209" t="inlineStr"/>
-      <c r="F209" t="inlineStr"/>
-      <c r="G209" t="inlineStr"/>
-      <c r="H209" t="inlineStr"/>
-      <c r="I209" t="inlineStr"/>
-      <c r="J209" t="inlineStr"/>
-      <c r="K209" t="inlineStr"/>
-      <c r="L209" t="inlineStr"/>
-      <c r="M209" t="inlineStr"/>
-      <c r="N209" t="inlineStr"/>
-      <c r="O209" t="inlineStr"/>
+      <c r="D209" s="0" t="inlineStr"/>
+      <c r="E209" s="0" t="inlineStr"/>
+      <c r="F209" s="0" t="inlineStr"/>
+      <c r="G209" s="0" t="inlineStr"/>
+      <c r="H209" s="0" t="inlineStr"/>
+      <c r="I209" s="0" t="inlineStr"/>
+      <c r="J209" s="0" t="inlineStr"/>
+      <c r="K209" s="0" t="inlineStr"/>
+      <c r="L209" s="0" t="inlineStr"/>
+      <c r="M209" s="0" t="inlineStr"/>
+      <c r="N209" s="0" t="inlineStr"/>
+      <c r="O209" s="0" t="inlineStr"/>
     </row>
     <row r="210" ht="18" customHeight="1" s="72">
       <c r="A210" s="96" t="inlineStr"/>
@@ -11201,14 +11200,14 @@
       <c r="E210" s="0" t="inlineStr"/>
       <c r="F210" s="0" t="inlineStr"/>
       <c r="G210" s="0" t="inlineStr"/>
-      <c r="H210" t="inlineStr"/>
+      <c r="H210" s="0" t="inlineStr"/>
       <c r="I210" s="0" t="inlineStr"/>
-      <c r="J210" t="inlineStr"/>
-      <c r="K210" t="inlineStr"/>
-      <c r="L210" t="inlineStr"/>
-      <c r="M210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
-      <c r="O210" t="inlineStr"/>
+      <c r="J210" s="0" t="inlineStr"/>
+      <c r="K210" s="0" t="inlineStr"/>
+      <c r="L210" s="0" t="inlineStr"/>
+      <c r="M210" s="0" t="inlineStr"/>
+      <c r="N210" s="0" t="inlineStr"/>
+      <c r="O210" s="0" t="inlineStr"/>
     </row>
     <row r="211" ht="15" customHeight="1" s="72">
       <c r="A211" s="33" t="inlineStr"/>
@@ -11381,38 +11380,38 @@
       <c r="O220" s="19" t="inlineStr"/>
     </row>
     <row r="221" ht="9.75" customHeight="1" s="72">
-      <c r="A221" t="inlineStr"/>
-      <c r="B221" t="inlineStr"/>
-      <c r="C221" t="inlineStr"/>
-      <c r="D221" t="inlineStr"/>
-      <c r="E221" t="inlineStr"/>
-      <c r="F221" t="inlineStr"/>
-      <c r="G221" t="inlineStr"/>
-      <c r="H221" t="inlineStr"/>
-      <c r="I221" t="inlineStr"/>
-      <c r="J221" t="inlineStr"/>
-      <c r="K221" t="inlineStr"/>
-      <c r="L221" t="inlineStr"/>
-      <c r="M221" t="inlineStr"/>
-      <c r="N221" t="inlineStr"/>
-      <c r="O221" t="inlineStr"/>
+      <c r="A221" s="0" t="inlineStr"/>
+      <c r="B221" s="0" t="inlineStr"/>
+      <c r="C221" s="0" t="inlineStr"/>
+      <c r="D221" s="0" t="inlineStr"/>
+      <c r="E221" s="0" t="inlineStr"/>
+      <c r="F221" s="0" t="inlineStr"/>
+      <c r="G221" s="0" t="inlineStr"/>
+      <c r="H221" s="0" t="inlineStr"/>
+      <c r="I221" s="0" t="inlineStr"/>
+      <c r="J221" s="0" t="inlineStr"/>
+      <c r="K221" s="0" t="inlineStr"/>
+      <c r="L221" s="0" t="inlineStr"/>
+      <c r="M221" s="0" t="inlineStr"/>
+      <c r="N221" s="0" t="inlineStr"/>
+      <c r="O221" s="0" t="inlineStr"/>
     </row>
     <row r="222" ht="15.75" customHeight="1" s="72">
       <c r="A222" s="88" t="inlineStr"/>
-      <c r="B222" t="inlineStr"/>
-      <c r="C222" t="inlineStr"/>
-      <c r="D222" t="inlineStr"/>
-      <c r="E222" t="inlineStr"/>
-      <c r="F222" t="inlineStr"/>
-      <c r="G222" t="inlineStr"/>
-      <c r="H222" t="inlineStr"/>
-      <c r="I222" t="inlineStr"/>
-      <c r="J222" t="inlineStr"/>
-      <c r="K222" t="inlineStr"/>
-      <c r="L222" t="inlineStr"/>
-      <c r="M222" t="inlineStr"/>
-      <c r="N222" t="inlineStr"/>
-      <c r="O222" t="inlineStr"/>
+      <c r="B222" s="0" t="inlineStr"/>
+      <c r="C222" s="0" t="inlineStr"/>
+      <c r="D222" s="0" t="inlineStr"/>
+      <c r="E222" s="0" t="inlineStr"/>
+      <c r="F222" s="0" t="inlineStr"/>
+      <c r="G222" s="0" t="inlineStr"/>
+      <c r="H222" s="0" t="inlineStr"/>
+      <c r="I222" s="0" t="inlineStr"/>
+      <c r="J222" s="0" t="inlineStr"/>
+      <c r="K222" s="0" t="inlineStr"/>
+      <c r="L222" s="0" t="inlineStr"/>
+      <c r="M222" s="0" t="inlineStr"/>
+      <c r="N222" s="0" t="inlineStr"/>
+      <c r="O222" s="0" t="inlineStr"/>
     </row>
     <row r="223" ht="15" customHeight="1" s="72">
       <c r="A223" s="45" t="inlineStr"/>
@@ -11435,18 +11434,18 @@
       <c r="A224" s="46" t="inlineStr"/>
       <c r="B224" s="89" t="inlineStr"/>
       <c r="C224" s="0" t="inlineStr"/>
-      <c r="D224" t="inlineStr"/>
-      <c r="E224" t="inlineStr"/>
-      <c r="F224" t="inlineStr"/>
-      <c r="G224" t="inlineStr"/>
-      <c r="H224" t="inlineStr"/>
-      <c r="I224" t="inlineStr"/>
-      <c r="J224" t="inlineStr"/>
-      <c r="K224" t="inlineStr"/>
-      <c r="L224" t="inlineStr"/>
-      <c r="M224" t="inlineStr"/>
-      <c r="N224" t="inlineStr"/>
-      <c r="O224" t="inlineStr"/>
+      <c r="D224" s="0" t="inlineStr"/>
+      <c r="E224" s="0" t="inlineStr"/>
+      <c r="F224" s="0" t="inlineStr"/>
+      <c r="G224" s="0" t="inlineStr"/>
+      <c r="H224" s="0" t="inlineStr"/>
+      <c r="I224" s="0" t="inlineStr"/>
+      <c r="J224" s="0" t="inlineStr"/>
+      <c r="K224" s="0" t="inlineStr"/>
+      <c r="L224" s="0" t="inlineStr"/>
+      <c r="M224" s="0" t="inlineStr"/>
+      <c r="N224" s="0" t="inlineStr"/>
+      <c r="O224" s="0" t="inlineStr"/>
     </row>
     <row r="225" ht="18" customHeight="1" s="72">
       <c r="A225" s="92" t="inlineStr"/>
@@ -11456,14 +11455,14 @@
       <c r="E225" s="0" t="inlineStr"/>
       <c r="F225" s="0" t="inlineStr"/>
       <c r="G225" s="0" t="inlineStr"/>
-      <c r="H225" t="inlineStr"/>
+      <c r="H225" s="0" t="inlineStr"/>
       <c r="I225" s="0" t="inlineStr"/>
-      <c r="J225" t="inlineStr"/>
-      <c r="K225" t="inlineStr"/>
-      <c r="L225" t="inlineStr"/>
-      <c r="M225" t="inlineStr"/>
-      <c r="N225" t="inlineStr"/>
-      <c r="O225" t="inlineStr"/>
+      <c r="J225" s="0" t="inlineStr"/>
+      <c r="K225" s="0" t="inlineStr"/>
+      <c r="L225" s="0" t="inlineStr"/>
+      <c r="M225" s="0" t="inlineStr"/>
+      <c r="N225" s="0" t="inlineStr"/>
+      <c r="O225" s="0" t="inlineStr"/>
     </row>
     <row r="226" ht="15" customHeight="1" s="72">
       <c r="A226" s="33" t="inlineStr"/>
@@ -11636,72 +11635,72 @@
       <c r="O235" s="19" t="inlineStr"/>
     </row>
     <row r="236" ht="9.75" customHeight="1" s="72">
-      <c r="A236" t="inlineStr"/>
-      <c r="B236" t="inlineStr"/>
-      <c r="C236" t="inlineStr"/>
-      <c r="D236" t="inlineStr"/>
-      <c r="E236" t="inlineStr"/>
-      <c r="F236" t="inlineStr"/>
-      <c r="G236" t="inlineStr"/>
-      <c r="H236" t="inlineStr"/>
-      <c r="I236" t="inlineStr"/>
-      <c r="J236" t="inlineStr"/>
-      <c r="K236" t="inlineStr"/>
-      <c r="L236" t="inlineStr"/>
-      <c r="M236" t="inlineStr"/>
-      <c r="N236" t="inlineStr"/>
-      <c r="O236" t="inlineStr"/>
+      <c r="A236" s="0" t="inlineStr"/>
+      <c r="B236" s="0" t="inlineStr"/>
+      <c r="C236" s="0" t="inlineStr"/>
+      <c r="D236" s="0" t="inlineStr"/>
+      <c r="E236" s="0" t="inlineStr"/>
+      <c r="F236" s="0" t="inlineStr"/>
+      <c r="G236" s="0" t="inlineStr"/>
+      <c r="H236" s="0" t="inlineStr"/>
+      <c r="I236" s="0" t="inlineStr"/>
+      <c r="J236" s="0" t="inlineStr"/>
+      <c r="K236" s="0" t="inlineStr"/>
+      <c r="L236" s="0" t="inlineStr"/>
+      <c r="M236" s="0" t="inlineStr"/>
+      <c r="N236" s="0" t="inlineStr"/>
+      <c r="O236" s="0" t="inlineStr"/>
     </row>
     <row r="237" ht="3.75" customHeight="1" s="72">
       <c r="A237" s="97" t="inlineStr"/>
-      <c r="B237" t="inlineStr"/>
-      <c r="C237" t="inlineStr"/>
-      <c r="D237" t="inlineStr"/>
-      <c r="E237" t="inlineStr"/>
-      <c r="F237" t="inlineStr"/>
-      <c r="G237" t="inlineStr"/>
-      <c r="H237" t="inlineStr"/>
-      <c r="I237" t="inlineStr"/>
-      <c r="J237" t="inlineStr"/>
-      <c r="K237" t="inlineStr"/>
-      <c r="L237" t="inlineStr"/>
-      <c r="M237" t="inlineStr"/>
-      <c r="N237" t="inlineStr"/>
-      <c r="O237" t="inlineStr"/>
+      <c r="B237" s="0" t="inlineStr"/>
+      <c r="C237" s="0" t="inlineStr"/>
+      <c r="D237" s="0" t="inlineStr"/>
+      <c r="E237" s="0" t="inlineStr"/>
+      <c r="F237" s="0" t="inlineStr"/>
+      <c r="G237" s="0" t="inlineStr"/>
+      <c r="H237" s="0" t="inlineStr"/>
+      <c r="I237" s="0" t="inlineStr"/>
+      <c r="J237" s="0" t="inlineStr"/>
+      <c r="K237" s="0" t="inlineStr"/>
+      <c r="L237" s="0" t="inlineStr"/>
+      <c r="M237" s="0" t="inlineStr"/>
+      <c r="N237" s="0" t="inlineStr"/>
+      <c r="O237" s="0" t="inlineStr"/>
     </row>
     <row r="238" ht="9.75" customHeight="1" s="72">
-      <c r="A238" t="inlineStr"/>
-      <c r="B238" t="inlineStr"/>
-      <c r="C238" t="inlineStr"/>
-      <c r="D238" t="inlineStr"/>
-      <c r="E238" t="inlineStr"/>
-      <c r="F238" t="inlineStr"/>
-      <c r="G238" t="inlineStr"/>
-      <c r="H238" t="inlineStr"/>
-      <c r="I238" t="inlineStr"/>
-      <c r="J238" t="inlineStr"/>
-      <c r="K238" t="inlineStr"/>
-      <c r="L238" t="inlineStr"/>
-      <c r="M238" t="inlineStr"/>
-      <c r="N238" t="inlineStr"/>
-      <c r="O238" t="inlineStr"/>
+      <c r="A238" s="0" t="inlineStr"/>
+      <c r="B238" s="0" t="inlineStr"/>
+      <c r="C238" s="0" t="inlineStr"/>
+      <c r="D238" s="0" t="inlineStr"/>
+      <c r="E238" s="0" t="inlineStr"/>
+      <c r="F238" s="0" t="inlineStr"/>
+      <c r="G238" s="0" t="inlineStr"/>
+      <c r="H238" s="0" t="inlineStr"/>
+      <c r="I238" s="0" t="inlineStr"/>
+      <c r="J238" s="0" t="inlineStr"/>
+      <c r="K238" s="0" t="inlineStr"/>
+      <c r="L238" s="0" t="inlineStr"/>
+      <c r="M238" s="0" t="inlineStr"/>
+      <c r="N238" s="0" t="inlineStr"/>
+      <c r="O238" s="0" t="inlineStr"/>
     </row>
     <row r="239" ht="9.75" customHeight="1" s="72">
-      <c r="A239" t="inlineStr"/>
-      <c r="B239" t="inlineStr"/>
-      <c r="C239" t="inlineStr"/>
-      <c r="D239" t="inlineStr"/>
-      <c r="E239" t="inlineStr"/>
-      <c r="F239" t="inlineStr"/>
-      <c r="G239" t="inlineStr"/>
-      <c r="H239" t="inlineStr"/>
-      <c r="I239" t="inlineStr"/>
-      <c r="J239" t="inlineStr"/>
-      <c r="K239" t="inlineStr"/>
-      <c r="L239" t="inlineStr"/>
-      <c r="M239" t="inlineStr"/>
-      <c r="N239" t="inlineStr"/>
-      <c r="O239" t="inlineStr"/>
+      <c r="A239" s="0" t="inlineStr"/>
+      <c r="B239" s="0" t="inlineStr"/>
+      <c r="C239" s="0" t="inlineStr"/>
+      <c r="D239" s="0" t="inlineStr"/>
+      <c r="E239" s="0" t="inlineStr"/>
+      <c r="F239" s="0" t="inlineStr"/>
+      <c r="G239" s="0" t="inlineStr"/>
+      <c r="H239" s="0" t="inlineStr"/>
+      <c r="I239" s="0" t="inlineStr"/>
+      <c r="J239" s="0" t="inlineStr"/>
+      <c r="K239" s="0" t="inlineStr"/>
+      <c r="L239" s="0" t="inlineStr"/>
+      <c r="M239" s="0" t="inlineStr"/>
+      <c r="N239" s="0" t="inlineStr"/>
+      <c r="O239" s="0" t="inlineStr"/>
     </row>
     <row r="240" ht="27.75" customHeight="1" s="72">
       <c r="A240" s="98" t="inlineStr">
@@ -13123,20 +13122,20 @@
     </row>
     <row r="270" ht="18" customHeight="1" s="72">
       <c r="A270" s="82" t="inlineStr"/>
-      <c r="B270" t="inlineStr"/>
-      <c r="C270" t="inlineStr"/>
-      <c r="D270" t="inlineStr"/>
-      <c r="E270" t="inlineStr"/>
-      <c r="F270" t="inlineStr"/>
-      <c r="G270" t="inlineStr"/>
-      <c r="H270" t="inlineStr"/>
-      <c r="I270" t="inlineStr"/>
-      <c r="J270" t="inlineStr"/>
-      <c r="K270" t="inlineStr"/>
-      <c r="L270" t="inlineStr"/>
-      <c r="M270" t="inlineStr"/>
-      <c r="N270" t="inlineStr"/>
-      <c r="O270" t="inlineStr"/>
+      <c r="B270" s="0" t="inlineStr"/>
+      <c r="C270" s="0" t="inlineStr"/>
+      <c r="D270" s="0" t="inlineStr"/>
+      <c r="E270" s="0" t="inlineStr"/>
+      <c r="F270" s="0" t="inlineStr"/>
+      <c r="G270" s="0" t="inlineStr"/>
+      <c r="H270" s="0" t="inlineStr"/>
+      <c r="I270" s="0" t="inlineStr"/>
+      <c r="J270" s="0" t="inlineStr"/>
+      <c r="K270" s="0" t="inlineStr"/>
+      <c r="L270" s="0" t="inlineStr"/>
+      <c r="M270" s="0" t="inlineStr"/>
+      <c r="N270" s="0" t="inlineStr"/>
+      <c r="O270" s="0" t="inlineStr"/>
     </row>
     <row r="271" ht="15" customHeight="1" s="72">
       <c r="A271" s="33" t="inlineStr">
@@ -13922,48 +13921,48 @@
           <t>Başlık</t>
         </is>
       </c>
-      <c r="B283" t="inlineStr">
+      <c r="B283" s="0" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="C283" t="inlineStr">
+      <c r="C283" s="0" t="inlineStr">
         <is>
           <t>İçerik / URL</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr">
+      <c r="D283" s="0" t="inlineStr">
         <is>
           <t>Genişlik</t>
         </is>
       </c>
-      <c r="E283" t="inlineStr">
+      <c r="E283" s="0" t="inlineStr">
         <is>
           <t>Yükseklik</t>
         </is>
       </c>
-      <c r="F283" t="inlineStr">
+      <c r="F283" s="0" t="inlineStr">
         <is>
           <t>Caption</t>
         </is>
       </c>
-      <c r="G283" t="inlineStr">
+      <c r="G283" s="0" t="inlineStr">
         <is>
           <t>Extra</t>
         </is>
       </c>
-      <c r="H283" t="inlineStr">
+      <c r="H283" s="0" t="inlineStr">
         <is>
           <t>Kod</t>
         </is>
       </c>
-      <c r="I283" t="inlineStr"/>
-      <c r="J283" t="inlineStr"/>
-      <c r="K283" t="inlineStr"/>
-      <c r="L283" t="inlineStr"/>
-      <c r="M283" t="inlineStr"/>
-      <c r="N283" t="inlineStr"/>
-      <c r="O283" t="inlineStr"/>
+      <c r="I283" s="0" t="inlineStr"/>
+      <c r="J283" s="0" t="inlineStr"/>
+      <c r="K283" s="0" t="inlineStr"/>
+      <c r="L283" s="0" t="inlineStr"/>
+      <c r="M283" s="0" t="inlineStr"/>
+      <c r="N283" s="0" t="inlineStr"/>
+      <c r="O283" s="0" t="inlineStr"/>
     </row>
     <row r="284" ht="15" customHeight="1" s="72">
       <c r="A284" s="39" t="inlineStr">
@@ -14022,22 +14021,22 @@
 ⭐ En Çok Tercih Edilen Seçenek</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
-      <c r="E285" t="inlineStr"/>
-      <c r="F285" t="inlineStr"/>
-      <c r="G285" t="inlineStr"/>
-      <c r="H285" t="inlineStr">
+      <c r="D285" s="0" t="inlineStr"/>
+      <c r="E285" s="0" t="inlineStr"/>
+      <c r="F285" s="0" t="inlineStr"/>
+      <c r="G285" s="0" t="inlineStr"/>
+      <c r="H285" s="0" t="inlineStr">
         <is>
           <t>toggle-1-right</t>
         </is>
       </c>
-      <c r="I285" t="inlineStr"/>
-      <c r="J285" t="inlineStr"/>
-      <c r="K285" t="inlineStr"/>
-      <c r="L285" t="inlineStr"/>
-      <c r="M285" t="inlineStr"/>
-      <c r="N285" t="inlineStr"/>
-      <c r="O285" t="inlineStr"/>
+      <c r="I285" s="0" t="inlineStr"/>
+      <c r="J285" s="0" t="inlineStr"/>
+      <c r="K285" s="0" t="inlineStr"/>
+      <c r="L285" s="0" t="inlineStr"/>
+      <c r="M285" s="0" t="inlineStr"/>
+      <c r="N285" s="0" t="inlineStr"/>
+      <c r="O285" s="0" t="inlineStr"/>
     </row>
     <row r="286" ht="18" customHeight="1" s="72">
       <c r="A286" s="96" t="inlineStr">
@@ -14063,18 +14062,18 @@
       <c r="E286" s="0" t="inlineStr"/>
       <c r="F286" s="0" t="inlineStr"/>
       <c r="G286" s="0" t="inlineStr"/>
-      <c r="H286" t="inlineStr">
+      <c r="H286" s="0" t="inlineStr">
         <is>
           <t>toggle-2-left</t>
         </is>
       </c>
       <c r="I286" s="0" t="inlineStr"/>
-      <c r="J286" t="inlineStr"/>
-      <c r="K286" t="inlineStr"/>
-      <c r="L286" t="inlineStr"/>
-      <c r="M286" t="inlineStr"/>
-      <c r="N286" t="inlineStr"/>
-      <c r="O286" t="inlineStr"/>
+      <c r="J286" s="0" t="inlineStr"/>
+      <c r="K286" s="0" t="inlineStr"/>
+      <c r="L286" s="0" t="inlineStr"/>
+      <c r="M286" s="0" t="inlineStr"/>
+      <c r="N286" s="0" t="inlineStr"/>
+      <c r="O286" s="0" t="inlineStr"/>
     </row>
     <row r="287" ht="15" customHeight="1" s="72">
       <c r="A287" s="33" t="inlineStr">
@@ -14115,42 +14114,38 @@
     <row r="288" ht="15" customHeight="1" s="72">
       <c r="A288" s="33" t="inlineStr">
         <is>
-          <t>slot01</t>
+          <t>Cephe Görseli</t>
         </is>
       </c>
       <c r="B288" s="19" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>image</t>
         </is>
       </c>
       <c r="C288" s="19" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>https://picsum.photos/seed/veaklasik/480/300</t>
         </is>
       </c>
       <c r="D288" s="19" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E288" s="19" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="F288" s="19" t="inlineStr">
         <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G288" s="19" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>Görsel</t>
+        </is>
+      </c>
+      <c r="G288" s="19" t="inlineStr"/>
       <c r="H288" s="19" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>toggle-1-left</t>
         </is>
       </c>
       <c r="I288" s="19" t="inlineStr"/>
@@ -14164,42 +14159,38 @@
     <row r="289" ht="15" customHeight="1" s="72">
       <c r="A289" s="33" t="inlineStr">
         <is>
-          <t>slot02</t>
+          <t>Tanıtım</t>
         </is>
       </c>
       <c r="B289" s="19" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="C289" s="19" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>https://www.youtube.com/watch?v=aqz-KE-bpKQ</t>
         </is>
       </c>
       <c r="D289" s="19" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E289" s="19" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>170px</t>
         </is>
       </c>
       <c r="F289" s="19" t="inlineStr">
         <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G289" s="19" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>Video</t>
+        </is>
+      </c>
+      <c r="G289" s="19" t="inlineStr"/>
       <c r="H289" s="19" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>toggle-1-left</t>
         </is>
       </c>
       <c r="I289" s="19" t="inlineStr"/>
@@ -14213,42 +14204,30 @@
     <row r="290" ht="15" customHeight="1" s="72">
       <c r="A290" s="33" t="inlineStr">
         <is>
-          <t>slot03</t>
+          <t>Broşür</t>
         </is>
       </c>
       <c r="B290" s="19" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>link</t>
         </is>
       </c>
       <c r="C290" s="19" t="inlineStr">
         <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D290" s="19" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E290" s="19" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>https://example.com/klasik-cephe-brosur.pdf</t>
+        </is>
+      </c>
+      <c r="D290" s="19" t="inlineStr"/>
+      <c r="E290" s="19" t="inlineStr"/>
       <c r="F290" s="19" t="inlineStr">
         <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G290" s="19" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>Broşür (PDF)</t>
+        </is>
+      </c>
+      <c r="G290" s="19" t="inlineStr"/>
       <c r="H290" s="19" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>toggle-1-left</t>
         </is>
       </c>
       <c r="I290" s="19" t="inlineStr"/>
@@ -14262,42 +14241,31 @@
     <row r="291" ht="15" customHeight="1" s="72">
       <c r="A291" s="33" t="inlineStr">
         <is>
-          <t>slot04</t>
+          <t>Ek Bilgi</t>
         </is>
       </c>
       <c r="B291" s="19" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C291" s="19" t="inlineStr">
         <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D291" s="19" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E291" s="19" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>**Ek Detay:** Klasik cephede kullanılan travertin Denizli Kocabaş ocağından doğal çıkarılmaktadır.
+25 yıl garanti.</t>
+        </is>
+      </c>
+      <c r="D291" s="19" t="inlineStr"/>
+      <c r="E291" s="19" t="inlineStr"/>
       <c r="F291" s="19" t="inlineStr">
         <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G291" s="19" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>Detay</t>
+        </is>
+      </c>
+      <c r="G291" s="19" t="inlineStr"/>
       <c r="H291" s="19" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>toggle-1-left</t>
         </is>
       </c>
       <c r="I291" s="19" t="inlineStr"/>
@@ -14311,7 +14279,7 @@
     <row r="292" ht="15" customHeight="1" s="72">
       <c r="A292" s="33" t="inlineStr">
         <is>
-          <t>slot05</t>
+          <t>slot01</t>
         </is>
       </c>
       <c r="B292" s="19" t="inlineStr">
@@ -14360,7 +14328,7 @@
     <row r="293" ht="15" customHeight="1" s="72">
       <c r="A293" s="33" t="inlineStr">
         <is>
-          <t>slot06</t>
+          <t>slot02</t>
         </is>
       </c>
       <c r="B293" s="19" t="inlineStr">
@@ -14409,7 +14377,7 @@
     <row r="294" ht="15" customHeight="1" s="72">
       <c r="A294" s="33" t="inlineStr">
         <is>
-          <t>slot07</t>
+          <t>slot03</t>
         </is>
       </c>
       <c r="B294" s="19" t="inlineStr">
@@ -14458,7 +14426,7 @@
     <row r="295" ht="15" customHeight="1" s="72">
       <c r="A295" s="33" t="inlineStr">
         <is>
-          <t>slot08</t>
+          <t>slot04</t>
         </is>
       </c>
       <c r="B295" s="19" t="inlineStr">
@@ -14507,7 +14475,7 @@
     <row r="296" ht="15" customHeight="1" s="72">
       <c r="A296" s="33" t="inlineStr">
         <is>
-          <t>slot09</t>
+          <t>slot05</t>
         </is>
       </c>
       <c r="B296" s="19" t="inlineStr">
@@ -14554,107 +14522,107 @@
       <c r="O296" s="19" t="inlineStr"/>
     </row>
     <row r="297" ht="9.75" customHeight="1" s="72">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>slot10</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F297" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G297" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H297" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="I297" t="inlineStr"/>
-      <c r="J297" t="inlineStr"/>
-      <c r="K297" t="inlineStr"/>
-      <c r="L297" t="inlineStr"/>
-      <c r="M297" t="inlineStr"/>
-      <c r="N297" t="inlineStr"/>
-      <c r="O297" t="inlineStr"/>
+      <c r="A297" s="0" t="inlineStr">
+        <is>
+          <t>slot06</t>
+        </is>
+      </c>
+      <c r="B297" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C297" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D297" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E297" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F297" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G297" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H297" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I297" s="0" t="inlineStr"/>
+      <c r="J297" s="0" t="inlineStr"/>
+      <c r="K297" s="0" t="inlineStr"/>
+      <c r="L297" s="0" t="inlineStr"/>
+      <c r="M297" s="0" t="inlineStr"/>
+      <c r="N297" s="0" t="inlineStr"/>
+      <c r="O297" s="0" t="inlineStr"/>
     </row>
     <row r="298" ht="15.75" customHeight="1" s="72">
       <c r="A298" s="88" t="inlineStr">
         <is>
-          <t>slot11</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F298" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H298" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="I298" t="inlineStr"/>
-      <c r="J298" t="inlineStr"/>
-      <c r="K298" t="inlineStr"/>
-      <c r="L298" t="inlineStr"/>
-      <c r="M298" t="inlineStr"/>
-      <c r="N298" t="inlineStr"/>
-      <c r="O298" t="inlineStr"/>
+          <t>slot07</t>
+        </is>
+      </c>
+      <c r="B298" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C298" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D298" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E298" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F298" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G298" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H298" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I298" s="0" t="inlineStr"/>
+      <c r="J298" s="0" t="inlineStr"/>
+      <c r="K298" s="0" t="inlineStr"/>
+      <c r="L298" s="0" t="inlineStr"/>
+      <c r="M298" s="0" t="inlineStr"/>
+      <c r="N298" s="0" t="inlineStr"/>
+      <c r="O298" s="0" t="inlineStr"/>
     </row>
     <row r="299" ht="15" customHeight="1" s="72">
       <c r="A299" s="45" t="inlineStr">
         <is>
-          <t>slot12</t>
+          <t>slot08</t>
         </is>
       </c>
       <c r="B299" s="45" t="inlineStr">
@@ -14703,7 +14671,7 @@
     <row r="300" ht="64.5" customHeight="1" s="72">
       <c r="A300" s="46" t="inlineStr">
         <is>
-          <t>slot13</t>
+          <t>slot09</t>
         </is>
       </c>
       <c r="B300" s="89" t="inlineStr">
@@ -14716,43 +14684,43 @@
           <t>null</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H300" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="I300" t="inlineStr"/>
-      <c r="J300" t="inlineStr"/>
-      <c r="K300" t="inlineStr"/>
-      <c r="L300" t="inlineStr"/>
-      <c r="M300" t="inlineStr"/>
-      <c r="N300" t="inlineStr"/>
-      <c r="O300" t="inlineStr"/>
+      <c r="D300" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E300" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F300" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G300" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H300" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I300" s="0" t="inlineStr"/>
+      <c r="J300" s="0" t="inlineStr"/>
+      <c r="K300" s="0" t="inlineStr"/>
+      <c r="L300" s="0" t="inlineStr"/>
+      <c r="M300" s="0" t="inlineStr"/>
+      <c r="N300" s="0" t="inlineStr"/>
+      <c r="O300" s="0" t="inlineStr"/>
     </row>
     <row r="301" ht="18" customHeight="1" s="72">
       <c r="A301" s="92" t="inlineStr">
         <is>
-          <t>slot14</t>
+          <t>slot10</t>
         </is>
       </c>
       <c r="B301" s="0" t="inlineStr">
@@ -14785,23 +14753,23 @@
           <t>null</t>
         </is>
       </c>
-      <c r="H301" t="inlineStr">
+      <c r="H301" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
       <c r="I301" s="0" t="inlineStr"/>
-      <c r="J301" t="inlineStr"/>
-      <c r="K301" t="inlineStr"/>
-      <c r="L301" t="inlineStr"/>
-      <c r="M301" t="inlineStr"/>
-      <c r="N301" t="inlineStr"/>
-      <c r="O301" t="inlineStr"/>
+      <c r="J301" s="0" t="inlineStr"/>
+      <c r="K301" s="0" t="inlineStr"/>
+      <c r="L301" s="0" t="inlineStr"/>
+      <c r="M301" s="0" t="inlineStr"/>
+      <c r="N301" s="0" t="inlineStr"/>
+      <c r="O301" s="0" t="inlineStr"/>
     </row>
     <row r="302" ht="15" customHeight="1" s="72">
       <c r="A302" s="33" t="inlineStr">
         <is>
-          <t>slot15</t>
+          <t>slot11</t>
         </is>
       </c>
       <c r="B302" s="19" t="inlineStr">
@@ -14850,7 +14818,7 @@
     <row r="303" ht="15" customHeight="1" s="72">
       <c r="A303" s="33" t="inlineStr">
         <is>
-          <t>slot16</t>
+          <t>slot12</t>
         </is>
       </c>
       <c r="B303" s="19" t="inlineStr">
@@ -14899,7 +14867,7 @@
     <row r="304" ht="15" customHeight="1" s="72">
       <c r="A304" s="33" t="inlineStr">
         <is>
-          <t>slot17</t>
+          <t>slot13</t>
         </is>
       </c>
       <c r="B304" s="19" t="inlineStr">
@@ -14948,7 +14916,7 @@
     <row r="305" ht="15" customHeight="1" s="72">
       <c r="A305" s="33" t="inlineStr">
         <is>
-          <t>slot18</t>
+          <t>slot14</t>
         </is>
       </c>
       <c r="B305" s="19" t="inlineStr">
@@ -14997,7 +14965,7 @@
     <row r="306" ht="15" customHeight="1" s="72">
       <c r="A306" s="33" t="inlineStr">
         <is>
-          <t>slot19</t>
+          <t>slot15</t>
         </is>
       </c>
       <c r="B306" s="19" t="inlineStr">
@@ -15046,7 +15014,7 @@
     <row r="307" ht="15" customHeight="1" s="72">
       <c r="A307" s="33" t="inlineStr">
         <is>
-          <t>slot20</t>
+          <t>slot16</t>
         </is>
       </c>
       <c r="B307" s="19" t="inlineStr">
@@ -15095,7 +15063,7 @@
     <row r="308" ht="15" customHeight="1" s="72">
       <c r="A308" s="33" t="inlineStr">
         <is>
-          <t>slot21</t>
+          <t>slot17</t>
         </is>
       </c>
       <c r="B308" s="19" t="inlineStr">
@@ -15144,7 +15112,7 @@
     <row r="309" ht="15" customHeight="1" s="72">
       <c r="A309" s="33" t="inlineStr">
         <is>
-          <t>slot22</t>
+          <t>slot18</t>
         </is>
       </c>
       <c r="B309" s="19" t="inlineStr">
@@ -15193,7 +15161,7 @@
     <row r="310" ht="15" customHeight="1" s="72">
       <c r="A310" s="33" t="inlineStr">
         <is>
-          <t>slot23</t>
+          <t>slot19</t>
         </is>
       </c>
       <c r="B310" s="19" t="inlineStr">
@@ -15242,7 +15210,7 @@
     <row r="311" ht="15" customHeight="1" s="72">
       <c r="A311" s="33" t="inlineStr">
         <is>
-          <t>slot24</t>
+          <t>slot20</t>
         </is>
       </c>
       <c r="B311" s="19" t="inlineStr">
@@ -15289,107 +15257,107 @@
       <c r="O311" s="19" t="inlineStr"/>
     </row>
     <row r="312" ht="9.75" customHeight="1" s="72">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>slot25</t>
-        </is>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F312" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G312" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H312" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="I312" t="inlineStr"/>
-      <c r="J312" t="inlineStr"/>
-      <c r="K312" t="inlineStr"/>
-      <c r="L312" t="inlineStr"/>
-      <c r="M312" t="inlineStr"/>
-      <c r="N312" t="inlineStr"/>
-      <c r="O312" t="inlineStr"/>
+      <c r="A312" s="0" t="inlineStr">
+        <is>
+          <t>slot21</t>
+        </is>
+      </c>
+      <c r="B312" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C312" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D312" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E312" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F312" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G312" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H312" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I312" s="0" t="inlineStr"/>
+      <c r="J312" s="0" t="inlineStr"/>
+      <c r="K312" s="0" t="inlineStr"/>
+      <c r="L312" s="0" t="inlineStr"/>
+      <c r="M312" s="0" t="inlineStr"/>
+      <c r="N312" s="0" t="inlineStr"/>
+      <c r="O312" s="0" t="inlineStr"/>
     </row>
     <row r="313" ht="15.75" customHeight="1" s="72">
       <c r="A313" s="84" t="inlineStr">
         <is>
-          <t>slot26</t>
-        </is>
-      </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F313" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G313" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H313" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="I313" t="inlineStr"/>
-      <c r="J313" t="inlineStr"/>
-      <c r="K313" t="inlineStr"/>
-      <c r="L313" t="inlineStr"/>
-      <c r="M313" t="inlineStr"/>
-      <c r="N313" t="inlineStr"/>
-      <c r="O313" t="inlineStr"/>
+          <t>slot22</t>
+        </is>
+      </c>
+      <c r="B313" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C313" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D313" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E313" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F313" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G313" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H313" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I313" s="0" t="inlineStr"/>
+      <c r="J313" s="0" t="inlineStr"/>
+      <c r="K313" s="0" t="inlineStr"/>
+      <c r="L313" s="0" t="inlineStr"/>
+      <c r="M313" s="0" t="inlineStr"/>
+      <c r="N313" s="0" t="inlineStr"/>
+      <c r="O313" s="0" t="inlineStr"/>
     </row>
     <row r="314" ht="15" customHeight="1" s="72">
       <c r="A314" s="39" t="inlineStr">
         <is>
-          <t>slot27</t>
+          <t>slot23</t>
         </is>
       </c>
       <c r="B314" s="39" t="inlineStr">
@@ -15438,7 +15406,7 @@
     <row r="315" ht="64.5" customHeight="1" s="72">
       <c r="A315" s="58" t="inlineStr">
         <is>
-          <t>slot28</t>
+          <t>slot24</t>
         </is>
       </c>
       <c r="B315" s="95" t="inlineStr">
@@ -15451,43 +15419,43 @@
           <t>null</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F315" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G315" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H315" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="I315" t="inlineStr"/>
-      <c r="J315" t="inlineStr"/>
-      <c r="K315" t="inlineStr"/>
-      <c r="L315" t="inlineStr"/>
-      <c r="M315" t="inlineStr"/>
-      <c r="N315" t="inlineStr"/>
-      <c r="O315" t="inlineStr"/>
+      <c r="D315" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E315" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F315" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G315" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H315" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I315" s="0" t="inlineStr"/>
+      <c r="J315" s="0" t="inlineStr"/>
+      <c r="K315" s="0" t="inlineStr"/>
+      <c r="L315" s="0" t="inlineStr"/>
+      <c r="M315" s="0" t="inlineStr"/>
+      <c r="N315" s="0" t="inlineStr"/>
+      <c r="O315" s="0" t="inlineStr"/>
     </row>
     <row r="316" ht="18" customHeight="1" s="72">
       <c r="A316" s="96" t="inlineStr">
         <is>
-          <t>slot29</t>
+          <t>slot25</t>
         </is>
       </c>
       <c r="B316" s="0" t="inlineStr">
@@ -15520,23 +15488,23 @@
           <t>null</t>
         </is>
       </c>
-      <c r="H316" t="inlineStr">
+      <c r="H316" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
       <c r="I316" s="0" t="inlineStr"/>
-      <c r="J316" t="inlineStr"/>
-      <c r="K316" t="inlineStr"/>
-      <c r="L316" t="inlineStr"/>
-      <c r="M316" t="inlineStr"/>
-      <c r="N316" t="inlineStr"/>
-      <c r="O316" t="inlineStr"/>
+      <c r="J316" s="0" t="inlineStr"/>
+      <c r="K316" s="0" t="inlineStr"/>
+      <c r="L316" s="0" t="inlineStr"/>
+      <c r="M316" s="0" t="inlineStr"/>
+      <c r="N316" s="0" t="inlineStr"/>
+      <c r="O316" s="0" t="inlineStr"/>
     </row>
     <row r="317" ht="15" customHeight="1" s="72">
       <c r="A317" s="33" t="inlineStr">
         <is>
-          <t>slot30</t>
+          <t>slot26</t>
         </is>
       </c>
       <c r="B317" s="19" t="inlineStr">
@@ -15736,38 +15704,38 @@
       <c r="O326" s="19" t="inlineStr"/>
     </row>
     <row r="327" ht="9.75" customHeight="1" s="72">
-      <c r="A327" t="inlineStr"/>
-      <c r="B327" t="inlineStr"/>
-      <c r="C327" t="inlineStr"/>
-      <c r="D327" t="inlineStr"/>
-      <c r="E327" t="inlineStr"/>
-      <c r="F327" t="inlineStr"/>
-      <c r="G327" t="inlineStr"/>
-      <c r="H327" t="inlineStr"/>
-      <c r="I327" t="inlineStr"/>
-      <c r="J327" t="inlineStr"/>
-      <c r="K327" t="inlineStr"/>
-      <c r="L327" t="inlineStr"/>
-      <c r="M327" t="inlineStr"/>
-      <c r="N327" t="inlineStr"/>
-      <c r="O327" t="inlineStr"/>
+      <c r="A327" s="0" t="inlineStr"/>
+      <c r="B327" s="0" t="inlineStr"/>
+      <c r="C327" s="0" t="inlineStr"/>
+      <c r="D327" s="0" t="inlineStr"/>
+      <c r="E327" s="0" t="inlineStr"/>
+      <c r="F327" s="0" t="inlineStr"/>
+      <c r="G327" s="0" t="inlineStr"/>
+      <c r="H327" s="0" t="inlineStr"/>
+      <c r="I327" s="0" t="inlineStr"/>
+      <c r="J327" s="0" t="inlineStr"/>
+      <c r="K327" s="0" t="inlineStr"/>
+      <c r="L327" s="0" t="inlineStr"/>
+      <c r="M327" s="0" t="inlineStr"/>
+      <c r="N327" s="0" t="inlineStr"/>
+      <c r="O327" s="0" t="inlineStr"/>
     </row>
     <row r="328" ht="15.75" customHeight="1" s="72">
       <c r="A328" s="88" t="inlineStr"/>
-      <c r="B328" t="inlineStr"/>
-      <c r="C328" t="inlineStr"/>
-      <c r="D328" t="inlineStr"/>
-      <c r="E328" t="inlineStr"/>
-      <c r="F328" t="inlineStr"/>
-      <c r="G328" t="inlineStr"/>
-      <c r="H328" t="inlineStr"/>
-      <c r="I328" t="inlineStr"/>
-      <c r="J328" t="inlineStr"/>
-      <c r="K328" t="inlineStr"/>
-      <c r="L328" t="inlineStr"/>
-      <c r="M328" t="inlineStr"/>
-      <c r="N328" t="inlineStr"/>
-      <c r="O328" t="inlineStr"/>
+      <c r="B328" s="0" t="inlineStr"/>
+      <c r="C328" s="0" t="inlineStr"/>
+      <c r="D328" s="0" t="inlineStr"/>
+      <c r="E328" s="0" t="inlineStr"/>
+      <c r="F328" s="0" t="inlineStr"/>
+      <c r="G328" s="0" t="inlineStr"/>
+      <c r="H328" s="0" t="inlineStr"/>
+      <c r="I328" s="0" t="inlineStr"/>
+      <c r="J328" s="0" t="inlineStr"/>
+      <c r="K328" s="0" t="inlineStr"/>
+      <c r="L328" s="0" t="inlineStr"/>
+      <c r="M328" s="0" t="inlineStr"/>
+      <c r="N328" s="0" t="inlineStr"/>
+      <c r="O328" s="0" t="inlineStr"/>
     </row>
     <row r="329" ht="15" customHeight="1" s="72">
       <c r="A329" s="45" t="inlineStr"/>
@@ -15790,18 +15758,18 @@
       <c r="A330" s="46" t="inlineStr"/>
       <c r="B330" s="89" t="inlineStr"/>
       <c r="C330" s="0" t="inlineStr"/>
-      <c r="D330" t="inlineStr"/>
-      <c r="E330" t="inlineStr"/>
-      <c r="F330" t="inlineStr"/>
-      <c r="G330" t="inlineStr"/>
-      <c r="H330" t="inlineStr"/>
-      <c r="I330" t="inlineStr"/>
-      <c r="J330" t="inlineStr"/>
-      <c r="K330" t="inlineStr"/>
-      <c r="L330" t="inlineStr"/>
-      <c r="M330" t="inlineStr"/>
-      <c r="N330" t="inlineStr"/>
-      <c r="O330" t="inlineStr"/>
+      <c r="D330" s="0" t="inlineStr"/>
+      <c r="E330" s="0" t="inlineStr"/>
+      <c r="F330" s="0" t="inlineStr"/>
+      <c r="G330" s="0" t="inlineStr"/>
+      <c r="H330" s="0" t="inlineStr"/>
+      <c r="I330" s="0" t="inlineStr"/>
+      <c r="J330" s="0" t="inlineStr"/>
+      <c r="K330" s="0" t="inlineStr"/>
+      <c r="L330" s="0" t="inlineStr"/>
+      <c r="M330" s="0" t="inlineStr"/>
+      <c r="N330" s="0" t="inlineStr"/>
+      <c r="O330" s="0" t="inlineStr"/>
     </row>
     <row r="331" ht="18" customHeight="1" s="72">
       <c r="A331" s="92" t="inlineStr"/>
@@ -15811,14 +15779,14 @@
       <c r="E331" s="0" t="inlineStr"/>
       <c r="F331" s="0" t="inlineStr"/>
       <c r="G331" s="0" t="inlineStr"/>
-      <c r="H331" t="inlineStr"/>
+      <c r="H331" s="0" t="inlineStr"/>
       <c r="I331" s="0" t="inlineStr"/>
-      <c r="J331" t="inlineStr"/>
-      <c r="K331" t="inlineStr"/>
-      <c r="L331" t="inlineStr"/>
-      <c r="M331" t="inlineStr"/>
-      <c r="N331" t="inlineStr"/>
-      <c r="O331" t="inlineStr"/>
+      <c r="J331" s="0" t="inlineStr"/>
+      <c r="K331" s="0" t="inlineStr"/>
+      <c r="L331" s="0" t="inlineStr"/>
+      <c r="M331" s="0" t="inlineStr"/>
+      <c r="N331" s="0" t="inlineStr"/>
+      <c r="O331" s="0" t="inlineStr"/>
     </row>
     <row r="332" ht="15" customHeight="1" s="72">
       <c r="A332" s="33" t="inlineStr"/>
@@ -15991,72 +15959,72 @@
       <c r="O341" s="19" t="inlineStr"/>
     </row>
     <row r="342" ht="9.75" customHeight="1" s="72">
-      <c r="A342" t="inlineStr"/>
-      <c r="B342" t="inlineStr"/>
-      <c r="C342" t="inlineStr"/>
-      <c r="D342" t="inlineStr"/>
-      <c r="E342" t="inlineStr"/>
-      <c r="F342" t="inlineStr"/>
-      <c r="G342" t="inlineStr"/>
-      <c r="H342" t="inlineStr"/>
-      <c r="I342" t="inlineStr"/>
-      <c r="J342" t="inlineStr"/>
-      <c r="K342" t="inlineStr"/>
-      <c r="L342" t="inlineStr"/>
-      <c r="M342" t="inlineStr"/>
-      <c r="N342" t="inlineStr"/>
-      <c r="O342" t="inlineStr"/>
+      <c r="A342" s="0" t="inlineStr"/>
+      <c r="B342" s="0" t="inlineStr"/>
+      <c r="C342" s="0" t="inlineStr"/>
+      <c r="D342" s="0" t="inlineStr"/>
+      <c r="E342" s="0" t="inlineStr"/>
+      <c r="F342" s="0" t="inlineStr"/>
+      <c r="G342" s="0" t="inlineStr"/>
+      <c r="H342" s="0" t="inlineStr"/>
+      <c r="I342" s="0" t="inlineStr"/>
+      <c r="J342" s="0" t="inlineStr"/>
+      <c r="K342" s="0" t="inlineStr"/>
+      <c r="L342" s="0" t="inlineStr"/>
+      <c r="M342" s="0" t="inlineStr"/>
+      <c r="N342" s="0" t="inlineStr"/>
+      <c r="O342" s="0" t="inlineStr"/>
     </row>
     <row r="343" ht="3.75" customHeight="1" s="72">
       <c r="A343" s="99" t="inlineStr"/>
-      <c r="B343" t="inlineStr"/>
-      <c r="C343" t="inlineStr"/>
-      <c r="D343" t="inlineStr"/>
-      <c r="E343" t="inlineStr"/>
-      <c r="F343" t="inlineStr"/>
-      <c r="G343" t="inlineStr"/>
-      <c r="H343" t="inlineStr"/>
-      <c r="I343" t="inlineStr"/>
-      <c r="J343" t="inlineStr"/>
-      <c r="K343" t="inlineStr"/>
-      <c r="L343" t="inlineStr"/>
-      <c r="M343" t="inlineStr"/>
-      <c r="N343" t="inlineStr"/>
-      <c r="O343" t="inlineStr"/>
+      <c r="B343" s="0" t="inlineStr"/>
+      <c r="C343" s="0" t="inlineStr"/>
+      <c r="D343" s="0" t="inlineStr"/>
+      <c r="E343" s="0" t="inlineStr"/>
+      <c r="F343" s="0" t="inlineStr"/>
+      <c r="G343" s="0" t="inlineStr"/>
+      <c r="H343" s="0" t="inlineStr"/>
+      <c r="I343" s="0" t="inlineStr"/>
+      <c r="J343" s="0" t="inlineStr"/>
+      <c r="K343" s="0" t="inlineStr"/>
+      <c r="L343" s="0" t="inlineStr"/>
+      <c r="M343" s="0" t="inlineStr"/>
+      <c r="N343" s="0" t="inlineStr"/>
+      <c r="O343" s="0" t="inlineStr"/>
     </row>
     <row r="344" ht="9.75" customHeight="1" s="72">
-      <c r="A344" t="inlineStr"/>
-      <c r="B344" t="inlineStr"/>
-      <c r="C344" t="inlineStr"/>
-      <c r="D344" t="inlineStr"/>
-      <c r="E344" t="inlineStr"/>
-      <c r="F344" t="inlineStr"/>
-      <c r="G344" t="inlineStr"/>
-      <c r="H344" t="inlineStr"/>
-      <c r="I344" t="inlineStr"/>
-      <c r="J344" t="inlineStr"/>
-      <c r="K344" t="inlineStr"/>
-      <c r="L344" t="inlineStr"/>
-      <c r="M344" t="inlineStr"/>
-      <c r="N344" t="inlineStr"/>
-      <c r="O344" t="inlineStr"/>
+      <c r="A344" s="0" t="inlineStr"/>
+      <c r="B344" s="0" t="inlineStr"/>
+      <c r="C344" s="0" t="inlineStr"/>
+      <c r="D344" s="0" t="inlineStr"/>
+      <c r="E344" s="0" t="inlineStr"/>
+      <c r="F344" s="0" t="inlineStr"/>
+      <c r="G344" s="0" t="inlineStr"/>
+      <c r="H344" s="0" t="inlineStr"/>
+      <c r="I344" s="0" t="inlineStr"/>
+      <c r="J344" s="0" t="inlineStr"/>
+      <c r="K344" s="0" t="inlineStr"/>
+      <c r="L344" s="0" t="inlineStr"/>
+      <c r="M344" s="0" t="inlineStr"/>
+      <c r="N344" s="0" t="inlineStr"/>
+      <c r="O344" s="0" t="inlineStr"/>
     </row>
     <row r="345" ht="9.75" customHeight="1" s="72">
-      <c r="A345" t="inlineStr"/>
-      <c r="B345" t="inlineStr"/>
-      <c r="C345" t="inlineStr"/>
-      <c r="D345" t="inlineStr"/>
-      <c r="E345" t="inlineStr"/>
-      <c r="F345" t="inlineStr"/>
-      <c r="G345" t="inlineStr"/>
-      <c r="H345" t="inlineStr"/>
-      <c r="I345" t="inlineStr"/>
-      <c r="J345" t="inlineStr"/>
-      <c r="K345" t="inlineStr"/>
-      <c r="L345" t="inlineStr"/>
-      <c r="M345" t="inlineStr"/>
-      <c r="N345" t="inlineStr"/>
-      <c r="O345" t="inlineStr"/>
+      <c r="A345" s="0" t="inlineStr"/>
+      <c r="B345" s="0" t="inlineStr"/>
+      <c r="C345" s="0" t="inlineStr"/>
+      <c r="D345" s="0" t="inlineStr"/>
+      <c r="E345" s="0" t="inlineStr"/>
+      <c r="F345" s="0" t="inlineStr"/>
+      <c r="G345" s="0" t="inlineStr"/>
+      <c r="H345" s="0" t="inlineStr"/>
+      <c r="I345" s="0" t="inlineStr"/>
+      <c r="J345" s="0" t="inlineStr"/>
+      <c r="K345" s="0" t="inlineStr"/>
+      <c r="L345" s="0" t="inlineStr"/>
+      <c r="M345" s="0" t="inlineStr"/>
+      <c r="N345" s="0" t="inlineStr"/>
+      <c r="O345" s="0" t="inlineStr"/>
     </row>
     <row r="346" ht="27.75" customHeight="1" s="72">
       <c r="A346" s="100" t="inlineStr">
@@ -17340,20 +17308,20 @@
     </row>
     <row r="372" ht="18" customHeight="1" s="72">
       <c r="A372" s="82" t="inlineStr"/>
-      <c r="B372" t="inlineStr"/>
-      <c r="C372" t="inlineStr"/>
-      <c r="D372" t="inlineStr"/>
-      <c r="E372" t="inlineStr"/>
-      <c r="F372" t="inlineStr"/>
-      <c r="G372" t="inlineStr"/>
-      <c r="H372" t="inlineStr"/>
-      <c r="I372" t="inlineStr"/>
-      <c r="J372" t="inlineStr"/>
-      <c r="K372" t="inlineStr"/>
-      <c r="L372" t="inlineStr"/>
-      <c r="M372" t="inlineStr"/>
-      <c r="N372" t="inlineStr"/>
-      <c r="O372" t="inlineStr"/>
+      <c r="B372" s="0" t="inlineStr"/>
+      <c r="C372" s="0" t="inlineStr"/>
+      <c r="D372" s="0" t="inlineStr"/>
+      <c r="E372" s="0" t="inlineStr"/>
+      <c r="F372" s="0" t="inlineStr"/>
+      <c r="G372" s="0" t="inlineStr"/>
+      <c r="H372" s="0" t="inlineStr"/>
+      <c r="I372" s="0" t="inlineStr"/>
+      <c r="J372" s="0" t="inlineStr"/>
+      <c r="K372" s="0" t="inlineStr"/>
+      <c r="L372" s="0" t="inlineStr"/>
+      <c r="M372" s="0" t="inlineStr"/>
+      <c r="N372" s="0" t="inlineStr"/>
+      <c r="O372" s="0" t="inlineStr"/>
     </row>
     <row r="373" ht="15" customHeight="1" s="72">
       <c r="A373" s="33" t="inlineStr">
@@ -18139,48 +18107,48 @@
           <t>Başlık</t>
         </is>
       </c>
-      <c r="B385" t="inlineStr">
+      <c r="B385" s="0" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="C385" t="inlineStr">
+      <c r="C385" s="0" t="inlineStr">
         <is>
           <t>İçerik / URL</t>
         </is>
       </c>
-      <c r="D385" t="inlineStr">
+      <c r="D385" s="0" t="inlineStr">
         <is>
           <t>Genişlik</t>
         </is>
       </c>
-      <c r="E385" t="inlineStr">
+      <c r="E385" s="0" t="inlineStr">
         <is>
           <t>Yükseklik</t>
         </is>
       </c>
-      <c r="F385" t="inlineStr">
+      <c r="F385" s="0" t="inlineStr">
         <is>
           <t>Caption</t>
         </is>
       </c>
-      <c r="G385" t="inlineStr">
+      <c r="G385" s="0" t="inlineStr">
         <is>
           <t>Extra</t>
         </is>
       </c>
-      <c r="H385" t="inlineStr">
+      <c r="H385" s="0" t="inlineStr">
         <is>
           <t>Kod</t>
         </is>
       </c>
-      <c r="I385" t="inlineStr"/>
-      <c r="J385" t="inlineStr"/>
-      <c r="K385" t="inlineStr"/>
-      <c r="L385" t="inlineStr"/>
-      <c r="M385" t="inlineStr"/>
-      <c r="N385" t="inlineStr"/>
-      <c r="O385" t="inlineStr"/>
+      <c r="I385" s="0" t="inlineStr"/>
+      <c r="J385" s="0" t="inlineStr"/>
+      <c r="K385" s="0" t="inlineStr"/>
+      <c r="L385" s="0" t="inlineStr"/>
+      <c r="M385" s="0" t="inlineStr"/>
+      <c r="N385" s="0" t="inlineStr"/>
+      <c r="O385" s="0" t="inlineStr"/>
     </row>
     <row r="386" ht="15" customHeight="1" s="72">
       <c r="A386" s="39" t="inlineStr">
@@ -18242,22 +18210,22 @@
 📦 Kargo Odası</t>
         </is>
       </c>
-      <c r="D387" t="inlineStr"/>
-      <c r="E387" t="inlineStr"/>
-      <c r="F387" t="inlineStr"/>
-      <c r="G387" t="inlineStr"/>
-      <c r="H387" t="inlineStr">
+      <c r="D387" s="0" t="inlineStr"/>
+      <c r="E387" s="0" t="inlineStr"/>
+      <c r="F387" s="0" t="inlineStr"/>
+      <c r="G387" s="0" t="inlineStr"/>
+      <c r="H387" s="0" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="I387" t="inlineStr"/>
-      <c r="J387" t="inlineStr"/>
-      <c r="K387" t="inlineStr"/>
-      <c r="L387" t="inlineStr"/>
-      <c r="M387" t="inlineStr"/>
-      <c r="N387" t="inlineStr"/>
-      <c r="O387" t="inlineStr"/>
+      <c r="I387" s="0" t="inlineStr"/>
+      <c r="J387" s="0" t="inlineStr"/>
+      <c r="K387" s="0" t="inlineStr"/>
+      <c r="L387" s="0" t="inlineStr"/>
+      <c r="M387" s="0" t="inlineStr"/>
+      <c r="N387" s="0" t="inlineStr"/>
+      <c r="O387" s="0" t="inlineStr"/>
     </row>
     <row r="388" ht="18" customHeight="1" s="72">
       <c r="A388" s="96" t="inlineStr">
@@ -18295,18 +18263,18 @@
           <t>null</t>
         </is>
       </c>
-      <c r="H388" t="inlineStr">
+      <c r="H388" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
       <c r="I388" s="0" t="inlineStr"/>
-      <c r="J388" t="inlineStr"/>
-      <c r="K388" t="inlineStr"/>
-      <c r="L388" t="inlineStr"/>
-      <c r="M388" t="inlineStr"/>
-      <c r="N388" t="inlineStr"/>
-      <c r="O388" t="inlineStr"/>
+      <c r="J388" s="0" t="inlineStr"/>
+      <c r="K388" s="0" t="inlineStr"/>
+      <c r="L388" s="0" t="inlineStr"/>
+      <c r="M388" s="0" t="inlineStr"/>
+      <c r="N388" s="0" t="inlineStr"/>
+      <c r="O388" s="0" t="inlineStr"/>
     </row>
     <row r="389" ht="15" customHeight="1" s="72">
       <c r="A389" s="33" t="inlineStr">
@@ -18799,53 +18767,53 @@
       <c r="O398" s="19" t="inlineStr"/>
     </row>
     <row r="399" ht="9.75" customHeight="1" s="72">
-      <c r="A399" t="inlineStr">
+      <c r="A399" s="0" t="inlineStr">
         <is>
           <t>slot12</t>
         </is>
       </c>
-      <c r="B399" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="C399" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D399" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E399" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F399" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G399" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H399" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="I399" t="inlineStr"/>
-      <c r="J399" t="inlineStr"/>
-      <c r="K399" t="inlineStr"/>
-      <c r="L399" t="inlineStr"/>
-      <c r="M399" t="inlineStr"/>
-      <c r="N399" t="inlineStr"/>
-      <c r="O399" t="inlineStr"/>
+      <c r="B399" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C399" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D399" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E399" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F399" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G399" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H399" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I399" s="0" t="inlineStr"/>
+      <c r="J399" s="0" t="inlineStr"/>
+      <c r="K399" s="0" t="inlineStr"/>
+      <c r="L399" s="0" t="inlineStr"/>
+      <c r="M399" s="0" t="inlineStr"/>
+      <c r="N399" s="0" t="inlineStr"/>
+      <c r="O399" s="0" t="inlineStr"/>
     </row>
     <row r="400" ht="15.75" customHeight="1" s="72">
       <c r="A400" s="88" t="inlineStr">
@@ -18853,48 +18821,48 @@
           <t>slot13</t>
         </is>
       </c>
-      <c r="B400" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="C400" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D400" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E400" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F400" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G400" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H400" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="I400" t="inlineStr"/>
-      <c r="J400" t="inlineStr"/>
-      <c r="K400" t="inlineStr"/>
-      <c r="L400" t="inlineStr"/>
-      <c r="M400" t="inlineStr"/>
-      <c r="N400" t="inlineStr"/>
-      <c r="O400" t="inlineStr"/>
+      <c r="B400" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C400" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D400" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E400" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F400" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G400" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H400" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I400" s="0" t="inlineStr"/>
+      <c r="J400" s="0" t="inlineStr"/>
+      <c r="K400" s="0" t="inlineStr"/>
+      <c r="L400" s="0" t="inlineStr"/>
+      <c r="M400" s="0" t="inlineStr"/>
+      <c r="N400" s="0" t="inlineStr"/>
+      <c r="O400" s="0" t="inlineStr"/>
     </row>
     <row r="401" ht="15" customHeight="1" s="72">
       <c r="A401" s="45" t="inlineStr">
@@ -18961,38 +18929,38 @@
           <t>null</t>
         </is>
       </c>
-      <c r="D402" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E402" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F402" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G402" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H402" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="I402" t="inlineStr"/>
-      <c r="J402" t="inlineStr"/>
-      <c r="K402" t="inlineStr"/>
-      <c r="L402" t="inlineStr"/>
-      <c r="M402" t="inlineStr"/>
-      <c r="N402" t="inlineStr"/>
-      <c r="O402" t="inlineStr"/>
+      <c r="D402" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E402" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F402" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G402" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H402" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I402" s="0" t="inlineStr"/>
+      <c r="J402" s="0" t="inlineStr"/>
+      <c r="K402" s="0" t="inlineStr"/>
+      <c r="L402" s="0" t="inlineStr"/>
+      <c r="M402" s="0" t="inlineStr"/>
+      <c r="N402" s="0" t="inlineStr"/>
+      <c r="O402" s="0" t="inlineStr"/>
     </row>
     <row r="403" ht="18" customHeight="1" s="72">
       <c r="A403" s="92" t="inlineStr">
@@ -19030,18 +18998,18 @@
           <t>null</t>
         </is>
       </c>
-      <c r="H403" t="inlineStr">
+      <c r="H403" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
       <c r="I403" s="0" t="inlineStr"/>
-      <c r="J403" t="inlineStr"/>
-      <c r="K403" t="inlineStr"/>
-      <c r="L403" t="inlineStr"/>
-      <c r="M403" t="inlineStr"/>
-      <c r="N403" t="inlineStr"/>
-      <c r="O403" t="inlineStr"/>
+      <c r="J403" s="0" t="inlineStr"/>
+      <c r="K403" s="0" t="inlineStr"/>
+      <c r="L403" s="0" t="inlineStr"/>
+      <c r="M403" s="0" t="inlineStr"/>
+      <c r="N403" s="0" t="inlineStr"/>
+      <c r="O403" s="0" t="inlineStr"/>
     </row>
     <row r="404" ht="15" customHeight="1" s="72">
       <c r="A404" s="33" t="inlineStr">
@@ -19534,53 +19502,53 @@
       <c r="O413" s="19" t="inlineStr"/>
     </row>
     <row r="414" ht="9.75" customHeight="1" s="72">
-      <c r="A414" t="inlineStr">
+      <c r="A414" s="0" t="inlineStr">
         <is>
           <t>slot27</t>
         </is>
       </c>
-      <c r="B414" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="C414" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D414" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E414" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F414" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G414" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H414" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="I414" t="inlineStr"/>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
-      <c r="N414" t="inlineStr"/>
-      <c r="O414" t="inlineStr"/>
+      <c r="B414" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C414" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D414" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E414" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F414" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G414" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H414" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I414" s="0" t="inlineStr"/>
+      <c r="J414" s="0" t="inlineStr"/>
+      <c r="K414" s="0" t="inlineStr"/>
+      <c r="L414" s="0" t="inlineStr"/>
+      <c r="M414" s="0" t="inlineStr"/>
+      <c r="N414" s="0" t="inlineStr"/>
+      <c r="O414" s="0" t="inlineStr"/>
     </row>
     <row r="415" ht="3.75" customHeight="1" s="72">
       <c r="A415" s="101" t="inlineStr">
@@ -19588,146 +19556,146 @@
           <t>slot28</t>
         </is>
       </c>
-      <c r="B415" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="C415" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E415" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F415" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G415" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H415" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="I415" t="inlineStr"/>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
-      <c r="N415" t="inlineStr"/>
-      <c r="O415" t="inlineStr"/>
+      <c r="B415" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C415" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D415" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E415" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F415" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G415" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H415" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I415" s="0" t="inlineStr"/>
+      <c r="J415" s="0" t="inlineStr"/>
+      <c r="K415" s="0" t="inlineStr"/>
+      <c r="L415" s="0" t="inlineStr"/>
+      <c r="M415" s="0" t="inlineStr"/>
+      <c r="N415" s="0" t="inlineStr"/>
+      <c r="O415" s="0" t="inlineStr"/>
     </row>
     <row r="416" ht="9.75" customHeight="1" s="72">
-      <c r="A416" t="inlineStr">
+      <c r="A416" s="0" t="inlineStr">
         <is>
           <t>slot29</t>
         </is>
       </c>
-      <c r="B416" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="C416" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E416" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F416" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G416" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H416" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="I416" t="inlineStr"/>
-      <c r="J416" t="inlineStr"/>
-      <c r="K416" t="inlineStr"/>
-      <c r="L416" t="inlineStr"/>
-      <c r="M416" t="inlineStr"/>
-      <c r="N416" t="inlineStr"/>
-      <c r="O416" t="inlineStr"/>
+      <c r="B416" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C416" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D416" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E416" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F416" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G416" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H416" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I416" s="0" t="inlineStr"/>
+      <c r="J416" s="0" t="inlineStr"/>
+      <c r="K416" s="0" t="inlineStr"/>
+      <c r="L416" s="0" t="inlineStr"/>
+      <c r="M416" s="0" t="inlineStr"/>
+      <c r="N416" s="0" t="inlineStr"/>
+      <c r="O416" s="0" t="inlineStr"/>
     </row>
     <row r="417" ht="9.75" customHeight="1" s="72">
-      <c r="A417" t="inlineStr">
+      <c r="A417" s="0" t="inlineStr">
         <is>
           <t>slot30</t>
         </is>
       </c>
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="C417" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E417" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F417" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G417" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H417" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="I417" t="inlineStr"/>
-      <c r="J417" t="inlineStr"/>
-      <c r="K417" t="inlineStr"/>
-      <c r="L417" t="inlineStr"/>
-      <c r="M417" t="inlineStr"/>
-      <c r="N417" t="inlineStr"/>
-      <c r="O417" t="inlineStr"/>
+      <c r="B417" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C417" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D417" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E417" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F417" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G417" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H417" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I417" s="0" t="inlineStr"/>
+      <c r="J417" s="0" t="inlineStr"/>
+      <c r="K417" s="0" t="inlineStr"/>
+      <c r="L417" s="0" t="inlineStr"/>
+      <c r="M417" s="0" t="inlineStr"/>
+      <c r="N417" s="0" t="inlineStr"/>
+      <c r="O417" s="0" t="inlineStr"/>
     </row>
     <row r="418" ht="27.75" customHeight="1" s="72">
       <c r="A418" s="102" t="inlineStr">
@@ -21076,20 +21044,20 @@
     </row>
     <row r="448" ht="18" customHeight="1" s="72">
       <c r="A448" s="82" t="inlineStr"/>
-      <c r="B448" t="inlineStr"/>
-      <c r="C448" t="inlineStr"/>
-      <c r="D448" t="inlineStr"/>
-      <c r="E448" t="inlineStr"/>
-      <c r="F448" t="inlineStr"/>
-      <c r="G448" t="inlineStr"/>
-      <c r="H448" t="inlineStr"/>
-      <c r="I448" t="inlineStr"/>
-      <c r="J448" t="inlineStr"/>
-      <c r="K448" t="inlineStr"/>
-      <c r="L448" t="inlineStr"/>
-      <c r="M448" t="inlineStr"/>
-      <c r="N448" t="inlineStr"/>
-      <c r="O448" t="inlineStr"/>
+      <c r="B448" s="0" t="inlineStr"/>
+      <c r="C448" s="0" t="inlineStr"/>
+      <c r="D448" s="0" t="inlineStr"/>
+      <c r="E448" s="0" t="inlineStr"/>
+      <c r="F448" s="0" t="inlineStr"/>
+      <c r="G448" s="0" t="inlineStr"/>
+      <c r="H448" s="0" t="inlineStr"/>
+      <c r="I448" s="0" t="inlineStr"/>
+      <c r="J448" s="0" t="inlineStr"/>
+      <c r="K448" s="0" t="inlineStr"/>
+      <c r="L448" s="0" t="inlineStr"/>
+      <c r="M448" s="0" t="inlineStr"/>
+      <c r="N448" s="0" t="inlineStr"/>
+      <c r="O448" s="0" t="inlineStr"/>
     </row>
     <row r="449" ht="15" customHeight="1" s="72">
       <c r="A449" s="33" t="inlineStr">
@@ -21875,48 +21843,48 @@
           <t>Başlık</t>
         </is>
       </c>
-      <c r="B461" t="inlineStr">
+      <c r="B461" s="0" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="C461" t="inlineStr">
+      <c r="C461" s="0" t="inlineStr">
         <is>
           <t>İçerik / URL</t>
         </is>
       </c>
-      <c r="D461" t="inlineStr">
+      <c r="D461" s="0" t="inlineStr">
         <is>
           <t>Genişlik</t>
         </is>
       </c>
-      <c r="E461" t="inlineStr">
+      <c r="E461" s="0" t="inlineStr">
         <is>
           <t>Yükseklik</t>
         </is>
       </c>
-      <c r="F461" t="inlineStr">
+      <c r="F461" s="0" t="inlineStr">
         <is>
           <t>Caption</t>
         </is>
       </c>
-      <c r="G461" t="inlineStr">
+      <c r="G461" s="0" t="inlineStr">
         <is>
           <t>Extra</t>
         </is>
       </c>
-      <c r="H461" t="inlineStr">
+      <c r="H461" s="0" t="inlineStr">
         <is>
           <t>Kod</t>
         </is>
       </c>
-      <c r="I461" t="inlineStr"/>
-      <c r="J461" t="inlineStr"/>
-      <c r="K461" t="inlineStr"/>
-      <c r="L461" t="inlineStr"/>
-      <c r="M461" t="inlineStr"/>
-      <c r="N461" t="inlineStr"/>
-      <c r="O461" t="inlineStr"/>
+      <c r="I461" s="0" t="inlineStr"/>
+      <c r="J461" s="0" t="inlineStr"/>
+      <c r="K461" s="0" t="inlineStr"/>
+      <c r="L461" s="0" t="inlineStr"/>
+      <c r="M461" s="0" t="inlineStr"/>
+      <c r="N461" s="0" t="inlineStr"/>
+      <c r="O461" s="0" t="inlineStr"/>
     </row>
     <row r="462" ht="15" customHeight="1" s="72">
       <c r="A462" s="39" t="inlineStr">
@@ -21975,22 +21943,22 @@
 * Aksesuarlar örnek gösterim amaçlıdır.</t>
         </is>
       </c>
-      <c r="D463" t="inlineStr"/>
-      <c r="E463" t="inlineStr"/>
-      <c r="F463" t="inlineStr"/>
-      <c r="G463" t="inlineStr"/>
-      <c r="H463" t="inlineStr">
+      <c r="D463" s="0" t="inlineStr"/>
+      <c r="E463" s="0" t="inlineStr"/>
+      <c r="F463" s="0" t="inlineStr"/>
+      <c r="G463" s="0" t="inlineStr"/>
+      <c r="H463" s="0" t="inlineStr">
         <is>
           <t>toggle-1-right</t>
         </is>
       </c>
-      <c r="I463" t="inlineStr"/>
-      <c r="J463" t="inlineStr"/>
-      <c r="K463" t="inlineStr"/>
-      <c r="L463" t="inlineStr"/>
-      <c r="M463" t="inlineStr"/>
-      <c r="N463" t="inlineStr"/>
-      <c r="O463" t="inlineStr"/>
+      <c r="I463" s="0" t="inlineStr"/>
+      <c r="J463" s="0" t="inlineStr"/>
+      <c r="K463" s="0" t="inlineStr"/>
+      <c r="L463" s="0" t="inlineStr"/>
+      <c r="M463" s="0" t="inlineStr"/>
+      <c r="N463" s="0" t="inlineStr"/>
+      <c r="O463" s="0" t="inlineStr"/>
     </row>
     <row r="464" ht="18" customHeight="1" s="72">
       <c r="A464" s="96" t="inlineStr">
@@ -22016,18 +21984,18 @@
       <c r="E464" s="0" t="inlineStr"/>
       <c r="F464" s="0" t="inlineStr"/>
       <c r="G464" s="0" t="inlineStr"/>
-      <c r="H464" t="inlineStr">
+      <c r="H464" s="0" t="inlineStr">
         <is>
           <t>toggle-2-left</t>
         </is>
       </c>
       <c r="I464" s="0" t="inlineStr"/>
-      <c r="J464" t="inlineStr"/>
-      <c r="K464" t="inlineStr"/>
-      <c r="L464" t="inlineStr"/>
-      <c r="M464" t="inlineStr"/>
-      <c r="N464" t="inlineStr"/>
-      <c r="O464" t="inlineStr"/>
+      <c r="J464" s="0" t="inlineStr"/>
+      <c r="K464" s="0" t="inlineStr"/>
+      <c r="L464" s="0" t="inlineStr"/>
+      <c r="M464" s="0" t="inlineStr"/>
+      <c r="N464" s="0" t="inlineStr"/>
+      <c r="O464" s="0" t="inlineStr"/>
     </row>
     <row r="465" ht="15" customHeight="1" s="72">
       <c r="A465" s="33" t="inlineStr">
@@ -22403,53 +22371,53 @@
       <c r="O474" s="19" t="inlineStr"/>
     </row>
     <row r="475" ht="9.75" customHeight="1" s="72">
-      <c r="A475" t="inlineStr">
+      <c r="A475" s="0" t="inlineStr">
         <is>
           <t>slot02</t>
         </is>
       </c>
-      <c r="B475" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="C475" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E475" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F475" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G475" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H475" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="I475" t="inlineStr"/>
-      <c r="J475" t="inlineStr"/>
-      <c r="K475" t="inlineStr"/>
-      <c r="L475" t="inlineStr"/>
-      <c r="M475" t="inlineStr"/>
-      <c r="N475" t="inlineStr"/>
-      <c r="O475" t="inlineStr"/>
+      <c r="B475" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C475" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D475" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E475" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F475" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G475" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H475" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I475" s="0" t="inlineStr"/>
+      <c r="J475" s="0" t="inlineStr"/>
+      <c r="K475" s="0" t="inlineStr"/>
+      <c r="L475" s="0" t="inlineStr"/>
+      <c r="M475" s="0" t="inlineStr"/>
+      <c r="N475" s="0" t="inlineStr"/>
+      <c r="O475" s="0" t="inlineStr"/>
     </row>
     <row r="476" ht="15.75" customHeight="1" s="72">
       <c r="A476" s="88" t="inlineStr">
@@ -22457,48 +22425,48 @@
           <t>slot03</t>
         </is>
       </c>
-      <c r="B476" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="C476" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D476" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E476" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F476" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G476" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H476" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="I476" t="inlineStr"/>
-      <c r="J476" t="inlineStr"/>
-      <c r="K476" t="inlineStr"/>
-      <c r="L476" t="inlineStr"/>
-      <c r="M476" t="inlineStr"/>
-      <c r="N476" t="inlineStr"/>
-      <c r="O476" t="inlineStr"/>
+      <c r="B476" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C476" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D476" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E476" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F476" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G476" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H476" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I476" s="0" t="inlineStr"/>
+      <c r="J476" s="0" t="inlineStr"/>
+      <c r="K476" s="0" t="inlineStr"/>
+      <c r="L476" s="0" t="inlineStr"/>
+      <c r="M476" s="0" t="inlineStr"/>
+      <c r="N476" s="0" t="inlineStr"/>
+      <c r="O476" s="0" t="inlineStr"/>
     </row>
     <row r="477" ht="15" customHeight="1" s="72">
       <c r="A477" s="45" t="inlineStr">
@@ -22565,38 +22533,38 @@
           <t>null</t>
         </is>
       </c>
-      <c r="D478" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E478" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F478" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G478" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H478" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="I478" t="inlineStr"/>
-      <c r="J478" t="inlineStr"/>
-      <c r="K478" t="inlineStr"/>
-      <c r="L478" t="inlineStr"/>
-      <c r="M478" t="inlineStr"/>
-      <c r="N478" t="inlineStr"/>
-      <c r="O478" t="inlineStr"/>
+      <c r="D478" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E478" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F478" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G478" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H478" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I478" s="0" t="inlineStr"/>
+      <c r="J478" s="0" t="inlineStr"/>
+      <c r="K478" s="0" t="inlineStr"/>
+      <c r="L478" s="0" t="inlineStr"/>
+      <c r="M478" s="0" t="inlineStr"/>
+      <c r="N478" s="0" t="inlineStr"/>
+      <c r="O478" s="0" t="inlineStr"/>
     </row>
     <row r="479" ht="18" customHeight="1" s="72">
       <c r="A479" s="92" t="inlineStr">
@@ -22634,18 +22602,18 @@
           <t>null</t>
         </is>
       </c>
-      <c r="H479" t="inlineStr">
+      <c r="H479" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
       <c r="I479" s="0" t="inlineStr"/>
-      <c r="J479" t="inlineStr"/>
-      <c r="K479" t="inlineStr"/>
-      <c r="L479" t="inlineStr"/>
-      <c r="M479" t="inlineStr"/>
-      <c r="N479" t="inlineStr"/>
-      <c r="O479" t="inlineStr"/>
+      <c r="J479" s="0" t="inlineStr"/>
+      <c r="K479" s="0" t="inlineStr"/>
+      <c r="L479" s="0" t="inlineStr"/>
+      <c r="M479" s="0" t="inlineStr"/>
+      <c r="N479" s="0" t="inlineStr"/>
+      <c r="O479" s="0" t="inlineStr"/>
     </row>
     <row r="480" ht="15" customHeight="1" s="72">
       <c r="A480" s="33" t="inlineStr">
@@ -23138,53 +23106,53 @@
       <c r="O489" s="19" t="inlineStr"/>
     </row>
     <row r="490" ht="9.75" customHeight="1" s="72">
-      <c r="A490" t="inlineStr">
+      <c r="A490" s="0" t="inlineStr">
         <is>
           <t>slot17</t>
         </is>
       </c>
-      <c r="B490" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="C490" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D490" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E490" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F490" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G490" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H490" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="I490" t="inlineStr"/>
-      <c r="J490" t="inlineStr"/>
-      <c r="K490" t="inlineStr"/>
-      <c r="L490" t="inlineStr"/>
-      <c r="M490" t="inlineStr"/>
-      <c r="N490" t="inlineStr"/>
-      <c r="O490" t="inlineStr"/>
+      <c r="B490" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C490" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D490" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E490" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F490" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G490" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H490" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I490" s="0" t="inlineStr"/>
+      <c r="J490" s="0" t="inlineStr"/>
+      <c r="K490" s="0" t="inlineStr"/>
+      <c r="L490" s="0" t="inlineStr"/>
+      <c r="M490" s="0" t="inlineStr"/>
+      <c r="N490" s="0" t="inlineStr"/>
+      <c r="O490" s="0" t="inlineStr"/>
     </row>
     <row r="491" ht="15.75" customHeight="1" s="72">
       <c r="A491" s="84" t="inlineStr">
@@ -23192,48 +23160,48 @@
           <t>slot18</t>
         </is>
       </c>
-      <c r="B491" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="C491" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D491" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E491" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F491" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G491" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H491" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="I491" t="inlineStr"/>
-      <c r="J491" t="inlineStr"/>
-      <c r="K491" t="inlineStr"/>
-      <c r="L491" t="inlineStr"/>
-      <c r="M491" t="inlineStr"/>
-      <c r="N491" t="inlineStr"/>
-      <c r="O491" t="inlineStr"/>
+      <c r="B491" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C491" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D491" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E491" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F491" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G491" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H491" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I491" s="0" t="inlineStr"/>
+      <c r="J491" s="0" t="inlineStr"/>
+      <c r="K491" s="0" t="inlineStr"/>
+      <c r="L491" s="0" t="inlineStr"/>
+      <c r="M491" s="0" t="inlineStr"/>
+      <c r="N491" s="0" t="inlineStr"/>
+      <c r="O491" s="0" t="inlineStr"/>
     </row>
     <row r="492" ht="15" customHeight="1" s="72">
       <c r="A492" s="39" t="inlineStr">
@@ -23300,38 +23268,38 @@
           <t>null</t>
         </is>
       </c>
-      <c r="D493" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E493" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F493" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G493" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H493" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="I493" t="inlineStr"/>
-      <c r="J493" t="inlineStr"/>
-      <c r="K493" t="inlineStr"/>
-      <c r="L493" t="inlineStr"/>
-      <c r="M493" t="inlineStr"/>
-      <c r="N493" t="inlineStr"/>
-      <c r="O493" t="inlineStr"/>
+      <c r="D493" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E493" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F493" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G493" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H493" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I493" s="0" t="inlineStr"/>
+      <c r="J493" s="0" t="inlineStr"/>
+      <c r="K493" s="0" t="inlineStr"/>
+      <c r="L493" s="0" t="inlineStr"/>
+      <c r="M493" s="0" t="inlineStr"/>
+      <c r="N493" s="0" t="inlineStr"/>
+      <c r="O493" s="0" t="inlineStr"/>
     </row>
     <row r="494" ht="18" customHeight="1" s="72">
       <c r="A494" s="96" t="inlineStr">
@@ -23369,18 +23337,18 @@
           <t>null</t>
         </is>
       </c>
-      <c r="H494" t="inlineStr">
+      <c r="H494" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
       <c r="I494" s="0" t="inlineStr"/>
-      <c r="J494" t="inlineStr"/>
-      <c r="K494" t="inlineStr"/>
-      <c r="L494" t="inlineStr"/>
-      <c r="M494" t="inlineStr"/>
-      <c r="N494" t="inlineStr"/>
-      <c r="O494" t="inlineStr"/>
+      <c r="J494" s="0" t="inlineStr"/>
+      <c r="K494" s="0" t="inlineStr"/>
+      <c r="L494" s="0" t="inlineStr"/>
+      <c r="M494" s="0" t="inlineStr"/>
+      <c r="N494" s="0" t="inlineStr"/>
+      <c r="O494" s="0" t="inlineStr"/>
     </row>
     <row r="495" ht="15" customHeight="1" s="72">
       <c r="A495" s="33" t="inlineStr">
@@ -23841,38 +23809,38 @@
       <c r="O504" s="19" t="inlineStr"/>
     </row>
     <row r="505" ht="9.75" customHeight="1" s="72">
-      <c r="A505" t="inlineStr"/>
-      <c r="B505" t="inlineStr"/>
-      <c r="C505" t="inlineStr"/>
-      <c r="D505" t="inlineStr"/>
-      <c r="E505" t="inlineStr"/>
-      <c r="F505" t="inlineStr"/>
-      <c r="G505" t="inlineStr"/>
-      <c r="H505" t="inlineStr"/>
-      <c r="I505" t="inlineStr"/>
-      <c r="J505" t="inlineStr"/>
-      <c r="K505" t="inlineStr"/>
-      <c r="L505" t="inlineStr"/>
-      <c r="M505" t="inlineStr"/>
-      <c r="N505" t="inlineStr"/>
-      <c r="O505" t="inlineStr"/>
+      <c r="A505" s="0" t="inlineStr"/>
+      <c r="B505" s="0" t="inlineStr"/>
+      <c r="C505" s="0" t="inlineStr"/>
+      <c r="D505" s="0" t="inlineStr"/>
+      <c r="E505" s="0" t="inlineStr"/>
+      <c r="F505" s="0" t="inlineStr"/>
+      <c r="G505" s="0" t="inlineStr"/>
+      <c r="H505" s="0" t="inlineStr"/>
+      <c r="I505" s="0" t="inlineStr"/>
+      <c r="J505" s="0" t="inlineStr"/>
+      <c r="K505" s="0" t="inlineStr"/>
+      <c r="L505" s="0" t="inlineStr"/>
+      <c r="M505" s="0" t="inlineStr"/>
+      <c r="N505" s="0" t="inlineStr"/>
+      <c r="O505" s="0" t="inlineStr"/>
     </row>
     <row r="506" ht="15.75" customHeight="1" s="72">
       <c r="A506" s="88" t="inlineStr"/>
-      <c r="B506" t="inlineStr"/>
-      <c r="C506" t="inlineStr"/>
-      <c r="D506" t="inlineStr"/>
-      <c r="E506" t="inlineStr"/>
-      <c r="F506" t="inlineStr"/>
-      <c r="G506" t="inlineStr"/>
-      <c r="H506" t="inlineStr"/>
-      <c r="I506" t="inlineStr"/>
-      <c r="J506" t="inlineStr"/>
-      <c r="K506" t="inlineStr"/>
-      <c r="L506" t="inlineStr"/>
-      <c r="M506" t="inlineStr"/>
-      <c r="N506" t="inlineStr"/>
-      <c r="O506" t="inlineStr"/>
+      <c r="B506" s="0" t="inlineStr"/>
+      <c r="C506" s="0" t="inlineStr"/>
+      <c r="D506" s="0" t="inlineStr"/>
+      <c r="E506" s="0" t="inlineStr"/>
+      <c r="F506" s="0" t="inlineStr"/>
+      <c r="G506" s="0" t="inlineStr"/>
+      <c r="H506" s="0" t="inlineStr"/>
+      <c r="I506" s="0" t="inlineStr"/>
+      <c r="J506" s="0" t="inlineStr"/>
+      <c r="K506" s="0" t="inlineStr"/>
+      <c r="L506" s="0" t="inlineStr"/>
+      <c r="M506" s="0" t="inlineStr"/>
+      <c r="N506" s="0" t="inlineStr"/>
+      <c r="O506" s="0" t="inlineStr"/>
     </row>
     <row r="507" ht="15" customHeight="1" s="72">
       <c r="A507" s="45" t="inlineStr"/>
@@ -23895,18 +23863,18 @@
       <c r="A508" s="46" t="inlineStr"/>
       <c r="B508" s="89" t="inlineStr"/>
       <c r="C508" s="0" t="inlineStr"/>
-      <c r="D508" t="inlineStr"/>
-      <c r="E508" t="inlineStr"/>
-      <c r="F508" t="inlineStr"/>
-      <c r="G508" t="inlineStr"/>
-      <c r="H508" t="inlineStr"/>
-      <c r="I508" t="inlineStr"/>
-      <c r="J508" t="inlineStr"/>
-      <c r="K508" t="inlineStr"/>
-      <c r="L508" t="inlineStr"/>
-      <c r="M508" t="inlineStr"/>
-      <c r="N508" t="inlineStr"/>
-      <c r="O508" t="inlineStr"/>
+      <c r="D508" s="0" t="inlineStr"/>
+      <c r="E508" s="0" t="inlineStr"/>
+      <c r="F508" s="0" t="inlineStr"/>
+      <c r="G508" s="0" t="inlineStr"/>
+      <c r="H508" s="0" t="inlineStr"/>
+      <c r="I508" s="0" t="inlineStr"/>
+      <c r="J508" s="0" t="inlineStr"/>
+      <c r="K508" s="0" t="inlineStr"/>
+      <c r="L508" s="0" t="inlineStr"/>
+      <c r="M508" s="0" t="inlineStr"/>
+      <c r="N508" s="0" t="inlineStr"/>
+      <c r="O508" s="0" t="inlineStr"/>
     </row>
     <row r="509" ht="18" customHeight="1" s="72">
       <c r="A509" s="92" t="inlineStr"/>
@@ -23916,14 +23884,14 @@
       <c r="E509" s="0" t="inlineStr"/>
       <c r="F509" s="0" t="inlineStr"/>
       <c r="G509" s="0" t="inlineStr"/>
-      <c r="H509" t="inlineStr"/>
+      <c r="H509" s="0" t="inlineStr"/>
       <c r="I509" s="0" t="inlineStr"/>
-      <c r="J509" t="inlineStr"/>
-      <c r="K509" t="inlineStr"/>
-      <c r="L509" t="inlineStr"/>
-      <c r="M509" t="inlineStr"/>
-      <c r="N509" t="inlineStr"/>
-      <c r="O509" t="inlineStr"/>
+      <c r="J509" s="0" t="inlineStr"/>
+      <c r="K509" s="0" t="inlineStr"/>
+      <c r="L509" s="0" t="inlineStr"/>
+      <c r="M509" s="0" t="inlineStr"/>
+      <c r="N509" s="0" t="inlineStr"/>
+      <c r="O509" s="0" t="inlineStr"/>
     </row>
     <row r="510" ht="15" customHeight="1" s="72">
       <c r="A510" s="33" t="inlineStr"/>
@@ -24096,38 +24064,38 @@
       <c r="O519" s="19" t="inlineStr"/>
     </row>
     <row r="520" ht="9.75" customHeight="1" s="72">
-      <c r="A520" t="inlineStr"/>
-      <c r="B520" t="inlineStr"/>
-      <c r="C520" t="inlineStr"/>
-      <c r="D520" t="inlineStr"/>
-      <c r="E520" t="inlineStr"/>
-      <c r="F520" t="inlineStr"/>
-      <c r="G520" t="inlineStr"/>
-      <c r="H520" t="inlineStr"/>
-      <c r="I520" t="inlineStr"/>
-      <c r="J520" t="inlineStr"/>
-      <c r="K520" t="inlineStr"/>
-      <c r="L520" t="inlineStr"/>
-      <c r="M520" t="inlineStr"/>
-      <c r="N520" t="inlineStr"/>
-      <c r="O520" t="inlineStr"/>
+      <c r="A520" s="0" t="inlineStr"/>
+      <c r="B520" s="0" t="inlineStr"/>
+      <c r="C520" s="0" t="inlineStr"/>
+      <c r="D520" s="0" t="inlineStr"/>
+      <c r="E520" s="0" t="inlineStr"/>
+      <c r="F520" s="0" t="inlineStr"/>
+      <c r="G520" s="0" t="inlineStr"/>
+      <c r="H520" s="0" t="inlineStr"/>
+      <c r="I520" s="0" t="inlineStr"/>
+      <c r="J520" s="0" t="inlineStr"/>
+      <c r="K520" s="0" t="inlineStr"/>
+      <c r="L520" s="0" t="inlineStr"/>
+      <c r="M520" s="0" t="inlineStr"/>
+      <c r="N520" s="0" t="inlineStr"/>
+      <c r="O520" s="0" t="inlineStr"/>
     </row>
     <row r="521" ht="15.75" customHeight="1" s="72">
       <c r="A521" s="84" t="inlineStr"/>
-      <c r="B521" t="inlineStr"/>
-      <c r="C521" t="inlineStr"/>
-      <c r="D521" t="inlineStr"/>
-      <c r="E521" t="inlineStr"/>
-      <c r="F521" t="inlineStr"/>
-      <c r="G521" t="inlineStr"/>
-      <c r="H521" t="inlineStr"/>
-      <c r="I521" t="inlineStr"/>
-      <c r="J521" t="inlineStr"/>
-      <c r="K521" t="inlineStr"/>
-      <c r="L521" t="inlineStr"/>
-      <c r="M521" t="inlineStr"/>
-      <c r="N521" t="inlineStr"/>
-      <c r="O521" t="inlineStr"/>
+      <c r="B521" s="0" t="inlineStr"/>
+      <c r="C521" s="0" t="inlineStr"/>
+      <c r="D521" s="0" t="inlineStr"/>
+      <c r="E521" s="0" t="inlineStr"/>
+      <c r="F521" s="0" t="inlineStr"/>
+      <c r="G521" s="0" t="inlineStr"/>
+      <c r="H521" s="0" t="inlineStr"/>
+      <c r="I521" s="0" t="inlineStr"/>
+      <c r="J521" s="0" t="inlineStr"/>
+      <c r="K521" s="0" t="inlineStr"/>
+      <c r="L521" s="0" t="inlineStr"/>
+      <c r="M521" s="0" t="inlineStr"/>
+      <c r="N521" s="0" t="inlineStr"/>
+      <c r="O521" s="0" t="inlineStr"/>
     </row>
     <row r="522" ht="15" customHeight="1" s="72">
       <c r="A522" s="39" t="inlineStr"/>
@@ -24150,18 +24118,18 @@
       <c r="A523" s="58" t="inlineStr"/>
       <c r="B523" s="95" t="inlineStr"/>
       <c r="C523" s="0" t="inlineStr"/>
-      <c r="D523" t="inlineStr"/>
-      <c r="E523" t="inlineStr"/>
-      <c r="F523" t="inlineStr"/>
-      <c r="G523" t="inlineStr"/>
-      <c r="H523" t="inlineStr"/>
-      <c r="I523" t="inlineStr"/>
-      <c r="J523" t="inlineStr"/>
-      <c r="K523" t="inlineStr"/>
-      <c r="L523" t="inlineStr"/>
-      <c r="M523" t="inlineStr"/>
-      <c r="N523" t="inlineStr"/>
-      <c r="O523" t="inlineStr"/>
+      <c r="D523" s="0" t="inlineStr"/>
+      <c r="E523" s="0" t="inlineStr"/>
+      <c r="F523" s="0" t="inlineStr"/>
+      <c r="G523" s="0" t="inlineStr"/>
+      <c r="H523" s="0" t="inlineStr"/>
+      <c r="I523" s="0" t="inlineStr"/>
+      <c r="J523" s="0" t="inlineStr"/>
+      <c r="K523" s="0" t="inlineStr"/>
+      <c r="L523" s="0" t="inlineStr"/>
+      <c r="M523" s="0" t="inlineStr"/>
+      <c r="N523" s="0" t="inlineStr"/>
+      <c r="O523" s="0" t="inlineStr"/>
     </row>
     <row r="524" ht="18" customHeight="1" s="72">
       <c r="A524" s="96" t="inlineStr"/>
@@ -24171,14 +24139,14 @@
       <c r="E524" s="0" t="inlineStr"/>
       <c r="F524" s="0" t="inlineStr"/>
       <c r="G524" s="0" t="inlineStr"/>
-      <c r="H524" t="inlineStr"/>
+      <c r="H524" s="0" t="inlineStr"/>
       <c r="I524" s="0" t="inlineStr"/>
-      <c r="J524" t="inlineStr"/>
-      <c r="K524" t="inlineStr"/>
-      <c r="L524" t="inlineStr"/>
-      <c r="M524" t="inlineStr"/>
-      <c r="N524" t="inlineStr"/>
-      <c r="O524" t="inlineStr"/>
+      <c r="J524" s="0" t="inlineStr"/>
+      <c r="K524" s="0" t="inlineStr"/>
+      <c r="L524" s="0" t="inlineStr"/>
+      <c r="M524" s="0" t="inlineStr"/>
+      <c r="N524" s="0" t="inlineStr"/>
+      <c r="O524" s="0" t="inlineStr"/>
     </row>
     <row r="525" ht="15" customHeight="1" s="72">
       <c r="A525" s="33" t="inlineStr"/>
@@ -24351,38 +24319,38 @@
       <c r="O534" s="19" t="inlineStr"/>
     </row>
     <row r="535" ht="9.75" customHeight="1" s="72">
-      <c r="A535" t="inlineStr"/>
-      <c r="B535" t="inlineStr"/>
-      <c r="C535" t="inlineStr"/>
-      <c r="D535" t="inlineStr"/>
-      <c r="E535" t="inlineStr"/>
-      <c r="F535" t="inlineStr"/>
-      <c r="G535" t="inlineStr"/>
-      <c r="H535" t="inlineStr"/>
-      <c r="I535" t="inlineStr"/>
-      <c r="J535" t="inlineStr"/>
-      <c r="K535" t="inlineStr"/>
-      <c r="L535" t="inlineStr"/>
-      <c r="M535" t="inlineStr"/>
-      <c r="N535" t="inlineStr"/>
-      <c r="O535" t="inlineStr"/>
+      <c r="A535" s="0" t="inlineStr"/>
+      <c r="B535" s="0" t="inlineStr"/>
+      <c r="C535" s="0" t="inlineStr"/>
+      <c r="D535" s="0" t="inlineStr"/>
+      <c r="E535" s="0" t="inlineStr"/>
+      <c r="F535" s="0" t="inlineStr"/>
+      <c r="G535" s="0" t="inlineStr"/>
+      <c r="H535" s="0" t="inlineStr"/>
+      <c r="I535" s="0" t="inlineStr"/>
+      <c r="J535" s="0" t="inlineStr"/>
+      <c r="K535" s="0" t="inlineStr"/>
+      <c r="L535" s="0" t="inlineStr"/>
+      <c r="M535" s="0" t="inlineStr"/>
+      <c r="N535" s="0" t="inlineStr"/>
+      <c r="O535" s="0" t="inlineStr"/>
     </row>
     <row r="536" ht="15.75" customHeight="1" s="72">
       <c r="A536" s="88" t="inlineStr"/>
-      <c r="B536" t="inlineStr"/>
-      <c r="C536" t="inlineStr"/>
-      <c r="D536" t="inlineStr"/>
-      <c r="E536" t="inlineStr"/>
-      <c r="F536" t="inlineStr"/>
-      <c r="G536" t="inlineStr"/>
-      <c r="H536" t="inlineStr"/>
-      <c r="I536" t="inlineStr"/>
-      <c r="J536" t="inlineStr"/>
-      <c r="K536" t="inlineStr"/>
-      <c r="L536" t="inlineStr"/>
-      <c r="M536" t="inlineStr"/>
-      <c r="N536" t="inlineStr"/>
-      <c r="O536" t="inlineStr"/>
+      <c r="B536" s="0" t="inlineStr"/>
+      <c r="C536" s="0" t="inlineStr"/>
+      <c r="D536" s="0" t="inlineStr"/>
+      <c r="E536" s="0" t="inlineStr"/>
+      <c r="F536" s="0" t="inlineStr"/>
+      <c r="G536" s="0" t="inlineStr"/>
+      <c r="H536" s="0" t="inlineStr"/>
+      <c r="I536" s="0" t="inlineStr"/>
+      <c r="J536" s="0" t="inlineStr"/>
+      <c r="K536" s="0" t="inlineStr"/>
+      <c r="L536" s="0" t="inlineStr"/>
+      <c r="M536" s="0" t="inlineStr"/>
+      <c r="N536" s="0" t="inlineStr"/>
+      <c r="O536" s="0" t="inlineStr"/>
     </row>
     <row r="537" ht="15" customHeight="1" s="72">
       <c r="A537" s="45" t="inlineStr"/>
@@ -24405,18 +24373,18 @@
       <c r="A538" s="46" t="inlineStr"/>
       <c r="B538" s="89" t="inlineStr"/>
       <c r="C538" s="0" t="inlineStr"/>
-      <c r="D538" t="inlineStr"/>
-      <c r="E538" t="inlineStr"/>
-      <c r="F538" t="inlineStr"/>
-      <c r="G538" t="inlineStr"/>
-      <c r="H538" t="inlineStr"/>
-      <c r="I538" t="inlineStr"/>
-      <c r="J538" t="inlineStr"/>
-      <c r="K538" t="inlineStr"/>
-      <c r="L538" t="inlineStr"/>
-      <c r="M538" t="inlineStr"/>
-      <c r="N538" t="inlineStr"/>
-      <c r="O538" t="inlineStr"/>
+      <c r="D538" s="0" t="inlineStr"/>
+      <c r="E538" s="0" t="inlineStr"/>
+      <c r="F538" s="0" t="inlineStr"/>
+      <c r="G538" s="0" t="inlineStr"/>
+      <c r="H538" s="0" t="inlineStr"/>
+      <c r="I538" s="0" t="inlineStr"/>
+      <c r="J538" s="0" t="inlineStr"/>
+      <c r="K538" s="0" t="inlineStr"/>
+      <c r="L538" s="0" t="inlineStr"/>
+      <c r="M538" s="0" t="inlineStr"/>
+      <c r="N538" s="0" t="inlineStr"/>
+      <c r="O538" s="0" t="inlineStr"/>
     </row>
     <row r="539" ht="18" customHeight="1" s="72">
       <c r="A539" s="92" t="inlineStr"/>
@@ -24426,14 +24394,14 @@
       <c r="E539" s="0" t="inlineStr"/>
       <c r="F539" s="0" t="inlineStr"/>
       <c r="G539" s="0" t="inlineStr"/>
-      <c r="H539" t="inlineStr"/>
+      <c r="H539" s="0" t="inlineStr"/>
       <c r="I539" s="0" t="inlineStr"/>
-      <c r="J539" t="inlineStr"/>
-      <c r="K539" t="inlineStr"/>
-      <c r="L539" t="inlineStr"/>
-      <c r="M539" t="inlineStr"/>
-      <c r="N539" t="inlineStr"/>
-      <c r="O539" t="inlineStr"/>
+      <c r="J539" s="0" t="inlineStr"/>
+      <c r="K539" s="0" t="inlineStr"/>
+      <c r="L539" s="0" t="inlineStr"/>
+      <c r="M539" s="0" t="inlineStr"/>
+      <c r="N539" s="0" t="inlineStr"/>
+      <c r="O539" s="0" t="inlineStr"/>
     </row>
     <row r="540" ht="15" customHeight="1" s="72">
       <c r="A540" s="33" t="inlineStr"/>
@@ -24606,38 +24574,38 @@
       <c r="O549" s="19" t="inlineStr"/>
     </row>
     <row r="550" ht="9.75" customHeight="1" s="72">
-      <c r="A550" t="inlineStr"/>
-      <c r="B550" t="inlineStr"/>
-      <c r="C550" t="inlineStr"/>
-      <c r="D550" t="inlineStr"/>
-      <c r="E550" t="inlineStr"/>
-      <c r="F550" t="inlineStr"/>
-      <c r="G550" t="inlineStr"/>
-      <c r="H550" t="inlineStr"/>
-      <c r="I550" t="inlineStr"/>
-      <c r="J550" t="inlineStr"/>
-      <c r="K550" t="inlineStr"/>
-      <c r="L550" t="inlineStr"/>
-      <c r="M550" t="inlineStr"/>
-      <c r="N550" t="inlineStr"/>
-      <c r="O550" t="inlineStr"/>
+      <c r="A550" s="0" t="inlineStr"/>
+      <c r="B550" s="0" t="inlineStr"/>
+      <c r="C550" s="0" t="inlineStr"/>
+      <c r="D550" s="0" t="inlineStr"/>
+      <c r="E550" s="0" t="inlineStr"/>
+      <c r="F550" s="0" t="inlineStr"/>
+      <c r="G550" s="0" t="inlineStr"/>
+      <c r="H550" s="0" t="inlineStr"/>
+      <c r="I550" s="0" t="inlineStr"/>
+      <c r="J550" s="0" t="inlineStr"/>
+      <c r="K550" s="0" t="inlineStr"/>
+      <c r="L550" s="0" t="inlineStr"/>
+      <c r="M550" s="0" t="inlineStr"/>
+      <c r="N550" s="0" t="inlineStr"/>
+      <c r="O550" s="0" t="inlineStr"/>
     </row>
     <row r="551" ht="15.75" customHeight="1" s="72">
       <c r="A551" s="84" t="inlineStr"/>
-      <c r="B551" t="inlineStr"/>
-      <c r="C551" t="inlineStr"/>
-      <c r="D551" t="inlineStr"/>
-      <c r="E551" t="inlineStr"/>
-      <c r="F551" t="inlineStr"/>
-      <c r="G551" t="inlineStr"/>
-      <c r="H551" t="inlineStr"/>
-      <c r="I551" t="inlineStr"/>
-      <c r="J551" t="inlineStr"/>
-      <c r="K551" t="inlineStr"/>
-      <c r="L551" t="inlineStr"/>
-      <c r="M551" t="inlineStr"/>
-      <c r="N551" t="inlineStr"/>
-      <c r="O551" t="inlineStr"/>
+      <c r="B551" s="0" t="inlineStr"/>
+      <c r="C551" s="0" t="inlineStr"/>
+      <c r="D551" s="0" t="inlineStr"/>
+      <c r="E551" s="0" t="inlineStr"/>
+      <c r="F551" s="0" t="inlineStr"/>
+      <c r="G551" s="0" t="inlineStr"/>
+      <c r="H551" s="0" t="inlineStr"/>
+      <c r="I551" s="0" t="inlineStr"/>
+      <c r="J551" s="0" t="inlineStr"/>
+      <c r="K551" s="0" t="inlineStr"/>
+      <c r="L551" s="0" t="inlineStr"/>
+      <c r="M551" s="0" t="inlineStr"/>
+      <c r="N551" s="0" t="inlineStr"/>
+      <c r="O551" s="0" t="inlineStr"/>
     </row>
     <row r="552" ht="15" customHeight="1" s="72">
       <c r="A552" s="39" t="inlineStr"/>
@@ -24660,18 +24628,18 @@
       <c r="A553" s="58" t="inlineStr"/>
       <c r="B553" s="95" t="inlineStr"/>
       <c r="C553" s="0" t="inlineStr"/>
-      <c r="D553" t="inlineStr"/>
-      <c r="E553" t="inlineStr"/>
-      <c r="F553" t="inlineStr"/>
-      <c r="G553" t="inlineStr"/>
-      <c r="H553" t="inlineStr"/>
-      <c r="I553" t="inlineStr"/>
-      <c r="J553" t="inlineStr"/>
-      <c r="K553" t="inlineStr"/>
-      <c r="L553" t="inlineStr"/>
-      <c r="M553" t="inlineStr"/>
-      <c r="N553" t="inlineStr"/>
-      <c r="O553" t="inlineStr"/>
+      <c r="D553" s="0" t="inlineStr"/>
+      <c r="E553" s="0" t="inlineStr"/>
+      <c r="F553" s="0" t="inlineStr"/>
+      <c r="G553" s="0" t="inlineStr"/>
+      <c r="H553" s="0" t="inlineStr"/>
+      <c r="I553" s="0" t="inlineStr"/>
+      <c r="J553" s="0" t="inlineStr"/>
+      <c r="K553" s="0" t="inlineStr"/>
+      <c r="L553" s="0" t="inlineStr"/>
+      <c r="M553" s="0" t="inlineStr"/>
+      <c r="N553" s="0" t="inlineStr"/>
+      <c r="O553" s="0" t="inlineStr"/>
     </row>
     <row r="554" ht="18" customHeight="1" s="72">
       <c r="A554" s="96" t="inlineStr"/>
@@ -24681,14 +24649,14 @@
       <c r="E554" s="0" t="inlineStr"/>
       <c r="F554" s="0" t="inlineStr"/>
       <c r="G554" s="0" t="inlineStr"/>
-      <c r="H554" t="inlineStr"/>
+      <c r="H554" s="0" t="inlineStr"/>
       <c r="I554" s="0" t="inlineStr"/>
-      <c r="J554" t="inlineStr"/>
-      <c r="K554" t="inlineStr"/>
-      <c r="L554" t="inlineStr"/>
-      <c r="M554" t="inlineStr"/>
-      <c r="N554" t="inlineStr"/>
-      <c r="O554" t="inlineStr"/>
+      <c r="J554" s="0" t="inlineStr"/>
+      <c r="K554" s="0" t="inlineStr"/>
+      <c r="L554" s="0" t="inlineStr"/>
+      <c r="M554" s="0" t="inlineStr"/>
+      <c r="N554" s="0" t="inlineStr"/>
+      <c r="O554" s="0" t="inlineStr"/>
     </row>
     <row r="555" ht="15" customHeight="1" s="72">
       <c r="A555" s="33" t="inlineStr"/>
@@ -24861,38 +24829,38 @@
       <c r="O564" s="19" t="inlineStr"/>
     </row>
     <row r="565" ht="9.75" customHeight="1" s="72">
-      <c r="A565" t="inlineStr"/>
-      <c r="B565" t="inlineStr"/>
-      <c r="C565" t="inlineStr"/>
-      <c r="D565" t="inlineStr"/>
-      <c r="E565" t="inlineStr"/>
-      <c r="F565" t="inlineStr"/>
-      <c r="G565" t="inlineStr"/>
-      <c r="H565" t="inlineStr"/>
-      <c r="I565" t="inlineStr"/>
-      <c r="J565" t="inlineStr"/>
-      <c r="K565" t="inlineStr"/>
-      <c r="L565" t="inlineStr"/>
-      <c r="M565" t="inlineStr"/>
-      <c r="N565" t="inlineStr"/>
-      <c r="O565" t="inlineStr"/>
+      <c r="A565" s="0" t="inlineStr"/>
+      <c r="B565" s="0" t="inlineStr"/>
+      <c r="C565" s="0" t="inlineStr"/>
+      <c r="D565" s="0" t="inlineStr"/>
+      <c r="E565" s="0" t="inlineStr"/>
+      <c r="F565" s="0" t="inlineStr"/>
+      <c r="G565" s="0" t="inlineStr"/>
+      <c r="H565" s="0" t="inlineStr"/>
+      <c r="I565" s="0" t="inlineStr"/>
+      <c r="J565" s="0" t="inlineStr"/>
+      <c r="K565" s="0" t="inlineStr"/>
+      <c r="L565" s="0" t="inlineStr"/>
+      <c r="M565" s="0" t="inlineStr"/>
+      <c r="N565" s="0" t="inlineStr"/>
+      <c r="O565" s="0" t="inlineStr"/>
     </row>
     <row r="566" ht="15.75" customHeight="1" s="72">
       <c r="A566" s="88" t="inlineStr"/>
-      <c r="B566" t="inlineStr"/>
-      <c r="C566" t="inlineStr"/>
-      <c r="D566" t="inlineStr"/>
-      <c r="E566" t="inlineStr"/>
-      <c r="F566" t="inlineStr"/>
-      <c r="G566" t="inlineStr"/>
-      <c r="H566" t="inlineStr"/>
-      <c r="I566" t="inlineStr"/>
-      <c r="J566" t="inlineStr"/>
-      <c r="K566" t="inlineStr"/>
-      <c r="L566" t="inlineStr"/>
-      <c r="M566" t="inlineStr"/>
-      <c r="N566" t="inlineStr"/>
-      <c r="O566" t="inlineStr"/>
+      <c r="B566" s="0" t="inlineStr"/>
+      <c r="C566" s="0" t="inlineStr"/>
+      <c r="D566" s="0" t="inlineStr"/>
+      <c r="E566" s="0" t="inlineStr"/>
+      <c r="F566" s="0" t="inlineStr"/>
+      <c r="G566" s="0" t="inlineStr"/>
+      <c r="H566" s="0" t="inlineStr"/>
+      <c r="I566" s="0" t="inlineStr"/>
+      <c r="J566" s="0" t="inlineStr"/>
+      <c r="K566" s="0" t="inlineStr"/>
+      <c r="L566" s="0" t="inlineStr"/>
+      <c r="M566" s="0" t="inlineStr"/>
+      <c r="N566" s="0" t="inlineStr"/>
+      <c r="O566" s="0" t="inlineStr"/>
     </row>
     <row r="567" ht="15" customHeight="1" s="72">
       <c r="A567" s="45" t="inlineStr"/>
@@ -24915,18 +24883,18 @@
       <c r="A568" s="46" t="inlineStr"/>
       <c r="B568" s="89" t="inlineStr"/>
       <c r="C568" s="0" t="inlineStr"/>
-      <c r="D568" t="inlineStr"/>
-      <c r="E568" t="inlineStr"/>
-      <c r="F568" t="inlineStr"/>
-      <c r="G568" t="inlineStr"/>
-      <c r="H568" t="inlineStr"/>
-      <c r="I568" t="inlineStr"/>
-      <c r="J568" t="inlineStr"/>
-      <c r="K568" t="inlineStr"/>
-      <c r="L568" t="inlineStr"/>
-      <c r="M568" t="inlineStr"/>
-      <c r="N568" t="inlineStr"/>
-      <c r="O568" t="inlineStr"/>
+      <c r="D568" s="0" t="inlineStr"/>
+      <c r="E568" s="0" t="inlineStr"/>
+      <c r="F568" s="0" t="inlineStr"/>
+      <c r="G568" s="0" t="inlineStr"/>
+      <c r="H568" s="0" t="inlineStr"/>
+      <c r="I568" s="0" t="inlineStr"/>
+      <c r="J568" s="0" t="inlineStr"/>
+      <c r="K568" s="0" t="inlineStr"/>
+      <c r="L568" s="0" t="inlineStr"/>
+      <c r="M568" s="0" t="inlineStr"/>
+      <c r="N568" s="0" t="inlineStr"/>
+      <c r="O568" s="0" t="inlineStr"/>
     </row>
     <row r="569" ht="18" customHeight="1" s="72">
       <c r="A569" s="92" t="inlineStr"/>
@@ -24936,14 +24904,14 @@
       <c r="E569" s="0" t="inlineStr"/>
       <c r="F569" s="0" t="inlineStr"/>
       <c r="G569" s="0" t="inlineStr"/>
-      <c r="H569" t="inlineStr"/>
+      <c r="H569" s="0" t="inlineStr"/>
       <c r="I569" s="0" t="inlineStr"/>
-      <c r="J569" t="inlineStr"/>
-      <c r="K569" t="inlineStr"/>
-      <c r="L569" t="inlineStr"/>
-      <c r="M569" t="inlineStr"/>
-      <c r="N569" t="inlineStr"/>
-      <c r="O569" t="inlineStr"/>
+      <c r="J569" s="0" t="inlineStr"/>
+      <c r="K569" s="0" t="inlineStr"/>
+      <c r="L569" s="0" t="inlineStr"/>
+      <c r="M569" s="0" t="inlineStr"/>
+      <c r="N569" s="0" t="inlineStr"/>
+      <c r="O569" s="0" t="inlineStr"/>
     </row>
     <row r="570" ht="15" customHeight="1" s="72">
       <c r="A570" s="33" t="inlineStr"/>
@@ -25116,38 +25084,38 @@
       <c r="O579" s="19" t="inlineStr"/>
     </row>
     <row r="580" ht="9.75" customHeight="1" s="72">
-      <c r="A580" t="inlineStr"/>
-      <c r="B580" t="inlineStr"/>
-      <c r="C580" t="inlineStr"/>
-      <c r="D580" t="inlineStr"/>
-      <c r="E580" t="inlineStr"/>
-      <c r="F580" t="inlineStr"/>
-      <c r="G580" t="inlineStr"/>
-      <c r="H580" t="inlineStr"/>
-      <c r="I580" t="inlineStr"/>
-      <c r="J580" t="inlineStr"/>
-      <c r="K580" t="inlineStr"/>
-      <c r="L580" t="inlineStr"/>
-      <c r="M580" t="inlineStr"/>
-      <c r="N580" t="inlineStr"/>
-      <c r="O580" t="inlineStr"/>
+      <c r="A580" s="0" t="inlineStr"/>
+      <c r="B580" s="0" t="inlineStr"/>
+      <c r="C580" s="0" t="inlineStr"/>
+      <c r="D580" s="0" t="inlineStr"/>
+      <c r="E580" s="0" t="inlineStr"/>
+      <c r="F580" s="0" t="inlineStr"/>
+      <c r="G580" s="0" t="inlineStr"/>
+      <c r="H580" s="0" t="inlineStr"/>
+      <c r="I580" s="0" t="inlineStr"/>
+      <c r="J580" s="0" t="inlineStr"/>
+      <c r="K580" s="0" t="inlineStr"/>
+      <c r="L580" s="0" t="inlineStr"/>
+      <c r="M580" s="0" t="inlineStr"/>
+      <c r="N580" s="0" t="inlineStr"/>
+      <c r="O580" s="0" t="inlineStr"/>
     </row>
     <row r="581" ht="15.75" customHeight="1" s="72">
       <c r="A581" s="84" t="inlineStr"/>
-      <c r="B581" t="inlineStr"/>
-      <c r="C581" t="inlineStr"/>
-      <c r="D581" t="inlineStr"/>
-      <c r="E581" t="inlineStr"/>
-      <c r="F581" t="inlineStr"/>
-      <c r="G581" t="inlineStr"/>
-      <c r="H581" t="inlineStr"/>
-      <c r="I581" t="inlineStr"/>
-      <c r="J581" t="inlineStr"/>
-      <c r="K581" t="inlineStr"/>
-      <c r="L581" t="inlineStr"/>
-      <c r="M581" t="inlineStr"/>
-      <c r="N581" t="inlineStr"/>
-      <c r="O581" t="inlineStr"/>
+      <c r="B581" s="0" t="inlineStr"/>
+      <c r="C581" s="0" t="inlineStr"/>
+      <c r="D581" s="0" t="inlineStr"/>
+      <c r="E581" s="0" t="inlineStr"/>
+      <c r="F581" s="0" t="inlineStr"/>
+      <c r="G581" s="0" t="inlineStr"/>
+      <c r="H581" s="0" t="inlineStr"/>
+      <c r="I581" s="0" t="inlineStr"/>
+      <c r="J581" s="0" t="inlineStr"/>
+      <c r="K581" s="0" t="inlineStr"/>
+      <c r="L581" s="0" t="inlineStr"/>
+      <c r="M581" s="0" t="inlineStr"/>
+      <c r="N581" s="0" t="inlineStr"/>
+      <c r="O581" s="0" t="inlineStr"/>
     </row>
     <row r="582" ht="15" customHeight="1" s="72">
       <c r="A582" s="39" t="inlineStr"/>
@@ -25170,18 +25138,18 @@
       <c r="A583" s="58" t="inlineStr"/>
       <c r="B583" s="95" t="inlineStr"/>
       <c r="C583" s="0" t="inlineStr"/>
-      <c r="D583" t="inlineStr"/>
-      <c r="E583" t="inlineStr"/>
-      <c r="F583" t="inlineStr"/>
-      <c r="G583" t="inlineStr"/>
-      <c r="H583" t="inlineStr"/>
-      <c r="I583" t="inlineStr"/>
-      <c r="J583" t="inlineStr"/>
-      <c r="K583" t="inlineStr"/>
-      <c r="L583" t="inlineStr"/>
-      <c r="M583" t="inlineStr"/>
-      <c r="N583" t="inlineStr"/>
-      <c r="O583" t="inlineStr"/>
+      <c r="D583" s="0" t="inlineStr"/>
+      <c r="E583" s="0" t="inlineStr"/>
+      <c r="F583" s="0" t="inlineStr"/>
+      <c r="G583" s="0" t="inlineStr"/>
+      <c r="H583" s="0" t="inlineStr"/>
+      <c r="I583" s="0" t="inlineStr"/>
+      <c r="J583" s="0" t="inlineStr"/>
+      <c r="K583" s="0" t="inlineStr"/>
+      <c r="L583" s="0" t="inlineStr"/>
+      <c r="M583" s="0" t="inlineStr"/>
+      <c r="N583" s="0" t="inlineStr"/>
+      <c r="O583" s="0" t="inlineStr"/>
     </row>
     <row r="584" ht="18" customHeight="1" s="72">
       <c r="A584" s="96" t="inlineStr"/>
@@ -25191,14 +25159,14 @@
       <c r="E584" s="0" t="inlineStr"/>
       <c r="F584" s="0" t="inlineStr"/>
       <c r="G584" s="0" t="inlineStr"/>
-      <c r="H584" t="inlineStr"/>
+      <c r="H584" s="0" t="inlineStr"/>
       <c r="I584" s="0" t="inlineStr"/>
-      <c r="J584" t="inlineStr"/>
-      <c r="K584" t="inlineStr"/>
-      <c r="L584" t="inlineStr"/>
-      <c r="M584" t="inlineStr"/>
-      <c r="N584" t="inlineStr"/>
-      <c r="O584" t="inlineStr"/>
+      <c r="J584" s="0" t="inlineStr"/>
+      <c r="K584" s="0" t="inlineStr"/>
+      <c r="L584" s="0" t="inlineStr"/>
+      <c r="M584" s="0" t="inlineStr"/>
+      <c r="N584" s="0" t="inlineStr"/>
+      <c r="O584" s="0" t="inlineStr"/>
     </row>
     <row r="585" ht="15" customHeight="1" s="72">
       <c r="A585" s="33" t="inlineStr"/>
@@ -25371,38 +25339,38 @@
       <c r="O594" s="19" t="inlineStr"/>
     </row>
     <row r="595" ht="9.75" customHeight="1" s="72">
-      <c r="A595" t="inlineStr"/>
-      <c r="B595" t="inlineStr"/>
-      <c r="C595" t="inlineStr"/>
-      <c r="D595" t="inlineStr"/>
-      <c r="E595" t="inlineStr"/>
-      <c r="F595" t="inlineStr"/>
-      <c r="G595" t="inlineStr"/>
-      <c r="H595" t="inlineStr"/>
-      <c r="I595" t="inlineStr"/>
-      <c r="J595" t="inlineStr"/>
-      <c r="K595" t="inlineStr"/>
-      <c r="L595" t="inlineStr"/>
-      <c r="M595" t="inlineStr"/>
-      <c r="N595" t="inlineStr"/>
-      <c r="O595" t="inlineStr"/>
+      <c r="A595" s="0" t="inlineStr"/>
+      <c r="B595" s="0" t="inlineStr"/>
+      <c r="C595" s="0" t="inlineStr"/>
+      <c r="D595" s="0" t="inlineStr"/>
+      <c r="E595" s="0" t="inlineStr"/>
+      <c r="F595" s="0" t="inlineStr"/>
+      <c r="G595" s="0" t="inlineStr"/>
+      <c r="H595" s="0" t="inlineStr"/>
+      <c r="I595" s="0" t="inlineStr"/>
+      <c r="J595" s="0" t="inlineStr"/>
+      <c r="K595" s="0" t="inlineStr"/>
+      <c r="L595" s="0" t="inlineStr"/>
+      <c r="M595" s="0" t="inlineStr"/>
+      <c r="N595" s="0" t="inlineStr"/>
+      <c r="O595" s="0" t="inlineStr"/>
     </row>
     <row r="596" ht="15.75" customHeight="1" s="72">
       <c r="A596" s="88" t="inlineStr"/>
-      <c r="B596" t="inlineStr"/>
-      <c r="C596" t="inlineStr"/>
-      <c r="D596" t="inlineStr"/>
-      <c r="E596" t="inlineStr"/>
-      <c r="F596" t="inlineStr"/>
-      <c r="G596" t="inlineStr"/>
-      <c r="H596" t="inlineStr"/>
-      <c r="I596" t="inlineStr"/>
-      <c r="J596" t="inlineStr"/>
-      <c r="K596" t="inlineStr"/>
-      <c r="L596" t="inlineStr"/>
-      <c r="M596" t="inlineStr"/>
-      <c r="N596" t="inlineStr"/>
-      <c r="O596" t="inlineStr"/>
+      <c r="B596" s="0" t="inlineStr"/>
+      <c r="C596" s="0" t="inlineStr"/>
+      <c r="D596" s="0" t="inlineStr"/>
+      <c r="E596" s="0" t="inlineStr"/>
+      <c r="F596" s="0" t="inlineStr"/>
+      <c r="G596" s="0" t="inlineStr"/>
+      <c r="H596" s="0" t="inlineStr"/>
+      <c r="I596" s="0" t="inlineStr"/>
+      <c r="J596" s="0" t="inlineStr"/>
+      <c r="K596" s="0" t="inlineStr"/>
+      <c r="L596" s="0" t="inlineStr"/>
+      <c r="M596" s="0" t="inlineStr"/>
+      <c r="N596" s="0" t="inlineStr"/>
+      <c r="O596" s="0" t="inlineStr"/>
     </row>
     <row r="597" ht="15" customHeight="1" s="72">
       <c r="A597" s="45" t="inlineStr"/>
@@ -25425,18 +25393,18 @@
       <c r="A598" s="46" t="inlineStr"/>
       <c r="B598" s="89" t="inlineStr"/>
       <c r="C598" s="0" t="inlineStr"/>
-      <c r="D598" t="inlineStr"/>
-      <c r="E598" t="inlineStr"/>
-      <c r="F598" t="inlineStr"/>
-      <c r="G598" t="inlineStr"/>
-      <c r="H598" t="inlineStr"/>
-      <c r="I598" t="inlineStr"/>
-      <c r="J598" t="inlineStr"/>
-      <c r="K598" t="inlineStr"/>
-      <c r="L598" t="inlineStr"/>
-      <c r="M598" t="inlineStr"/>
-      <c r="N598" t="inlineStr"/>
-      <c r="O598" t="inlineStr"/>
+      <c r="D598" s="0" t="inlineStr"/>
+      <c r="E598" s="0" t="inlineStr"/>
+      <c r="F598" s="0" t="inlineStr"/>
+      <c r="G598" s="0" t="inlineStr"/>
+      <c r="H598" s="0" t="inlineStr"/>
+      <c r="I598" s="0" t="inlineStr"/>
+      <c r="J598" s="0" t="inlineStr"/>
+      <c r="K598" s="0" t="inlineStr"/>
+      <c r="L598" s="0" t="inlineStr"/>
+      <c r="M598" s="0" t="inlineStr"/>
+      <c r="N598" s="0" t="inlineStr"/>
+      <c r="O598" s="0" t="inlineStr"/>
     </row>
     <row r="599" ht="18" customHeight="1" s="72">
       <c r="A599" s="92" t="inlineStr"/>
@@ -25446,14 +25414,14 @@
       <c r="E599" s="0" t="inlineStr"/>
       <c r="F599" s="0" t="inlineStr"/>
       <c r="G599" s="0" t="inlineStr"/>
-      <c r="H599" t="inlineStr"/>
+      <c r="H599" s="0" t="inlineStr"/>
       <c r="I599" s="0" t="inlineStr"/>
-      <c r="J599" t="inlineStr"/>
-      <c r="K599" t="inlineStr"/>
-      <c r="L599" t="inlineStr"/>
-      <c r="M599" t="inlineStr"/>
-      <c r="N599" t="inlineStr"/>
-      <c r="O599" t="inlineStr"/>
+      <c r="J599" s="0" t="inlineStr"/>
+      <c r="K599" s="0" t="inlineStr"/>
+      <c r="L599" s="0" t="inlineStr"/>
+      <c r="M599" s="0" t="inlineStr"/>
+      <c r="N599" s="0" t="inlineStr"/>
+      <c r="O599" s="0" t="inlineStr"/>
     </row>
     <row r="600" ht="15" customHeight="1" s="72">
       <c r="A600" s="33" t="inlineStr"/>
@@ -25626,38 +25594,38 @@
       <c r="O609" s="19" t="inlineStr"/>
     </row>
     <row r="610" ht="9.75" customHeight="1" s="72">
-      <c r="A610" t="inlineStr"/>
-      <c r="B610" t="inlineStr"/>
-      <c r="C610" t="inlineStr"/>
-      <c r="D610" t="inlineStr"/>
-      <c r="E610" t="inlineStr"/>
-      <c r="F610" t="inlineStr"/>
-      <c r="G610" t="inlineStr"/>
-      <c r="H610" t="inlineStr"/>
-      <c r="I610" t="inlineStr"/>
-      <c r="J610" t="inlineStr"/>
-      <c r="K610" t="inlineStr"/>
-      <c r="L610" t="inlineStr"/>
-      <c r="M610" t="inlineStr"/>
-      <c r="N610" t="inlineStr"/>
-      <c r="O610" t="inlineStr"/>
+      <c r="A610" s="0" t="inlineStr"/>
+      <c r="B610" s="0" t="inlineStr"/>
+      <c r="C610" s="0" t="inlineStr"/>
+      <c r="D610" s="0" t="inlineStr"/>
+      <c r="E610" s="0" t="inlineStr"/>
+      <c r="F610" s="0" t="inlineStr"/>
+      <c r="G610" s="0" t="inlineStr"/>
+      <c r="H610" s="0" t="inlineStr"/>
+      <c r="I610" s="0" t="inlineStr"/>
+      <c r="J610" s="0" t="inlineStr"/>
+      <c r="K610" s="0" t="inlineStr"/>
+      <c r="L610" s="0" t="inlineStr"/>
+      <c r="M610" s="0" t="inlineStr"/>
+      <c r="N610" s="0" t="inlineStr"/>
+      <c r="O610" s="0" t="inlineStr"/>
     </row>
     <row r="611" ht="15.75" customHeight="1" s="72">
       <c r="A611" s="84" t="inlineStr"/>
-      <c r="B611" t="inlineStr"/>
-      <c r="C611" t="inlineStr"/>
-      <c r="D611" t="inlineStr"/>
-      <c r="E611" t="inlineStr"/>
-      <c r="F611" t="inlineStr"/>
-      <c r="G611" t="inlineStr"/>
-      <c r="H611" t="inlineStr"/>
-      <c r="I611" t="inlineStr"/>
-      <c r="J611" t="inlineStr"/>
-      <c r="K611" t="inlineStr"/>
-      <c r="L611" t="inlineStr"/>
-      <c r="M611" t="inlineStr"/>
-      <c r="N611" t="inlineStr"/>
-      <c r="O611" t="inlineStr"/>
+      <c r="B611" s="0" t="inlineStr"/>
+      <c r="C611" s="0" t="inlineStr"/>
+      <c r="D611" s="0" t="inlineStr"/>
+      <c r="E611" s="0" t="inlineStr"/>
+      <c r="F611" s="0" t="inlineStr"/>
+      <c r="G611" s="0" t="inlineStr"/>
+      <c r="H611" s="0" t="inlineStr"/>
+      <c r="I611" s="0" t="inlineStr"/>
+      <c r="J611" s="0" t="inlineStr"/>
+      <c r="K611" s="0" t="inlineStr"/>
+      <c r="L611" s="0" t="inlineStr"/>
+      <c r="M611" s="0" t="inlineStr"/>
+      <c r="N611" s="0" t="inlineStr"/>
+      <c r="O611" s="0" t="inlineStr"/>
     </row>
     <row r="612" ht="15" customHeight="1" s="72">
       <c r="A612" s="39" t="inlineStr"/>
@@ -25680,18 +25648,18 @@
       <c r="A613" s="58" t="inlineStr"/>
       <c r="B613" s="95" t="inlineStr"/>
       <c r="C613" s="0" t="inlineStr"/>
-      <c r="D613" t="inlineStr"/>
-      <c r="E613" t="inlineStr"/>
-      <c r="F613" t="inlineStr"/>
-      <c r="G613" t="inlineStr"/>
-      <c r="H613" t="inlineStr"/>
-      <c r="I613" t="inlineStr"/>
-      <c r="J613" t="inlineStr"/>
-      <c r="K613" t="inlineStr"/>
-      <c r="L613" t="inlineStr"/>
-      <c r="M613" t="inlineStr"/>
-      <c r="N613" t="inlineStr"/>
-      <c r="O613" t="inlineStr"/>
+      <c r="D613" s="0" t="inlineStr"/>
+      <c r="E613" s="0" t="inlineStr"/>
+      <c r="F613" s="0" t="inlineStr"/>
+      <c r="G613" s="0" t="inlineStr"/>
+      <c r="H613" s="0" t="inlineStr"/>
+      <c r="I613" s="0" t="inlineStr"/>
+      <c r="J613" s="0" t="inlineStr"/>
+      <c r="K613" s="0" t="inlineStr"/>
+      <c r="L613" s="0" t="inlineStr"/>
+      <c r="M613" s="0" t="inlineStr"/>
+      <c r="N613" s="0" t="inlineStr"/>
+      <c r="O613" s="0" t="inlineStr"/>
     </row>
     <row r="614" ht="18" customHeight="1" s="72">
       <c r="A614" s="96" t="inlineStr"/>
@@ -25701,14 +25669,14 @@
       <c r="E614" s="0" t="inlineStr"/>
       <c r="F614" s="0" t="inlineStr"/>
       <c r="G614" s="0" t="inlineStr"/>
-      <c r="H614" t="inlineStr"/>
+      <c r="H614" s="0" t="inlineStr"/>
       <c r="I614" s="0" t="inlineStr"/>
-      <c r="J614" t="inlineStr"/>
-      <c r="K614" t="inlineStr"/>
-      <c r="L614" t="inlineStr"/>
-      <c r="M614" t="inlineStr"/>
-      <c r="N614" t="inlineStr"/>
-      <c r="O614" t="inlineStr"/>
+      <c r="J614" s="0" t="inlineStr"/>
+      <c r="K614" s="0" t="inlineStr"/>
+      <c r="L614" s="0" t="inlineStr"/>
+      <c r="M614" s="0" t="inlineStr"/>
+      <c r="N614" s="0" t="inlineStr"/>
+      <c r="O614" s="0" t="inlineStr"/>
     </row>
     <row r="615" ht="15" customHeight="1" s="72">
       <c r="A615" s="33" t="inlineStr"/>
@@ -25881,38 +25849,38 @@
       <c r="O624" s="19" t="inlineStr"/>
     </row>
     <row r="625" ht="9.75" customHeight="1" s="72">
-      <c r="A625" t="inlineStr"/>
-      <c r="B625" t="inlineStr"/>
-      <c r="C625" t="inlineStr"/>
-      <c r="D625" t="inlineStr"/>
-      <c r="E625" t="inlineStr"/>
-      <c r="F625" t="inlineStr"/>
-      <c r="G625" t="inlineStr"/>
-      <c r="H625" t="inlineStr"/>
-      <c r="I625" t="inlineStr"/>
-      <c r="J625" t="inlineStr"/>
-      <c r="K625" t="inlineStr"/>
-      <c r="L625" t="inlineStr"/>
-      <c r="M625" t="inlineStr"/>
-      <c r="N625" t="inlineStr"/>
-      <c r="O625" t="inlineStr"/>
+      <c r="A625" s="0" t="inlineStr"/>
+      <c r="B625" s="0" t="inlineStr"/>
+      <c r="C625" s="0" t="inlineStr"/>
+      <c r="D625" s="0" t="inlineStr"/>
+      <c r="E625" s="0" t="inlineStr"/>
+      <c r="F625" s="0" t="inlineStr"/>
+      <c r="G625" s="0" t="inlineStr"/>
+      <c r="H625" s="0" t="inlineStr"/>
+      <c r="I625" s="0" t="inlineStr"/>
+      <c r="J625" s="0" t="inlineStr"/>
+      <c r="K625" s="0" t="inlineStr"/>
+      <c r="L625" s="0" t="inlineStr"/>
+      <c r="M625" s="0" t="inlineStr"/>
+      <c r="N625" s="0" t="inlineStr"/>
+      <c r="O625" s="0" t="inlineStr"/>
     </row>
     <row r="626" ht="15.75" customHeight="1" s="72">
       <c r="A626" s="88" t="inlineStr"/>
-      <c r="B626" t="inlineStr"/>
-      <c r="C626" t="inlineStr"/>
-      <c r="D626" t="inlineStr"/>
-      <c r="E626" t="inlineStr"/>
-      <c r="F626" t="inlineStr"/>
-      <c r="G626" t="inlineStr"/>
-      <c r="H626" t="inlineStr"/>
-      <c r="I626" t="inlineStr"/>
-      <c r="J626" t="inlineStr"/>
-      <c r="K626" t="inlineStr"/>
-      <c r="L626" t="inlineStr"/>
-      <c r="M626" t="inlineStr"/>
-      <c r="N626" t="inlineStr"/>
-      <c r="O626" t="inlineStr"/>
+      <c r="B626" s="0" t="inlineStr"/>
+      <c r="C626" s="0" t="inlineStr"/>
+      <c r="D626" s="0" t="inlineStr"/>
+      <c r="E626" s="0" t="inlineStr"/>
+      <c r="F626" s="0" t="inlineStr"/>
+      <c r="G626" s="0" t="inlineStr"/>
+      <c r="H626" s="0" t="inlineStr"/>
+      <c r="I626" s="0" t="inlineStr"/>
+      <c r="J626" s="0" t="inlineStr"/>
+      <c r="K626" s="0" t="inlineStr"/>
+      <c r="L626" s="0" t="inlineStr"/>
+      <c r="M626" s="0" t="inlineStr"/>
+      <c r="N626" s="0" t="inlineStr"/>
+      <c r="O626" s="0" t="inlineStr"/>
     </row>
     <row r="627" ht="15" customHeight="1" s="72">
       <c r="A627" s="45" t="inlineStr"/>
@@ -25935,18 +25903,18 @@
       <c r="A628" s="46" t="inlineStr"/>
       <c r="B628" s="89" t="inlineStr"/>
       <c r="C628" s="0" t="inlineStr"/>
-      <c r="D628" t="inlineStr"/>
-      <c r="E628" t="inlineStr"/>
-      <c r="F628" t="inlineStr"/>
-      <c r="G628" t="inlineStr"/>
-      <c r="H628" t="inlineStr"/>
-      <c r="I628" t="inlineStr"/>
-      <c r="J628" t="inlineStr"/>
-      <c r="K628" t="inlineStr"/>
-      <c r="L628" t="inlineStr"/>
-      <c r="M628" t="inlineStr"/>
-      <c r="N628" t="inlineStr"/>
-      <c r="O628" t="inlineStr"/>
+      <c r="D628" s="0" t="inlineStr"/>
+      <c r="E628" s="0" t="inlineStr"/>
+      <c r="F628" s="0" t="inlineStr"/>
+      <c r="G628" s="0" t="inlineStr"/>
+      <c r="H628" s="0" t="inlineStr"/>
+      <c r="I628" s="0" t="inlineStr"/>
+      <c r="J628" s="0" t="inlineStr"/>
+      <c r="K628" s="0" t="inlineStr"/>
+      <c r="L628" s="0" t="inlineStr"/>
+      <c r="M628" s="0" t="inlineStr"/>
+      <c r="N628" s="0" t="inlineStr"/>
+      <c r="O628" s="0" t="inlineStr"/>
     </row>
     <row r="629" ht="18" customHeight="1" s="72">
       <c r="A629" s="92" t="inlineStr"/>
@@ -25956,14 +25924,14 @@
       <c r="E629" s="0" t="inlineStr"/>
       <c r="F629" s="0" t="inlineStr"/>
       <c r="G629" s="0" t="inlineStr"/>
-      <c r="H629" t="inlineStr"/>
+      <c r="H629" s="0" t="inlineStr"/>
       <c r="I629" s="0" t="inlineStr"/>
-      <c r="J629" t="inlineStr"/>
-      <c r="K629" t="inlineStr"/>
-      <c r="L629" t="inlineStr"/>
-      <c r="M629" t="inlineStr"/>
-      <c r="N629" t="inlineStr"/>
-      <c r="O629" t="inlineStr"/>
+      <c r="J629" s="0" t="inlineStr"/>
+      <c r="K629" s="0" t="inlineStr"/>
+      <c r="L629" s="0" t="inlineStr"/>
+      <c r="M629" s="0" t="inlineStr"/>
+      <c r="N629" s="0" t="inlineStr"/>
+      <c r="O629" s="0" t="inlineStr"/>
     </row>
     <row r="630" ht="15" customHeight="1" s="72">
       <c r="A630" s="33" t="inlineStr"/>
@@ -26136,72 +26104,72 @@
       <c r="O639" s="19" t="inlineStr"/>
     </row>
     <row r="640" ht="9.75" customHeight="1" s="72">
-      <c r="A640" t="inlineStr"/>
-      <c r="B640" t="inlineStr"/>
-      <c r="C640" t="inlineStr"/>
-      <c r="D640" t="inlineStr"/>
-      <c r="E640" t="inlineStr"/>
-      <c r="F640" t="inlineStr"/>
-      <c r="G640" t="inlineStr"/>
-      <c r="H640" t="inlineStr"/>
-      <c r="I640" t="inlineStr"/>
-      <c r="J640" t="inlineStr"/>
-      <c r="K640" t="inlineStr"/>
-      <c r="L640" t="inlineStr"/>
-      <c r="M640" t="inlineStr"/>
-      <c r="N640" t="inlineStr"/>
-      <c r="O640" t="inlineStr"/>
+      <c r="A640" s="0" t="inlineStr"/>
+      <c r="B640" s="0" t="inlineStr"/>
+      <c r="C640" s="0" t="inlineStr"/>
+      <c r="D640" s="0" t="inlineStr"/>
+      <c r="E640" s="0" t="inlineStr"/>
+      <c r="F640" s="0" t="inlineStr"/>
+      <c r="G640" s="0" t="inlineStr"/>
+      <c r="H640" s="0" t="inlineStr"/>
+      <c r="I640" s="0" t="inlineStr"/>
+      <c r="J640" s="0" t="inlineStr"/>
+      <c r="K640" s="0" t="inlineStr"/>
+      <c r="L640" s="0" t="inlineStr"/>
+      <c r="M640" s="0" t="inlineStr"/>
+      <c r="N640" s="0" t="inlineStr"/>
+      <c r="O640" s="0" t="inlineStr"/>
     </row>
     <row r="641" ht="3.75" customHeight="1" s="72">
       <c r="A641" s="103" t="inlineStr"/>
-      <c r="B641" t="inlineStr"/>
-      <c r="C641" t="inlineStr"/>
-      <c r="D641" t="inlineStr"/>
-      <c r="E641" t="inlineStr"/>
-      <c r="F641" t="inlineStr"/>
-      <c r="G641" t="inlineStr"/>
-      <c r="H641" t="inlineStr"/>
-      <c r="I641" t="inlineStr"/>
-      <c r="J641" t="inlineStr"/>
-      <c r="K641" t="inlineStr"/>
-      <c r="L641" t="inlineStr"/>
-      <c r="M641" t="inlineStr"/>
-      <c r="N641" t="inlineStr"/>
-      <c r="O641" t="inlineStr"/>
+      <c r="B641" s="0" t="inlineStr"/>
+      <c r="C641" s="0" t="inlineStr"/>
+      <c r="D641" s="0" t="inlineStr"/>
+      <c r="E641" s="0" t="inlineStr"/>
+      <c r="F641" s="0" t="inlineStr"/>
+      <c r="G641" s="0" t="inlineStr"/>
+      <c r="H641" s="0" t="inlineStr"/>
+      <c r="I641" s="0" t="inlineStr"/>
+      <c r="J641" s="0" t="inlineStr"/>
+      <c r="K641" s="0" t="inlineStr"/>
+      <c r="L641" s="0" t="inlineStr"/>
+      <c r="M641" s="0" t="inlineStr"/>
+      <c r="N641" s="0" t="inlineStr"/>
+      <c r="O641" s="0" t="inlineStr"/>
     </row>
     <row r="642" ht="9.75" customHeight="1" s="72">
-      <c r="A642" t="inlineStr"/>
-      <c r="B642" t="inlineStr"/>
-      <c r="C642" t="inlineStr"/>
-      <c r="D642" t="inlineStr"/>
-      <c r="E642" t="inlineStr"/>
-      <c r="F642" t="inlineStr"/>
-      <c r="G642" t="inlineStr"/>
-      <c r="H642" t="inlineStr"/>
-      <c r="I642" t="inlineStr"/>
-      <c r="J642" t="inlineStr"/>
-      <c r="K642" t="inlineStr"/>
-      <c r="L642" t="inlineStr"/>
-      <c r="M642" t="inlineStr"/>
-      <c r="N642" t="inlineStr"/>
-      <c r="O642" t="inlineStr"/>
+      <c r="A642" s="0" t="inlineStr"/>
+      <c r="B642" s="0" t="inlineStr"/>
+      <c r="C642" s="0" t="inlineStr"/>
+      <c r="D642" s="0" t="inlineStr"/>
+      <c r="E642" s="0" t="inlineStr"/>
+      <c r="F642" s="0" t="inlineStr"/>
+      <c r="G642" s="0" t="inlineStr"/>
+      <c r="H642" s="0" t="inlineStr"/>
+      <c r="I642" s="0" t="inlineStr"/>
+      <c r="J642" s="0" t="inlineStr"/>
+      <c r="K642" s="0" t="inlineStr"/>
+      <c r="L642" s="0" t="inlineStr"/>
+      <c r="M642" s="0" t="inlineStr"/>
+      <c r="N642" s="0" t="inlineStr"/>
+      <c r="O642" s="0" t="inlineStr"/>
     </row>
     <row r="643" ht="9.75" customHeight="1" s="72">
-      <c r="A643" t="inlineStr"/>
-      <c r="B643" t="inlineStr"/>
-      <c r="C643" t="inlineStr"/>
-      <c r="D643" t="inlineStr"/>
-      <c r="E643" t="inlineStr"/>
-      <c r="F643" t="inlineStr"/>
-      <c r="G643" t="inlineStr"/>
-      <c r="H643" t="inlineStr"/>
-      <c r="I643" t="inlineStr"/>
-      <c r="J643" t="inlineStr"/>
-      <c r="K643" t="inlineStr"/>
-      <c r="L643" t="inlineStr"/>
-      <c r="M643" t="inlineStr"/>
-      <c r="N643" t="inlineStr"/>
-      <c r="O643" t="inlineStr"/>
+      <c r="A643" s="0" t="inlineStr"/>
+      <c r="B643" s="0" t="inlineStr"/>
+      <c r="C643" s="0" t="inlineStr"/>
+      <c r="D643" s="0" t="inlineStr"/>
+      <c r="E643" s="0" t="inlineStr"/>
+      <c r="F643" s="0" t="inlineStr"/>
+      <c r="G643" s="0" t="inlineStr"/>
+      <c r="H643" s="0" t="inlineStr"/>
+      <c r="I643" s="0" t="inlineStr"/>
+      <c r="J643" s="0" t="inlineStr"/>
+      <c r="K643" s="0" t="inlineStr"/>
+      <c r="L643" s="0" t="inlineStr"/>
+      <c r="M643" s="0" t="inlineStr"/>
+      <c r="N643" s="0" t="inlineStr"/>
+      <c r="O643" s="0" t="inlineStr"/>
     </row>
     <row r="644" ht="27.75" customHeight="1" s="72">
       <c r="A644" s="104" t="inlineStr">
@@ -27405,20 +27373,20 @@
     </row>
     <row r="670" ht="18" customHeight="1" s="72">
       <c r="A670" s="82" t="inlineStr"/>
-      <c r="B670" t="inlineStr"/>
-      <c r="C670" t="inlineStr"/>
-      <c r="D670" t="inlineStr"/>
-      <c r="E670" t="inlineStr"/>
-      <c r="F670" t="inlineStr"/>
-      <c r="G670" t="inlineStr"/>
-      <c r="H670" t="inlineStr"/>
-      <c r="I670" t="inlineStr"/>
-      <c r="J670" t="inlineStr"/>
-      <c r="K670" t="inlineStr"/>
-      <c r="L670" t="inlineStr"/>
-      <c r="M670" t="inlineStr"/>
-      <c r="N670" t="inlineStr"/>
-      <c r="O670" t="inlineStr"/>
+      <c r="B670" s="0" t="inlineStr"/>
+      <c r="C670" s="0" t="inlineStr"/>
+      <c r="D670" s="0" t="inlineStr"/>
+      <c r="E670" s="0" t="inlineStr"/>
+      <c r="F670" s="0" t="inlineStr"/>
+      <c r="G670" s="0" t="inlineStr"/>
+      <c r="H670" s="0" t="inlineStr"/>
+      <c r="I670" s="0" t="inlineStr"/>
+      <c r="J670" s="0" t="inlineStr"/>
+      <c r="K670" s="0" t="inlineStr"/>
+      <c r="L670" s="0" t="inlineStr"/>
+      <c r="M670" s="0" t="inlineStr"/>
+      <c r="N670" s="0" t="inlineStr"/>
+      <c r="O670" s="0" t="inlineStr"/>
     </row>
     <row r="671" ht="15" customHeight="1" s="72">
       <c r="A671" s="33" t="inlineStr">
@@ -28204,48 +28172,48 @@
           <t>Başlık</t>
         </is>
       </c>
-      <c r="B683" t="inlineStr">
+      <c r="B683" s="0" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="C683" t="inlineStr">
+      <c r="C683" s="0" t="inlineStr">
         <is>
           <t>İçerik / URL</t>
         </is>
       </c>
-      <c r="D683" t="inlineStr">
+      <c r="D683" s="0" t="inlineStr">
         <is>
           <t>Genişlik</t>
         </is>
       </c>
-      <c r="E683" t="inlineStr">
+      <c r="E683" s="0" t="inlineStr">
         <is>
           <t>Yükseklik</t>
         </is>
       </c>
-      <c r="F683" t="inlineStr">
+      <c r="F683" s="0" t="inlineStr">
         <is>
           <t>Caption</t>
         </is>
       </c>
-      <c r="G683" t="inlineStr">
+      <c r="G683" s="0" t="inlineStr">
         <is>
           <t>Extra</t>
         </is>
       </c>
-      <c r="H683" t="inlineStr">
+      <c r="H683" s="0" t="inlineStr">
         <is>
           <t>Kod</t>
         </is>
       </c>
-      <c r="I683" t="inlineStr"/>
-      <c r="J683" t="inlineStr"/>
-      <c r="K683" t="inlineStr"/>
-      <c r="L683" t="inlineStr"/>
-      <c r="M683" t="inlineStr"/>
-      <c r="N683" t="inlineStr"/>
-      <c r="O683" t="inlineStr"/>
+      <c r="I683" s="0" t="inlineStr"/>
+      <c r="J683" s="0" t="inlineStr"/>
+      <c r="K683" s="0" t="inlineStr"/>
+      <c r="L683" s="0" t="inlineStr"/>
+      <c r="M683" s="0" t="inlineStr"/>
+      <c r="N683" s="0" t="inlineStr"/>
+      <c r="O683" s="0" t="inlineStr"/>
     </row>
     <row r="684" ht="15" customHeight="1" s="72">
       <c r="A684" s="39" t="inlineStr">
@@ -28305,22 +28273,22 @@
 VR kulaklık bağlıysa: Enter VR seçin</t>
         </is>
       </c>
-      <c r="D685" t="inlineStr"/>
-      <c r="E685" t="inlineStr"/>
-      <c r="F685" t="inlineStr"/>
-      <c r="G685" t="inlineStr"/>
-      <c r="H685" t="inlineStr">
+      <c r="D685" s="0" t="inlineStr"/>
+      <c r="E685" s="0" t="inlineStr"/>
+      <c r="F685" s="0" t="inlineStr"/>
+      <c r="G685" s="0" t="inlineStr"/>
+      <c r="H685" s="0" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="I685" t="inlineStr"/>
-      <c r="J685" t="inlineStr"/>
-      <c r="K685" t="inlineStr"/>
-      <c r="L685" t="inlineStr"/>
-      <c r="M685" t="inlineStr"/>
-      <c r="N685" t="inlineStr"/>
-      <c r="O685" t="inlineStr"/>
+      <c r="I685" s="0" t="inlineStr"/>
+      <c r="J685" s="0" t="inlineStr"/>
+      <c r="K685" s="0" t="inlineStr"/>
+      <c r="L685" s="0" t="inlineStr"/>
+      <c r="M685" s="0" t="inlineStr"/>
+      <c r="N685" s="0" t="inlineStr"/>
+      <c r="O685" s="0" t="inlineStr"/>
     </row>
     <row r="686" ht="18" customHeight="1" s="72">
       <c r="A686" s="96" t="inlineStr">
@@ -28358,18 +28326,18 @@
           <t>null</t>
         </is>
       </c>
-      <c r="H686" t="inlineStr">
+      <c r="H686" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
       <c r="I686" s="0" t="inlineStr"/>
-      <c r="J686" t="inlineStr"/>
-      <c r="K686" t="inlineStr"/>
-      <c r="L686" t="inlineStr"/>
-      <c r="M686" t="inlineStr"/>
-      <c r="N686" t="inlineStr"/>
-      <c r="O686" t="inlineStr"/>
+      <c r="J686" s="0" t="inlineStr"/>
+      <c r="K686" s="0" t="inlineStr"/>
+      <c r="L686" s="0" t="inlineStr"/>
+      <c r="M686" s="0" t="inlineStr"/>
+      <c r="N686" s="0" t="inlineStr"/>
+      <c r="O686" s="0" t="inlineStr"/>
     </row>
     <row r="687" ht="15" customHeight="1" s="72">
       <c r="A687" s="33" t="inlineStr">
@@ -28862,53 +28830,53 @@
       <c r="O696" s="19" t="inlineStr"/>
     </row>
     <row r="697" ht="9.75" customHeight="1" s="72">
-      <c r="A697" t="inlineStr">
+      <c r="A697" s="0" t="inlineStr">
         <is>
           <t>slot12</t>
         </is>
       </c>
-      <c r="B697" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="C697" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D697" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E697" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F697" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G697" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H697" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="I697" t="inlineStr"/>
-      <c r="J697" t="inlineStr"/>
-      <c r="K697" t="inlineStr"/>
-      <c r="L697" t="inlineStr"/>
-      <c r="M697" t="inlineStr"/>
-      <c r="N697" t="inlineStr"/>
-      <c r="O697" t="inlineStr"/>
+      <c r="B697" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C697" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D697" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E697" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F697" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G697" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H697" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I697" s="0" t="inlineStr"/>
+      <c r="J697" s="0" t="inlineStr"/>
+      <c r="K697" s="0" t="inlineStr"/>
+      <c r="L697" s="0" t="inlineStr"/>
+      <c r="M697" s="0" t="inlineStr"/>
+      <c r="N697" s="0" t="inlineStr"/>
+      <c r="O697" s="0" t="inlineStr"/>
     </row>
     <row r="698" ht="15.75" customHeight="1" s="72">
       <c r="A698" s="88" t="inlineStr">
@@ -28916,48 +28884,48 @@
           <t>slot13</t>
         </is>
       </c>
-      <c r="B698" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="C698" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D698" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E698" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F698" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G698" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H698" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="I698" t="inlineStr"/>
-      <c r="J698" t="inlineStr"/>
-      <c r="K698" t="inlineStr"/>
-      <c r="L698" t="inlineStr"/>
-      <c r="M698" t="inlineStr"/>
-      <c r="N698" t="inlineStr"/>
-      <c r="O698" t="inlineStr"/>
+      <c r="B698" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C698" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D698" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E698" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F698" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G698" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H698" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I698" s="0" t="inlineStr"/>
+      <c r="J698" s="0" t="inlineStr"/>
+      <c r="K698" s="0" t="inlineStr"/>
+      <c r="L698" s="0" t="inlineStr"/>
+      <c r="M698" s="0" t="inlineStr"/>
+      <c r="N698" s="0" t="inlineStr"/>
+      <c r="O698" s="0" t="inlineStr"/>
     </row>
     <row r="699" ht="15" customHeight="1" s="72">
       <c r="A699" s="45" t="inlineStr">
@@ -29024,38 +28992,38 @@
           <t>null</t>
         </is>
       </c>
-      <c r="D700" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E700" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F700" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G700" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H700" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="I700" t="inlineStr"/>
-      <c r="J700" t="inlineStr"/>
-      <c r="K700" t="inlineStr"/>
-      <c r="L700" t="inlineStr"/>
-      <c r="M700" t="inlineStr"/>
-      <c r="N700" t="inlineStr"/>
-      <c r="O700" t="inlineStr"/>
+      <c r="D700" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E700" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F700" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G700" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H700" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I700" s="0" t="inlineStr"/>
+      <c r="J700" s="0" t="inlineStr"/>
+      <c r="K700" s="0" t="inlineStr"/>
+      <c r="L700" s="0" t="inlineStr"/>
+      <c r="M700" s="0" t="inlineStr"/>
+      <c r="N700" s="0" t="inlineStr"/>
+      <c r="O700" s="0" t="inlineStr"/>
     </row>
     <row r="701" ht="18" customHeight="1" s="72">
       <c r="A701" s="92" t="inlineStr">
@@ -29093,18 +29061,18 @@
           <t>null</t>
         </is>
       </c>
-      <c r="H701" t="inlineStr">
+      <c r="H701" s="0" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
       <c r="I701" s="0" t="inlineStr"/>
-      <c r="J701" t="inlineStr"/>
-      <c r="K701" t="inlineStr"/>
-      <c r="L701" t="inlineStr"/>
-      <c r="M701" t="inlineStr"/>
-      <c r="N701" t="inlineStr"/>
-      <c r="O701" t="inlineStr"/>
+      <c r="J701" s="0" t="inlineStr"/>
+      <c r="K701" s="0" t="inlineStr"/>
+      <c r="L701" s="0" t="inlineStr"/>
+      <c r="M701" s="0" t="inlineStr"/>
+      <c r="N701" s="0" t="inlineStr"/>
+      <c r="O701" s="0" t="inlineStr"/>
     </row>
     <row r="702" ht="15" customHeight="1" s="72">
       <c r="A702" s="33" t="inlineStr">
@@ -29597,53 +29565,53 @@
       <c r="O711" s="19" t="inlineStr"/>
     </row>
     <row r="712" ht="9.75" customHeight="1" s="72">
-      <c r="A712" t="inlineStr">
+      <c r="A712" s="0" t="inlineStr">
         <is>
           <t>slot27</t>
         </is>
       </c>
-      <c r="B712" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="C712" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D712" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E712" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F712" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G712" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H712" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="I712" t="inlineStr"/>
-      <c r="J712" t="inlineStr"/>
-      <c r="K712" t="inlineStr"/>
-      <c r="L712" t="inlineStr"/>
-      <c r="M712" t="inlineStr"/>
-      <c r="N712" t="inlineStr"/>
-      <c r="O712" t="inlineStr"/>
+      <c r="B712" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C712" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D712" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E712" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F712" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G712" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H712" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I712" s="0" t="inlineStr"/>
+      <c r="J712" s="0" t="inlineStr"/>
+      <c r="K712" s="0" t="inlineStr"/>
+      <c r="L712" s="0" t="inlineStr"/>
+      <c r="M712" s="0" t="inlineStr"/>
+      <c r="N712" s="0" t="inlineStr"/>
+      <c r="O712" s="0" t="inlineStr"/>
     </row>
     <row r="713" ht="3.75" customHeight="1" s="72">
       <c r="A713" s="105" t="inlineStr">
@@ -29651,180 +29619,180 @@
           <t>slot28</t>
         </is>
       </c>
-      <c r="B713" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="C713" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D713" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E713" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F713" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G713" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H713" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="I713" t="inlineStr"/>
-      <c r="J713" t="inlineStr"/>
-      <c r="K713" t="inlineStr"/>
-      <c r="L713" t="inlineStr"/>
-      <c r="M713" t="inlineStr"/>
-      <c r="N713" t="inlineStr"/>
-      <c r="O713" t="inlineStr"/>
+      <c r="B713" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C713" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D713" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E713" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F713" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G713" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H713" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I713" s="0" t="inlineStr"/>
+      <c r="J713" s="0" t="inlineStr"/>
+      <c r="K713" s="0" t="inlineStr"/>
+      <c r="L713" s="0" t="inlineStr"/>
+      <c r="M713" s="0" t="inlineStr"/>
+      <c r="N713" s="0" t="inlineStr"/>
+      <c r="O713" s="0" t="inlineStr"/>
     </row>
     <row r="714" ht="9.75" customHeight="1" s="72">
-      <c r="A714" t="inlineStr">
+      <c r="A714" s="0" t="inlineStr">
         <is>
           <t>slot29</t>
         </is>
       </c>
-      <c r="B714" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="C714" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D714" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E714" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F714" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G714" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H714" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="I714" t="inlineStr"/>
-      <c r="J714" t="inlineStr"/>
-      <c r="K714" t="inlineStr"/>
-      <c r="L714" t="inlineStr"/>
-      <c r="M714" t="inlineStr"/>
-      <c r="N714" t="inlineStr"/>
-      <c r="O714" t="inlineStr"/>
+      <c r="B714" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C714" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D714" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E714" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F714" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G714" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H714" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I714" s="0" t="inlineStr"/>
+      <c r="J714" s="0" t="inlineStr"/>
+      <c r="K714" s="0" t="inlineStr"/>
+      <c r="L714" s="0" t="inlineStr"/>
+      <c r="M714" s="0" t="inlineStr"/>
+      <c r="N714" s="0" t="inlineStr"/>
+      <c r="O714" s="0" t="inlineStr"/>
     </row>
     <row r="715" ht="9.75" customHeight="1" s="72">
-      <c r="A715" t="inlineStr">
+      <c r="A715" s="0" t="inlineStr">
         <is>
           <t>slot30</t>
         </is>
       </c>
-      <c r="B715" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="C715" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="D715" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E715" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F715" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G715" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H715" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="I715" t="inlineStr"/>
-      <c r="J715" t="inlineStr"/>
-      <c r="K715" t="inlineStr"/>
-      <c r="L715" t="inlineStr"/>
-      <c r="M715" t="inlineStr"/>
-      <c r="N715" t="inlineStr"/>
-      <c r="O715" t="inlineStr"/>
+      <c r="B715" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C715" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D715" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E715" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F715" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G715" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H715" s="0" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I715" s="0" t="inlineStr"/>
+      <c r="J715" s="0" t="inlineStr"/>
+      <c r="K715" s="0" t="inlineStr"/>
+      <c r="L715" s="0" t="inlineStr"/>
+      <c r="M715" s="0" t="inlineStr"/>
+      <c r="N715" s="0" t="inlineStr"/>
+      <c r="O715" s="0" t="inlineStr"/>
     </row>
     <row r="716" ht="9.75" customHeight="1" s="72">
-      <c r="A716" t="inlineStr"/>
-      <c r="B716" t="inlineStr"/>
-      <c r="C716" t="inlineStr"/>
-      <c r="D716" t="inlineStr"/>
-      <c r="E716" t="inlineStr"/>
-      <c r="F716" t="inlineStr"/>
-      <c r="G716" t="inlineStr"/>
-      <c r="H716" t="inlineStr"/>
-      <c r="I716" t="inlineStr"/>
-      <c r="J716" t="inlineStr"/>
-      <c r="K716" t="inlineStr"/>
-      <c r="L716" t="inlineStr"/>
-      <c r="M716" t="inlineStr"/>
-      <c r="N716" t="inlineStr"/>
-      <c r="O716" t="inlineStr"/>
+      <c r="A716" s="0" t="inlineStr"/>
+      <c r="B716" s="0" t="inlineStr"/>
+      <c r="C716" s="0" t="inlineStr"/>
+      <c r="D716" s="0" t="inlineStr"/>
+      <c r="E716" s="0" t="inlineStr"/>
+      <c r="F716" s="0" t="inlineStr"/>
+      <c r="G716" s="0" t="inlineStr"/>
+      <c r="H716" s="0" t="inlineStr"/>
+      <c r="I716" s="0" t="inlineStr"/>
+      <c r="J716" s="0" t="inlineStr"/>
+      <c r="K716" s="0" t="inlineStr"/>
+      <c r="L716" s="0" t="inlineStr"/>
+      <c r="M716" s="0" t="inlineStr"/>
+      <c r="N716" s="0" t="inlineStr"/>
+      <c r="O716" s="0" t="inlineStr"/>
     </row>
     <row r="717" ht="19.5" customHeight="1" s="72">
       <c r="A717" s="106" t="inlineStr"/>
-      <c r="B717" t="inlineStr"/>
-      <c r="C717" t="inlineStr"/>
-      <c r="D717" t="inlineStr"/>
-      <c r="E717" t="inlineStr"/>
-      <c r="F717" t="inlineStr"/>
-      <c r="G717" t="inlineStr"/>
-      <c r="H717" t="inlineStr"/>
-      <c r="I717" t="inlineStr"/>
-      <c r="J717" t="inlineStr"/>
-      <c r="K717" t="inlineStr"/>
-      <c r="L717" t="inlineStr"/>
-      <c r="M717" t="inlineStr"/>
-      <c r="N717" t="inlineStr"/>
-      <c r="O717" t="inlineStr"/>
+      <c r="B717" s="0" t="inlineStr"/>
+      <c r="C717" s="0" t="inlineStr"/>
+      <c r="D717" s="0" t="inlineStr"/>
+      <c r="E717" s="0" t="inlineStr"/>
+      <c r="F717" s="0" t="inlineStr"/>
+      <c r="G717" s="0" t="inlineStr"/>
+      <c r="H717" s="0" t="inlineStr"/>
+      <c r="I717" s="0" t="inlineStr"/>
+      <c r="J717" s="0" t="inlineStr"/>
+      <c r="K717" s="0" t="inlineStr"/>
+      <c r="L717" s="0" t="inlineStr"/>
+      <c r="M717" s="0" t="inlineStr"/>
+      <c r="N717" s="0" t="inlineStr"/>
+      <c r="O717" s="0" t="inlineStr"/>
     </row>
     <row r="718" ht="15.75" customHeight="1" s="72"/>
     <row r="719" ht="15.75" customHeight="1" s="72"/>

--- a/demo2-xlsx/demo2-input_3.xlsx
+++ b/demo2-xlsx/demo2-input_3.xlsx
@@ -1051,7 +1051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:O717"/>
+  <dimension ref="A2:O751"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="18" customWidth="1" style="72" min="1" max="1"/>
@@ -29796,38 +29796,2320 @@
     </row>
     <row r="718" ht="15.75" customHeight="1" s="72"/>
     <row r="719" ht="15.75" customHeight="1" s="72"/>
-    <row r="720" ht="15.75" customHeight="1" s="72"/>
-    <row r="721" ht="15.75" customHeight="1" s="72"/>
-    <row r="722" ht="15.75" customHeight="1" s="72"/>
-    <row r="723" ht="15.75" customHeight="1" s="72"/>
-    <row r="724" ht="15.75" customHeight="1" s="72"/>
-    <row r="725" ht="15.75" customHeight="1" s="72"/>
-    <row r="726" ht="15.75" customHeight="1" s="72"/>
-    <row r="727" ht="15.75" customHeight="1" s="72"/>
-    <row r="728" ht="15.75" customHeight="1" s="72"/>
-    <row r="729" ht="15.75" customHeight="1" s="72"/>
-    <row r="730" ht="15.75" customHeight="1" s="72"/>
-    <row r="731" ht="15.75" customHeight="1" s="72"/>
-    <row r="732" ht="15.75" customHeight="1" s="72"/>
-    <row r="733" ht="15.75" customHeight="1" s="72"/>
-    <row r="734" ht="15.75" customHeight="1" s="72"/>
-    <row r="735" ht="15.75" customHeight="1" s="72"/>
-    <row r="736" ht="15.75" customHeight="1" s="72"/>
-    <row r="737" ht="15.75" customHeight="1" s="72"/>
-    <row r="738" ht="15.75" customHeight="1" s="72"/>
-    <row r="739" ht="15.75" customHeight="1" s="72"/>
-    <row r="740" ht="15.75" customHeight="1" s="72"/>
-    <row r="741" ht="15.75" customHeight="1" s="72"/>
-    <row r="742" ht="15.75" customHeight="1" s="72"/>
-    <row r="743" ht="15.75" customHeight="1" s="72"/>
-    <row r="744" ht="15.75" customHeight="1" s="72"/>
-    <row r="745" ht="15.75" customHeight="1" s="72"/>
-    <row r="746" ht="15.75" customHeight="1" s="72"/>
-    <row r="747" ht="15.75" customHeight="1" s="72"/>
-    <row r="748" ht="15.75" customHeight="1" s="72"/>
-    <row r="749" ht="15.75" customHeight="1" s="72"/>
-    <row r="750" ht="15.75" customHeight="1" s="72"/>
-    <row r="751" ht="15.75" customHeight="1" s="72"/>
+    <row r="720" ht="15.75" customHeight="1" s="72">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>▌ BÖLÜM 2  —  HOTSPOT SLOTLARI  (3D İşaretçiler &amp; Popup'lar)</t>
+        </is>
+      </c>
+    </row>
+    <row r="721" ht="15.75" customHeight="1" s="72">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>Hotspot Tip</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>Hotspot Link</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>Popup Tip</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>Popup İçerik / Link</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>Pos X</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>Pos Y</t>
+        </is>
+      </c>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>Pos Z</t>
+        </is>
+      </c>
+      <c r="J721" t="inlineStr">
+        <is>
+          <t>Rot X</t>
+        </is>
+      </c>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>Rot Y</t>
+        </is>
+      </c>
+      <c r="L721" t="inlineStr">
+        <is>
+          <t>Rot Z</t>
+        </is>
+      </c>
+      <c r="M721" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="N721" t="inlineStr">
+        <is>
+          <t>Toggle Kod</t>
+        </is>
+      </c>
+      <c r="O721" t="inlineStr">
+        <is>
+          <t>Sahne</t>
+        </is>
+      </c>
+    </row>
+    <row r="722" ht="15.75" customHeight="1" s="72">
+      <c r="A722" t="n">
+        <v>1</v>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>Giriş Noktası</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>png</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/decentralize-dfw/vea_001/main/VEADEMO1.jpg</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>Binanın ana giriş noktası. Güney cepheden erişim sağlanır.</t>
+        </is>
+      </c>
+      <c r="G722" t="n">
+        <v>0</v>
+      </c>
+      <c r="H722" t="n">
+        <v>2</v>
+      </c>
+      <c r="I722" t="n">
+        <v>5</v>
+      </c>
+      <c r="J722" t="n">
+        <v>0</v>
+      </c>
+      <c r="K722" t="n">
+        <v>0</v>
+      </c>
+      <c r="L722" t="n">
+        <v>0</v>
+      </c>
+      <c r="M722" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N722" t="inlineStr"/>
+      <c r="O722" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="723" ht="15.75" customHeight="1" s="72">
+      <c r="A723" t="n">
+        <v>2</v>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="J723" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L723" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M723" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N723" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="O723" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="724" ht="15.75" customHeight="1" s="72">
+      <c r="A724" t="n">
+        <v>3</v>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="J724" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L724" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M724" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N724" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="O724" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="725" ht="15.75" customHeight="1" s="72">
+      <c r="A725" t="n">
+        <v>4</v>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="J725" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L725" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M725" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N725" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="O725" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="726" ht="15.75" customHeight="1" s="72">
+      <c r="A726" t="n">
+        <v>5</v>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="J726" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L726" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M726" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N726" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="O726" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="727" ht="15.75" customHeight="1" s="72">
+      <c r="A727" t="n">
+        <v>6</v>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="J727" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L727" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M727" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N727" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="O727" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="728" ht="15.75" customHeight="1" s="72">
+      <c r="A728" t="n">
+        <v>7</v>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="J728" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L728" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M728" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N728" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="O728" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="729" ht="15.75" customHeight="1" s="72">
+      <c r="A729" t="n">
+        <v>8</v>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="J729" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L729" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M729" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N729" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="O729" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="730" ht="15.75" customHeight="1" s="72">
+      <c r="A730" t="n">
+        <v>9</v>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L730" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M730" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N730" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="O730" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="731" ht="15.75" customHeight="1" s="72">
+      <c r="A731" t="n">
+        <v>10</v>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="J731" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L731" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M731" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N731" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="O731" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="732" ht="15.75" customHeight="1" s="72">
+      <c r="A732" t="n">
+        <v>11</v>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="J732" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L732" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M732" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N732" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="O732" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="733" ht="15.75" customHeight="1" s="72">
+      <c r="A733" t="n">
+        <v>12</v>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="J733" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L733" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M733" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N733" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="O733" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="734" ht="15.75" customHeight="1" s="72">
+      <c r="A734" t="n">
+        <v>13</v>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="J734" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L734" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M734" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N734" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="O734" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="735" ht="15.75" customHeight="1" s="72">
+      <c r="A735" t="n">
+        <v>14</v>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="J735" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L735" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M735" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N735" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="O735" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="736" ht="15.75" customHeight="1" s="72">
+      <c r="A736" t="n">
+        <v>15</v>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I736" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="J736" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L736" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M736" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N736" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="O736" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="737" ht="15.75" customHeight="1" s="72">
+      <c r="A737" t="n">
+        <v>16</v>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L737" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M737" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N737" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="O737" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="738" ht="15.75" customHeight="1" s="72">
+      <c r="A738" t="n">
+        <v>17</v>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L738" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M738" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N738" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="O738" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="739" ht="15.75" customHeight="1" s="72">
+      <c r="A739" t="n">
+        <v>18</v>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="J739" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L739" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M739" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N739" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="O739" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="740" ht="15.75" customHeight="1" s="72">
+      <c r="A740" t="n">
+        <v>19</v>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="J740" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L740" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M740" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N740" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="O740" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="741" ht="15.75" customHeight="1" s="72">
+      <c r="A741" t="n">
+        <v>20</v>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L741" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M741" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N741" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="O741" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="742" ht="15.75" customHeight="1" s="72">
+      <c r="A742" t="n">
+        <v>21</v>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="J742" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L742" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M742" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N742" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="O742" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="743" ht="15.75" customHeight="1" s="72">
+      <c r="A743" t="n">
+        <v>22</v>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="J743" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L743" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M743" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N743" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="O743" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="744" ht="15.75" customHeight="1" s="72">
+      <c r="A744" t="n">
+        <v>23</v>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="J744" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L744" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M744" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N744" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="O744" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="745" ht="15.75" customHeight="1" s="72">
+      <c r="A745" t="n">
+        <v>24</v>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L745" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M745" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N745" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="O745" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="746" ht="15.75" customHeight="1" s="72">
+      <c r="A746" t="n">
+        <v>25</v>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="J746" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L746" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M746" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N746" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="O746" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="747" ht="15.75" customHeight="1" s="72">
+      <c r="A747" t="n">
+        <v>26</v>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="J747" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L747" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M747" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N747" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="O747" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="748" ht="15.75" customHeight="1" s="72">
+      <c r="A748" t="n">
+        <v>27</v>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="J748" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L748" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M748" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N748" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="O748" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="749" ht="15.75" customHeight="1" s="72">
+      <c r="A749" t="n">
+        <v>28</v>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="J749" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L749" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M749" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N749" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="O749" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="750" ht="15.75" customHeight="1" s="72">
+      <c r="A750" t="n">
+        <v>29</v>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="J750" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L750" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M750" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N750" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="O750" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="751" ht="15.75" customHeight="1" s="72">
+      <c r="A751" t="n">
+        <v>30</v>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="J751" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L751" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M751" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N751" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="O751" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
     <row r="752" ht="15.75" customHeight="1" s="72"/>
     <row r="753" ht="15.75" customHeight="1" s="72"/>
     <row r="754" ht="15.75" customHeight="1" s="72"/>
